--- a/data/3FEB_25_26/teams_25_26_3FEB.xlsx
+++ b/data/3FEB_25_26/teams_25_26_3FEB.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD15"/>
+  <dimension ref="A1:CD15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -579,6 +579,266 @@
           <t>PJ</t>
         </is>
       </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL_MINUTOS JUGADOS</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL_T2 CONVERTIDO</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL_T2 INTENTADO</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL_T3 CONVERTIDO</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL_T3 INTENTADO</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL_TL CONVERTIDOS</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL_TL INTENTADOS</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL_REB OFFENSIVO</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL_REB DEFENSIVO</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL_ASISTENCIAS</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL_RECUPEROS</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL_PERDIDAS</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL_FaltasCOMETIDAS</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL_FaltasRECIBIDAS</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL_TAPONES</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL_PLAYS</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL_POSS</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL_PPP</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL_PPP OPP</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL_OFFRTG</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL_DEFRTG</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL_NETRTG</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL_%OREB</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL_%DREB</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL_%REB</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>LOCAL_PJ</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>VISITANTE_MINUTOS JUGADOS</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>VISITANTE_T2 CONVERTIDO</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>VISITANTE_T2 INTENTADO</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>VISITANTE_T3 CONVERTIDO</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>VISITANTE_T3 INTENTADO</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>VISITANTE_TL CONVERTIDOS</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>VISITANTE_TL INTENTADOS</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>VISITANTE_REB OFFENSIVO</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>VISITANTE_REB DEFENSIVO</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>VISITANTE_ASISTENCIAS</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>VISITANTE_RECUPEROS</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>VISITANTE_PERDIDAS</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>VISITANTE_FaltasCOMETIDAS</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>VISITANTE_FaltasRECIBIDAS</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>VISITANTE_TAPONES</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>VISITANTE_PLAYS</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>VISITANTE_POSS</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>VISITANTE_PPP</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>VISITANTE_PPP OPP</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>VISITANTE_OFFRTG</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>VISITANTE_DEFRTG</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>VISITANTE_NETRTG</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>VISITANTE_%OREB</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>VISITANTE_%DREB</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>VISITANTE_%REB</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>VISITANTE_PJ</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -592,88 +852,244 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7932264412435124</v>
+        <v>0.79421905085401</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8992976359462221</v>
+        <v>0.8931077229714582</v>
       </c>
       <c r="E2" t="n">
-        <v>87.4664346378414</v>
+        <v>87.65138864477106</v>
       </c>
       <c r="F2" t="n">
-        <v>104.2302483697388</v>
+        <v>103.3387773577649</v>
       </c>
       <c r="G2" t="n">
-        <v>-16.7638137318974</v>
+        <v>-15.68738871299387</v>
       </c>
       <c r="H2" t="n">
-        <v>0.226156362485468</v>
+        <v>0.2287458374084601</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6328018275900354</v>
+        <v>0.6365387046513382</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4255063016022989</v>
+        <v>0.4284206934210179</v>
       </c>
       <c r="K2" t="n">
-        <v>4575</v>
+        <v>4775</v>
       </c>
       <c r="L2" t="n">
-        <v>1629</v>
+        <v>1703</v>
       </c>
       <c r="M2" t="n">
-        <v>422</v>
+        <v>445</v>
       </c>
       <c r="N2" t="n">
-        <v>916</v>
+        <v>958</v>
       </c>
       <c r="O2" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="P2" t="n">
-        <v>544</v>
+        <v>563</v>
       </c>
       <c r="Q2" t="n">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="R2" t="n">
-        <v>520</v>
+        <v>542</v>
       </c>
       <c r="S2" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="T2" t="n">
-        <v>517</v>
+        <v>540</v>
       </c>
       <c r="U2" t="n">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="V2" t="n">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="W2" t="n">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="X2" t="n">
-        <v>525</v>
+        <v>551</v>
       </c>
       <c r="Y2" t="n">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="Z2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AA2" t="n">
-        <v>1949</v>
+        <v>2020</v>
       </c>
       <c r="AB2" t="n">
-        <v>2060.8</v>
+        <v>2151.48</v>
       </c>
       <c r="AC2" t="n">
-        <v>1860.8</v>
+        <v>1941.48</v>
       </c>
       <c r="AD2" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>2275</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>227</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>469</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>72</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>261</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>175</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>275</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>93</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>252</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>89</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>167</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>267</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>237</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>925</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.8325794091126206</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.9326252458599732</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>91.32082229766547</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>108.5220535040225</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-17.201231206357</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0.2103867681662326</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0.6233329813250507</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0.4142152404063349</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>2500</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>218</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>489</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>81</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>302</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>179</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>267</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>117</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>288</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>168</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>109</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>225</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>284</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>246</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>17</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>1133.48</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>1016.48</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>0.7590553891169501</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>0.8568833269903194</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>84.28774112961786</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>98.5874408903622</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>-14.29969976074433</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>0.2455749842138355</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>0.6486439510337686</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>0.4414423586844773</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -688,88 +1104,244 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7798389713717182</v>
+        <v>0.7788429133784546</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8769533715354867</v>
+        <v>0.8743056798289419</v>
       </c>
       <c r="E3" t="n">
-        <v>88.60003873601418</v>
+        <v>88.38814205594136</v>
       </c>
       <c r="F3" t="n">
-        <v>100.2015447008609</v>
+        <v>99.83279827026803</v>
       </c>
       <c r="G3" t="n">
-        <v>-11.60150596484677</v>
+        <v>-11.44465621432664</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2825978129770437</v>
+        <v>0.2825392124128244</v>
       </c>
       <c r="I3" t="n">
-        <v>0.693671706083327</v>
+        <v>0.6945679673095176</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4869005962403929</v>
+        <v>0.4877946001676438</v>
       </c>
       <c r="K3" t="n">
-        <v>4500</v>
+        <v>4700</v>
       </c>
       <c r="L3" t="n">
-        <v>1621</v>
+        <v>1692</v>
       </c>
       <c r="M3" t="n">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="N3" t="n">
-        <v>949</v>
+        <v>989</v>
       </c>
       <c r="O3" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="P3" t="n">
-        <v>501</v>
+        <v>526</v>
       </c>
       <c r="Q3" t="n">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="R3" t="n">
-        <v>587</v>
+        <v>607</v>
       </c>
       <c r="S3" t="n">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="T3" t="n">
-        <v>607</v>
+        <v>632</v>
       </c>
       <c r="U3" t="n">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="V3" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="W3" t="n">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="X3" t="n">
-        <v>511</v>
+        <v>536</v>
       </c>
       <c r="Y3" t="n">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="Z3" t="n">
         <v>38</v>
       </c>
       <c r="AA3" t="n">
-        <v>1854</v>
+        <v>1928</v>
       </c>
       <c r="AB3" t="n">
-        <v>2074.28</v>
+        <v>2168.08</v>
       </c>
       <c r="AC3" t="n">
-        <v>1825.28</v>
+        <v>1910.08</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2425</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>225</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>520</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>278</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>191</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>291</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>141</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>298</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>119</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>88</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>195</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>269</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>262</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1121.04</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>980.04</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.7447167418509636</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.9173596606819795</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>85.18072152433017</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>105.3200257751431</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-20.1393042508129</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0.2893831029863625</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0.664883229227427</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0.4699609216836479</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>2275</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>227</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>469</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>70</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>248</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>195</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>316</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>117</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>334</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>154</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>81</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>191</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>267</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>264</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>1047.04</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>930.0400000000001</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>0.8160714641357174</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>0.8273377007165371</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>91.88714627224449</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>93.84673190131342</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>-1.959585629068915</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>0.2750731499689644</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>0.7269513179445258</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0.5072495221501847</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -784,88 +1356,244 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8609141374644953</v>
+        <v>0.8552340941452962</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8569956194411837</v>
+        <v>0.8565393372336615</v>
       </c>
       <c r="E4" t="n">
-        <v>96.43103268080809</v>
+        <v>96.45266167279361</v>
       </c>
       <c r="F4" t="n">
-        <v>96.32674195563141</v>
+        <v>96.18436661761011</v>
       </c>
       <c r="G4" t="n">
-        <v>0.104290725176662</v>
+        <v>0.2682950551834975</v>
       </c>
       <c r="H4" t="n">
-        <v>0.276842720735008</v>
+        <v>0.2861350388654794</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7227071598186717</v>
+        <v>0.7238938050439468</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5015828769638487</v>
+        <v>0.50535037336184</v>
       </c>
       <c r="K4" t="n">
-        <v>4400</v>
+        <v>4600</v>
       </c>
       <c r="L4" t="n">
-        <v>1689</v>
+        <v>1766</v>
       </c>
       <c r="M4" t="n">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="N4" t="n">
-        <v>789</v>
+        <v>837</v>
       </c>
       <c r="O4" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="P4" t="n">
-        <v>579</v>
+        <v>611</v>
       </c>
       <c r="Q4" t="n">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="R4" t="n">
-        <v>554</v>
+        <v>580</v>
       </c>
       <c r="S4" t="n">
-        <v>209</v>
+        <v>235</v>
       </c>
       <c r="T4" t="n">
-        <v>564</v>
+        <v>588</v>
       </c>
       <c r="U4" t="n">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="V4" t="n">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="W4" t="n">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="X4" t="n">
-        <v>548</v>
+        <v>573</v>
       </c>
       <c r="Y4" t="n">
-        <v>502</v>
+        <v>529</v>
       </c>
       <c r="Z4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AA4" t="n">
-        <v>1677</v>
+        <v>1752</v>
       </c>
       <c r="AB4" t="n">
-        <v>1959.76</v>
+        <v>2065.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>1750.76</v>
+        <v>1830.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2200</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>194</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>404</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>77</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>288</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>170</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>265</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>97</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>275</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>140</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>165</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>276</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>250</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>973.6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>876.6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.8112845099956398</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.8427723790680651</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>90.0643309952619</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>94.94027726900917</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-4.875946273747268</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.2579706936183871</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0.7094003932538758</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0.4840333923164064</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>2400</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>202</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>433</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>115</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>323</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>228</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>315</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>138</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>313</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>180</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>93</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>197</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>297</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>279</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>15</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>1091.6</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>953.6</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0.8955212129491478</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0.8691590488854583</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>102.308631460531</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>97.32478185382764</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>4.983849606703366</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0.3119523553419807</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>0.7371794325181783</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0.5248909393201541</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -963,6 +1691,162 @@
       <c r="AD5" t="n">
         <v>22</v>
       </c>
+      <c r="AE5" t="n">
+        <v>2400</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>218</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>465</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>72</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>306</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>152</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>261</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>105</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>318</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>150</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>108</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>173</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>261</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>231</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1058.84</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>953.84</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.7609639197224817</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.8300582054482447</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>84.47980423604744</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>94.89754631805302</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-10.4177420820056</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0.2248932579416265</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0.7055990021296555</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.4646934272215936</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>195</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>399</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>72</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>239</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>129</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>200</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>94</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>250</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>143</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>78</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>144</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>226</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>189</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>34</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>870</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>776</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0.8497493654267423</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0.8659530476704186</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>95.18769127030717</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>99.52050065476222</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>-4.332809384455037</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0.2753194409663689</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>0.6797123057390178</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0.4824204316939832</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1059,6 +1943,162 @@
       <c r="AD6" t="n">
         <v>22</v>
       </c>
+      <c r="AE6" t="n">
+        <v>2225</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>193</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>402</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>88</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>306</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>212</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>286</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>124</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>247</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>144</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>92</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>161</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>240</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>251</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>994.84</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>870.84</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.86869424566162</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.9001813857681568</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>99.21282133313046</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>103.2737218897539</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-4.060900556623451</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0.3023873469761691</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0.6554273861291534</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.4714508141145842</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>2200</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>185</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>393</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>98</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>308</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>195</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>274</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>141</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>288</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>142</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>102</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>147</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>219</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>248</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>41</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>968.5599999999999</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>827.5599999999999</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0.8889125882110558</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0.8044988712324487</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>103.6628342555971</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>90.65068987236315</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>13.01214438323399</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0.3404160576951831</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0.7251482951140941</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0.5324210545722137</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1155,6 +2195,162 @@
       <c r="AD7" t="n">
         <v>22</v>
       </c>
+      <c r="AE7" t="n">
+        <v>2225</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>203</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>423</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>105</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>311</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>189</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>307</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>149</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>266</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>162</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>107</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>135</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>266</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>257</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1004.08</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>855.08</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.9090901349216334</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.7725100510678167</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>106.5743399536909</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>90.05926312319251</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>16.51507683049837</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.3660971155739813</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.6584750752269134</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.5141991181747219</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>2225</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>238</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>457</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>75</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>291</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>171</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>251</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>139</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>283</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>170</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>139</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>145</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>251</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>228</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>36</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1003.44</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>864.4399999999999</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0.8707625284534896</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0.7404079264289493</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>100.873034714564</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>83.00693417814875</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>17.86610053641522</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0.3416891558818338</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0.729813023126999</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0.5301654327429968</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1251,6 +2447,162 @@
       <c r="AD8" t="n">
         <v>22</v>
       </c>
+      <c r="AE8" t="n">
+        <v>2200</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>225</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>430</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>107</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>316</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>164</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>275</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>124</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>236</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>172</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>111</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>142</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>249</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>252</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1009</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>885</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.9253628591597004</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.9093653200407121</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>105.4136550526525</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>102.410289398452</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>3.003365654200495</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0.3089596745490724</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0.6811995161557435</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0.4853324056179123</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>2200</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>251</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>439</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>114</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>315</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>177</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>259</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>135</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>311</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>174</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>101</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>176</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>252</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>229</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>25</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>1043.96</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>908.96</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0.9768864975052385</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0.8381641429136938</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>112.4975467875901</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>94.55467491312605</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>17.94287187446406</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0.3628221481796532</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0.7329371046994038</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0.558600385217771</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1347,6 +2699,162 @@
       <c r="AD9" t="n">
         <v>22</v>
       </c>
+      <c r="AE9" t="n">
+        <v>2250</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>224</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>463</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>88</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>287</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>185</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>260</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>122</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>246</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>128</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>154</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>282</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>234</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1018.4</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>896.4</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.8924302470204059</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.916204087882969</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>100.681634986238</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>103.8540478338802</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>-3.172412847642221</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.2805952855821541</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.6683499037971179</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.4608105522848097</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>2225</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>209</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>419</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>98</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>309</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>185</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>261</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>120</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>288</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>125</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>98</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>176</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>281</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>247</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>21</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1018.84</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>898.8399999999999</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.8847417279158093</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0.8726908458129556</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>100.0965245505916</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>100.8269359778485</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>-0.7304114272569897</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0.3019295435579464</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0.6788325578583657</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0.496100939586104</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1360,88 +2868,244 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.8133013749223772</v>
+        <v>0.8157211956343801</v>
       </c>
       <c r="D10" t="n">
-        <v>0.871750130415911</v>
+        <v>0.8671414328768302</v>
       </c>
       <c r="E10" t="n">
-        <v>92.15516956181369</v>
+        <v>92.25459836921318</v>
       </c>
       <c r="F10" t="n">
-        <v>97.11729209044762</v>
+        <v>96.88363240243056</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.962122528633909</v>
+        <v>-4.629034033217362</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2915979078853461</v>
+        <v>0.2883204430301665</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7362647496035581</v>
+        <v>0.7270793257077512</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5042018536195352</v>
+        <v>0.4986549633153544</v>
       </c>
       <c r="K10" t="n">
-        <v>4475</v>
+        <v>4675</v>
       </c>
       <c r="L10" t="n">
-        <v>1640</v>
+        <v>1727</v>
       </c>
       <c r="M10" t="n">
-        <v>404</v>
+        <v>429</v>
       </c>
       <c r="N10" t="n">
-        <v>862</v>
+        <v>910</v>
       </c>
       <c r="O10" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="P10" t="n">
-        <v>570</v>
+        <v>592</v>
       </c>
       <c r="Q10" t="n">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="R10" t="n">
-        <v>526</v>
+        <v>549</v>
       </c>
       <c r="S10" t="n">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="T10" t="n">
-        <v>552</v>
+        <v>573</v>
       </c>
       <c r="U10" t="n">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="V10" t="n">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="W10" t="n">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="X10" t="n">
-        <v>496</v>
+        <v>514</v>
       </c>
       <c r="Y10" t="n">
+        <v>504</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1804</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2126.56</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1876.56</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2450</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>214</v>
+      </c>
+      <c r="AG10" t="n">
         <v>486</v>
       </c>
-      <c r="Z10" t="n">
-        <v>33</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1716</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2026.44</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1784.44</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>22</v>
+      <c r="AH10" t="n">
+        <v>88</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>299</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>194</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>298</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>142</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>308</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>185</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>128</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>213</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>262</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>265</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1129.12</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>987.12</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.7874884738876604</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.8640924156729811</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>89.845713417261</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>96.15271479759168</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-6.307001380330674</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0.2993406720134754</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0.7458962851115857</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0.5081427539148284</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>2225</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>215</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>424</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>82</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>293</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>165</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>251</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>108</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>265</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>165</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>122</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>170</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>252</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>239</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>18</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>997.4400000000001</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>889.4400000000001</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0.8465205284489834</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0.8704676334628471</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>94.88247286225192</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>97.68099706225476</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>-2.79852420000284</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0.276298375048375</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0.7065517336308411</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0.4883046462977463</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -1456,88 +3120,244 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8659964842198242</v>
+        <v>0.8651488600654045</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8894924049662237</v>
+        <v>0.8825698282773843</v>
       </c>
       <c r="E11" t="n">
-        <v>99.16802165723639</v>
+        <v>98.90211241914531</v>
       </c>
       <c r="F11" t="n">
-        <v>99.22541318456575</v>
+        <v>99.12554737204009</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.05739152732933597</v>
+        <v>-0.2234349528947509</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3182660895611033</v>
+        <v>0.3152979987106205</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7324637522385526</v>
+        <v>0.7227668048483613</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5223887144796326</v>
+        <v>0.5175789749754031</v>
       </c>
       <c r="K11" t="n">
-        <v>4425</v>
+        <v>4625</v>
       </c>
       <c r="L11" t="n">
-        <v>1715</v>
+        <v>1790</v>
       </c>
       <c r="M11" t="n">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="N11" t="n">
-        <v>862</v>
+        <v>898</v>
       </c>
       <c r="O11" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="P11" t="n">
-        <v>554</v>
+        <v>573</v>
       </c>
       <c r="Q11" t="n">
-        <v>336</v>
+        <v>365</v>
       </c>
       <c r="R11" t="n">
-        <v>517</v>
+        <v>557</v>
       </c>
       <c r="S11" t="n">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="T11" t="n">
-        <v>541</v>
+        <v>568</v>
       </c>
       <c r="U11" t="n">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="V11" t="n">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="W11" t="n">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="X11" t="n">
-        <v>502</v>
+        <v>529</v>
       </c>
       <c r="Y11" t="n">
-        <v>473</v>
+        <v>498</v>
       </c>
       <c r="Z11" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AA11" t="n">
-        <v>1717</v>
+        <v>1794</v>
       </c>
       <c r="AB11" t="n">
-        <v>1973.48</v>
+        <v>2062.08</v>
       </c>
       <c r="AC11" t="n">
-        <v>1726.48</v>
+        <v>1807.08</v>
       </c>
       <c r="AD11" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2200</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>208</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>423</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>81</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>262</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>182</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>265</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>112</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>278</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>144</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>91</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>178</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>250</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>236</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>979.6</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>867.6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.8548206842280048</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.8645562443169893</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>96.5053428133982</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>99.03797808924797</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-2.532635275849762</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.2890379628790085</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.6919336187785066</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.4959883724417103</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>2425</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>230</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>475</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>102</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>311</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>183</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>292</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>143</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>290</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>168</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>103</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>168</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>279</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>262</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>26</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>1082.48</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>939.48</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0.8746163545830208</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>0.8990822802410793</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>101.0991512244135</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>99.20581921459949</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1.893332009814009</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0.3393696982229317</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0.7510305587457284</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0.537370360631288</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -1635,6 +3455,162 @@
       <c r="AD12" t="n">
         <v>22</v>
       </c>
+      <c r="AE12" t="n">
+        <v>2225</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>189</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>409</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>78</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>276</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>207</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>332</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>117</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>297</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>168</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>94</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>161</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>214</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>264</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>992.08</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>875.08</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.8326150419113723</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.8132670660103916</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>93.75148197408929</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>94.77946658778515</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>-1.027984613695842</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0.2698945497370477</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0.6739685297548448</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0.4802046638684241</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>2225</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>205</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>405</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>87</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>290</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>179</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>274</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>114</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>300</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>181</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>89</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>181</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>232</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>230</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>20</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>996.5599999999999</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>882.5599999999999</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0.8545907026542751</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0.8295703444047248</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>96.45771050675101</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>95.65050799610221</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0.8072025106488018</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0.2964350580724492</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>0.6832061096070086</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0.5047904799075101</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1648,88 +3624,244 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.764152160435032</v>
+        <v>0.7618110407067801</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8320716013647623</v>
+        <v>0.8365592782562316</v>
       </c>
       <c r="E13" t="n">
-        <v>86.83287074287749</v>
+        <v>86.42742413597821</v>
       </c>
       <c r="F13" t="n">
-        <v>94.78885824270829</v>
+        <v>95.2560109870852</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.955987499830806</v>
+        <v>-8.828586851106968</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3015342644310964</v>
+        <v>0.2963292173609696</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7173783052805086</v>
+        <v>0.7196327602348679</v>
       </c>
       <c r="J13" t="n">
-        <v>0.520495594230318</v>
+        <v>0.5196044814376954</v>
       </c>
       <c r="K13" t="n">
-        <v>4425</v>
+        <v>4625</v>
       </c>
       <c r="L13" t="n">
-        <v>1533</v>
+        <v>1584</v>
       </c>
       <c r="M13" t="n">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="N13" t="n">
-        <v>901</v>
+        <v>927</v>
       </c>
       <c r="O13" t="n">
+        <v>137</v>
+      </c>
+      <c r="P13" t="n">
+        <v>491</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>337</v>
+      </c>
+      <c r="R13" t="n">
+        <v>583</v>
+      </c>
+      <c r="S13" t="n">
+        <v>247</v>
+      </c>
+      <c r="T13" t="n">
+        <v>669</v>
+      </c>
+      <c r="U13" t="n">
+        <v>261</v>
+      </c>
+      <c r="V13" t="n">
         <v>131</v>
       </c>
-      <c r="P13" t="n">
-        <v>465</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>324</v>
-      </c>
-      <c r="R13" t="n">
-        <v>563</v>
-      </c>
-      <c r="S13" t="n">
-        <v>241</v>
-      </c>
-      <c r="T13" t="n">
-        <v>639</v>
-      </c>
-      <c r="U13" t="n">
-        <v>255</v>
-      </c>
-      <c r="V13" t="n">
-        <v>127</v>
-      </c>
       <c r="W13" t="n">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="X13" t="n">
-        <v>475</v>
+        <v>499</v>
       </c>
       <c r="Y13" t="n">
-        <v>505</v>
+        <v>524</v>
       </c>
       <c r="Z13" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="AA13" t="n">
-        <v>1696</v>
+        <v>1770</v>
       </c>
       <c r="AB13" t="n">
-        <v>1999.72</v>
+        <v>2071.52</v>
       </c>
       <c r="AC13" t="n">
-        <v>1758.72</v>
+        <v>1824.52</v>
       </c>
       <c r="AD13" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2225</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>202</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>449</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>71</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>243</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>140</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>254</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>113</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>129</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>77</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>196</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>229</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>239</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>35</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>999.7600000000001</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>886.7600000000001</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.7533543401955403</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.8970354519330868</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>84.79436881259511</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>101.9322365993565</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-17.1378677867614</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0.2771059079766087</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0.7035055059056577</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0.4931052979364868</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>2400</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>216</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>478</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>66</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>248</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>197</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>329</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>134</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>369</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>132</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>54</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>201</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>270</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>285</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>17</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>1071.76</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>937.76</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0.7695630161754164</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0.7811227857191141</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>87.92439151574608</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>89.13613750916981</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>-1.211745993423738</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0.3139505842966339</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>0.7344160767033108</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0.5438953996471366</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -1744,88 +3876,244 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.8799761036781867</v>
+        <v>0.8823809761212461</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8010601772164747</v>
+        <v>0.7971143611064209</v>
       </c>
       <c r="E14" t="n">
-        <v>102.0561002154936</v>
+        <v>102.2072859175755</v>
       </c>
       <c r="F14" t="n">
-        <v>90.04719660776537</v>
+        <v>89.50199670239273</v>
       </c>
       <c r="G14" t="n">
-        <v>12.00890360772826</v>
+        <v>12.70528921518279</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3555718494602838</v>
+        <v>0.3501456486476293</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7197637816016141</v>
+        <v>0.7240428266703186</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5352791530150728</v>
+        <v>0.5337452767970261</v>
       </c>
       <c r="K14" t="n">
-        <v>4400</v>
+        <v>4600</v>
       </c>
       <c r="L14" t="n">
-        <v>1774</v>
+        <v>1848</v>
       </c>
       <c r="M14" t="n">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="N14" t="n">
-        <v>887</v>
+        <v>916</v>
       </c>
       <c r="O14" t="n">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="P14" t="n">
-        <v>528</v>
+        <v>558</v>
       </c>
       <c r="Q14" t="n">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="R14" t="n">
-        <v>621</v>
+        <v>644</v>
       </c>
       <c r="S14" t="n">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="T14" t="n">
-        <v>543</v>
+        <v>570</v>
       </c>
       <c r="U14" t="n">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="V14" t="n">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="W14" t="n">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="X14" t="n">
-        <v>483</v>
+        <v>502</v>
       </c>
       <c r="Y14" t="n">
-        <v>513</v>
+        <v>537</v>
       </c>
       <c r="Z14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AA14" t="n">
-        <v>1552</v>
+        <v>1603</v>
       </c>
       <c r="AB14" t="n">
-        <v>2024.24</v>
+        <v>2103.36</v>
       </c>
       <c r="AC14" t="n">
-        <v>1740.24</v>
+        <v>1810.36</v>
       </c>
       <c r="AD14" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2400</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>227</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>464</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>87</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>290</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>220</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>330</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>146</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>281</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>178</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>122</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>192</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>260</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>275</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1091.2</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>945.2</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.8579125355168932</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.8001294364521695</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>99.14644894654832</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>90.47100931146706</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>8.675439635081265</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0.3391079582810658</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.6987378860353025</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0.5115993662105542</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>2200</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>216</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>452</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>90</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>268</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>211</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>314</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>147</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>289</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>175</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>101</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>154</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>242</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>262</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>20</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>1012.16</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>865.16</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0.9090738204169039</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0.7938251880019677</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>105.5463807950597</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>88.44489203794801</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>17.10148875711173</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0.3621867654111532</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>0.7516482164539725</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0.5579044519822681</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -1840,88 +4128,244 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.8853490855213964</v>
+        <v>0.880149129064686</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8236939815713545</v>
+        <v>0.8256619498203585</v>
       </c>
       <c r="E15" t="n">
-        <v>100.4537761277143</v>
+        <v>100.0750519163378</v>
       </c>
       <c r="F15" t="n">
-        <v>93.65181179708325</v>
+        <v>93.68616920294927</v>
       </c>
       <c r="G15" t="n">
-        <v>6.801964330631065</v>
+        <v>6.388882713388553</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3206387008983376</v>
+        <v>0.3273500617288446</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7008047185347842</v>
+        <v>0.7044125039803929</v>
       </c>
       <c r="J15" t="n">
-        <v>0.513855830278152</v>
+        <v>0.518617603891129</v>
       </c>
       <c r="K15" t="n">
-        <v>4400</v>
+        <v>4600</v>
       </c>
       <c r="L15" t="n">
-        <v>1909</v>
+        <v>1997</v>
       </c>
       <c r="M15" t="n">
-        <v>504</v>
+        <v>534</v>
       </c>
       <c r="N15" t="n">
-        <v>984</v>
+        <v>1036</v>
       </c>
       <c r="O15" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="P15" t="n">
-        <v>558</v>
+        <v>582</v>
       </c>
       <c r="Q15" t="n">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="R15" t="n">
-        <v>568</v>
+        <v>586</v>
       </c>
       <c r="S15" t="n">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="T15" t="n">
-        <v>595</v>
+        <v>624</v>
       </c>
       <c r="U15" t="n">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="V15" t="n">
+        <v>220</v>
+      </c>
+      <c r="W15" t="n">
+        <v>402</v>
+      </c>
+      <c r="X15" t="n">
+        <v>513</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>525</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1850</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2277.84</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1999.84</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2200</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>233</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>482</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>76</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>273</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>207</v>
       </c>
-      <c r="W15" t="n">
-        <v>371</v>
-      </c>
-      <c r="X15" t="n">
-        <v>494</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>508</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>76</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1763</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2162.92</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1903.92</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>22</v>
+      <c r="AK15" t="n">
+        <v>292</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>128</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>295</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>167</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>98</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>188</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>252</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>257</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1071.48</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>943.48</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.8417005746116856</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.8470073855075468</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>95.58730700069906</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>95.04760365974967</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.5397033409494014</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0.3078753317739781</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0.7223581563243425</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0.5121215224769812</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>2400</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>301</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>554</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>97</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>309</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>203</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>294</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>150</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>329</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>240</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>122</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>214</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>261</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>268</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>36</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>1206.36</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>1056.36</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0.9153936373132697</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0.8060953004404361</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>104.1888180890067</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>92.43818761754891</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>11.75063047145778</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0.3452018975208058</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0.6879623226651059</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0.5245723451874311</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data/3FEB_25_26/teams_25_26_3FEB.xlsx
+++ b/data/3FEB_25_26/teams_25_26_3FEB.xlsx
@@ -852,166 +852,166 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.79421905085401</v>
+        <v>0.7928294889524842</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8931077229714582</v>
+        <v>0.8986599544797419</v>
       </c>
       <c r="E2" t="n">
-        <v>87.65138864477106</v>
+        <v>87.60007049650642</v>
       </c>
       <c r="F2" t="n">
-        <v>103.3387773577649</v>
+        <v>103.77011001493</v>
       </c>
       <c r="G2" t="n">
-        <v>-15.68738871299387</v>
+        <v>-16.1700395184236</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2287458374084601</v>
+        <v>0.2296314275164409</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6365387046513382</v>
+        <v>0.6406535135261598</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4284206934210179</v>
+        <v>0.4298006004259114</v>
       </c>
       <c r="K2" t="n">
-        <v>4775</v>
+        <v>4975</v>
       </c>
       <c r="L2" t="n">
-        <v>1703</v>
+        <v>1773</v>
       </c>
       <c r="M2" t="n">
-        <v>445</v>
+        <v>468</v>
       </c>
       <c r="N2" t="n">
-        <v>958</v>
+        <v>1011</v>
       </c>
       <c r="O2" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="P2" t="n">
-        <v>563</v>
+        <v>579</v>
       </c>
       <c r="Q2" t="n">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="R2" t="n">
-        <v>542</v>
+        <v>567</v>
       </c>
       <c r="S2" t="n">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="T2" t="n">
-        <v>540</v>
+        <v>565</v>
       </c>
       <c r="U2" t="n">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="V2" t="n">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="W2" t="n">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="X2" t="n">
-        <v>551</v>
+        <v>571</v>
       </c>
       <c r="Y2" t="n">
-        <v>483</v>
+        <v>501</v>
       </c>
       <c r="Z2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="AA2" t="n">
-        <v>2020</v>
+        <v>2115</v>
       </c>
       <c r="AB2" t="n">
-        <v>2151.48</v>
+        <v>2243.48</v>
       </c>
       <c r="AC2" t="n">
-        <v>1941.48</v>
+        <v>2022.48</v>
       </c>
       <c r="AD2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE2" t="n">
-        <v>2275</v>
+        <v>2475</v>
       </c>
       <c r="AF2" t="n">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="AG2" t="n">
-        <v>469</v>
+        <v>522</v>
       </c>
       <c r="AH2" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AI2" t="n">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="AJ2" t="n">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="AK2" t="n">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="AL2" t="n">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="AM2" t="n">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="AN2" t="n">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="AO2" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="AP2" t="n">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="AQ2" t="n">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="AR2" t="n">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="AS2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AT2" t="n">
-        <v>1018</v>
+        <v>1110</v>
       </c>
       <c r="AU2" t="n">
-        <v>925</v>
+        <v>1006</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.8325794091126206</v>
+        <v>0.8266035887880183</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.9326252458599732</v>
+        <v>0.9404365819691645</v>
       </c>
       <c r="AX2" t="n">
-        <v>91.32082229766547</v>
+        <v>90.91239986339498</v>
       </c>
       <c r="AY2" t="n">
-        <v>108.5220535040225</v>
+        <v>108.9527791394979</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-17.201231206357</v>
+        <v>-18.04037927610286</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.2103867681662326</v>
+        <v>0.2136878708190465</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.6233329813250507</v>
+        <v>0.6326630760185513</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.4142152404063349</v>
+        <v>0.4181588421673454</v>
       </c>
       <c r="BD2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BE2" t="n">
         <v>2500</v>
@@ -1104,88 +1104,88 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7788429133784546</v>
+        <v>0.7761132237011646</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8743056798289419</v>
+        <v>0.8752694388958985</v>
       </c>
       <c r="E3" t="n">
-        <v>88.38814205594136</v>
+        <v>88.2741821754877</v>
       </c>
       <c r="F3" t="n">
-        <v>99.83279827026803</v>
+        <v>100.1415291687097</v>
       </c>
       <c r="G3" t="n">
-        <v>-11.44465621432664</v>
+        <v>-11.86734699322201</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2825392124128244</v>
+        <v>0.2860106476679811</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6945679673095176</v>
+        <v>0.6890651353382878</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4877946001676438</v>
+        <v>0.4863054415990148</v>
       </c>
       <c r="K3" t="n">
-        <v>4700</v>
+        <v>4900</v>
       </c>
       <c r="L3" t="n">
-        <v>1692</v>
+        <v>1756</v>
       </c>
       <c r="M3" t="n">
-        <v>452</v>
+        <v>473</v>
       </c>
       <c r="N3" t="n">
-        <v>989</v>
+        <v>1030</v>
       </c>
       <c r="O3" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="P3" t="n">
-        <v>526</v>
+        <v>555</v>
       </c>
       <c r="Q3" t="n">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="R3" t="n">
-        <v>607</v>
+        <v>620</v>
       </c>
       <c r="S3" t="n">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="T3" t="n">
-        <v>632</v>
+        <v>650</v>
       </c>
       <c r="U3" t="n">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="V3" t="n">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="W3" t="n">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="X3" t="n">
-        <v>536</v>
+        <v>556</v>
       </c>
       <c r="Y3" t="n">
-        <v>526</v>
+        <v>545</v>
       </c>
       <c r="Z3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="AA3" t="n">
-        <v>1928</v>
+        <v>2005</v>
       </c>
       <c r="AB3" t="n">
-        <v>2168.08</v>
+        <v>2257.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>1910.08</v>
+        <v>1984.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE3" t="n">
         <v>2425</v>
@@ -1266,82 +1266,82 @@
         <v>12</v>
       </c>
       <c r="BE3" t="n">
-        <v>2275</v>
+        <v>2475</v>
       </c>
       <c r="BF3" t="n">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="BG3" t="n">
-        <v>469</v>
+        <v>510</v>
       </c>
       <c r="BH3" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="BI3" t="n">
-        <v>248</v>
+        <v>277</v>
       </c>
       <c r="BJ3" t="n">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="BK3" t="n">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="BL3" t="n">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="BM3" t="n">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="BN3" t="n">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="BO3" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="BP3" t="n">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="BQ3" t="n">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="BR3" t="n">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="BS3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BT3" t="n">
-        <v>1047.04</v>
+        <v>1136.76</v>
       </c>
       <c r="BU3" t="n">
-        <v>930.0400000000001</v>
+        <v>1004.76</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.8160714641357174</v>
+        <v>0.8075097055513655</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.8273377007165371</v>
+        <v>0.8331792171098171</v>
       </c>
       <c r="BX3" t="n">
-        <v>91.88714627224449</v>
+        <v>91.36764282664525</v>
       </c>
       <c r="BY3" t="n">
-        <v>93.84673190131342</v>
+        <v>94.96303256227638</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-1.959585629068915</v>
+        <v>-3.595389735631134</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.2750731499689644</v>
+        <v>0.2826381923495995</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.7269513179445258</v>
+        <v>0.7132470414491486</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.5072495221501847</v>
+        <v>0.5026499615143817</v>
       </c>
       <c r="CD3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -1860,88 +1860,88 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8788034169363379</v>
+        <v>0.8789396993117592</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8523401285003032</v>
+        <v>0.8523930884133065</v>
       </c>
       <c r="E6" t="n">
-        <v>101.4378277943638</v>
+        <v>101.0512653000211</v>
       </c>
       <c r="F6" t="n">
-        <v>96.96220588105854</v>
+        <v>96.93093791543052</v>
       </c>
       <c r="G6" t="n">
-        <v>4.475621913305269</v>
+        <v>4.12032738459059</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3214017023356761</v>
+        <v>0.3117755413645598</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6902878406216236</v>
+        <v>0.6911677743245737</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5019359343433991</v>
+        <v>0.4973924544778555</v>
       </c>
       <c r="K6" t="n">
-        <v>4425</v>
+        <v>4625</v>
       </c>
       <c r="L6" t="n">
-        <v>1721</v>
+        <v>1796</v>
       </c>
       <c r="M6" t="n">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="N6" t="n">
-        <v>795</v>
+        <v>838</v>
       </c>
       <c r="O6" t="n">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="P6" t="n">
-        <v>614</v>
+        <v>640</v>
       </c>
       <c r="Q6" t="n">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="R6" t="n">
-        <v>560</v>
+        <v>576</v>
       </c>
       <c r="S6" t="n">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="T6" t="n">
-        <v>535</v>
+        <v>562</v>
       </c>
       <c r="U6" t="n">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="V6" t="n">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="W6" t="n">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="X6" t="n">
-        <v>459</v>
+        <v>475</v>
       </c>
       <c r="Y6" t="n">
-        <v>499</v>
+        <v>513</v>
       </c>
       <c r="Z6" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AA6" t="n">
-        <v>1679</v>
+        <v>1762</v>
       </c>
       <c r="AB6" t="n">
-        <v>1963.4</v>
+        <v>2048.44</v>
       </c>
       <c r="AC6" t="n">
-        <v>1698.4</v>
+        <v>1779.44</v>
       </c>
       <c r="AD6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE6" t="n">
         <v>2225</v>
@@ -2022,82 +2022,82 @@
         <v>11</v>
       </c>
       <c r="BE6" t="n">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="BF6" t="n">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="BG6" t="n">
-        <v>393</v>
+        <v>436</v>
       </c>
       <c r="BH6" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="BI6" t="n">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="BJ6" t="n">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="BK6" t="n">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="BL6" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="BM6" t="n">
-        <v>288</v>
+        <v>315</v>
       </c>
       <c r="BN6" t="n">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="BO6" t="n">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="BP6" t="n">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="BQ6" t="n">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="BR6" t="n">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="BS6" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="BT6" t="n">
-        <v>968.5599999999999</v>
+        <v>1053.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>827.5599999999999</v>
+        <v>908.6</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.8889125882110558</v>
+        <v>0.8883313651577199</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.8044988712324487</v>
+        <v>0.8085871491713599</v>
       </c>
       <c r="BX6" t="n">
-        <v>103.6628342555971</v>
+        <v>102.7365056030042</v>
       </c>
       <c r="BY6" t="n">
-        <v>90.65068987236315</v>
+        <v>91.11671927230073</v>
       </c>
       <c r="BZ6" t="n">
-        <v>13.01214438323399</v>
+        <v>11.61978633070346</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.3404160576951831</v>
+        <v>0.3203813862205845</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.7251482951140941</v>
+        <v>0.7239297968370425</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.5324210545722137</v>
+        <v>0.5211722914775206</v>
       </c>
       <c r="CD6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -2112,88 +2112,88 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.8899263316875614</v>
+        <v>0.8828071603471722</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7564589887483829</v>
+        <v>0.7480008392960273</v>
       </c>
       <c r="E7" t="n">
-        <v>103.7236873341274</v>
+        <v>103.1750037849061</v>
       </c>
       <c r="F7" t="n">
-        <v>86.53309865067062</v>
+        <v>85.65952282289264</v>
       </c>
       <c r="G7" t="n">
-        <v>17.1905886834568</v>
+        <v>17.51548096201343</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3538931357279076</v>
+        <v>0.3591586515658247</v>
       </c>
       <c r="I7" t="n">
-        <v>0.694144049176956</v>
+        <v>0.6909909001528111</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5221822754588593</v>
+        <v>0.5231941132847586</v>
       </c>
       <c r="K7" t="n">
-        <v>4450</v>
+        <v>4650</v>
       </c>
       <c r="L7" t="n">
-        <v>1782</v>
+        <v>1850</v>
       </c>
       <c r="M7" t="n">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="N7" t="n">
-        <v>880</v>
+        <v>914</v>
       </c>
       <c r="O7" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="P7" t="n">
-        <v>602</v>
+        <v>632</v>
       </c>
       <c r="Q7" t="n">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="R7" t="n">
-        <v>558</v>
+        <v>589</v>
       </c>
       <c r="S7" t="n">
-        <v>288</v>
+        <v>307</v>
       </c>
       <c r="T7" t="n">
-        <v>549</v>
+        <v>572</v>
       </c>
       <c r="U7" t="n">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="V7" t="n">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="W7" t="n">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="X7" t="n">
-        <v>517</v>
+        <v>538</v>
       </c>
       <c r="Y7" t="n">
-        <v>485</v>
+        <v>509</v>
       </c>
       <c r="Z7" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AA7" t="n">
-        <v>1473</v>
+        <v>1524</v>
       </c>
       <c r="AB7" t="n">
-        <v>2007.52</v>
+        <v>2101.16</v>
       </c>
       <c r="AC7" t="n">
-        <v>1719.52</v>
+        <v>1794.16</v>
       </c>
       <c r="AD7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE7" t="n">
         <v>2225</v>
@@ -2274,82 +2274,82 @@
         <v>11</v>
       </c>
       <c r="BE7" t="n">
-        <v>2225</v>
+        <v>2425</v>
       </c>
       <c r="BF7" t="n">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="BG7" t="n">
-        <v>457</v>
+        <v>491</v>
       </c>
       <c r="BH7" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="BI7" t="n">
-        <v>291</v>
+        <v>321</v>
       </c>
       <c r="BJ7" t="n">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="BK7" t="n">
-        <v>251</v>
+        <v>282</v>
       </c>
       <c r="BL7" t="n">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="BM7" t="n">
-        <v>283</v>
+        <v>306</v>
       </c>
       <c r="BN7" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="BO7" t="n">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="BP7" t="n">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="BQ7" t="n">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="BR7" t="n">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="BS7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BT7" t="n">
-        <v>1003.44</v>
+        <v>1097.08</v>
       </c>
       <c r="BU7" t="n">
-        <v>864.4399999999999</v>
+        <v>939.0799999999999</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.8707625284534896</v>
+        <v>0.858714433653916</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.7404079264289493</v>
+        <v>0.7255340618385538</v>
       </c>
       <c r="BX7" t="n">
-        <v>100.873034714564</v>
+        <v>100.0589456301867</v>
       </c>
       <c r="BY7" t="n">
-        <v>83.00693417814875</v>
+        <v>81.62642754761778</v>
       </c>
       <c r="BZ7" t="n">
-        <v>17.86610053641522</v>
+        <v>18.43251808256892</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.3416891558818338</v>
+        <v>0.352798392891681</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.729813023126999</v>
+        <v>0.7207970730015508</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.5301654327429968</v>
+        <v>0.5314395254689591</v>
       </c>
       <c r="CD7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -2364,88 +2364,88 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9511246783324694</v>
+        <v>0.9498924400998298</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8737647314772029</v>
+        <v>0.8675705963652832</v>
       </c>
       <c r="E8" t="n">
-        <v>108.9556009201213</v>
+        <v>108.6539176433104</v>
       </c>
       <c r="F8" t="n">
-        <v>98.48248215578904</v>
+        <v>97.83594119831035</v>
       </c>
       <c r="G8" t="n">
-        <v>10.47311876433228</v>
+        <v>10.81797644500007</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3358909113643628</v>
+        <v>0.3331446662062285</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7070683104275736</v>
+        <v>0.7044592023015666</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5219663954178416</v>
+        <v>0.5193890115807258</v>
       </c>
       <c r="K8" t="n">
-        <v>4400</v>
+        <v>4600</v>
       </c>
       <c r="L8" t="n">
-        <v>1956</v>
+        <v>2043</v>
       </c>
       <c r="M8" t="n">
-        <v>476</v>
+        <v>505</v>
       </c>
       <c r="N8" t="n">
-        <v>869</v>
+        <v>914</v>
       </c>
       <c r="O8" t="n">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="P8" t="n">
-        <v>631</v>
+        <v>656</v>
       </c>
       <c r="Q8" t="n">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="R8" t="n">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="S8" t="n">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="T8" t="n">
-        <v>547</v>
+        <v>569</v>
       </c>
       <c r="U8" t="n">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="V8" t="n">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="W8" t="n">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="X8" t="n">
-        <v>501</v>
+        <v>516</v>
       </c>
       <c r="Y8" t="n">
-        <v>481</v>
+        <v>496</v>
       </c>
       <c r="Z8" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AA8" t="n">
-        <v>1733</v>
+        <v>1803</v>
       </c>
       <c r="AB8" t="n">
-        <v>2052.96</v>
+        <v>2147.24</v>
       </c>
       <c r="AC8" t="n">
-        <v>1793.96</v>
+        <v>1879.24</v>
       </c>
       <c r="AD8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE8" t="n">
         <v>2200</v>
@@ -2526,82 +2526,82 @@
         <v>11</v>
       </c>
       <c r="BE8" t="n">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="BF8" t="n">
-        <v>251</v>
+        <v>280</v>
       </c>
       <c r="BG8" t="n">
-        <v>439</v>
+        <v>484</v>
       </c>
       <c r="BH8" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="BI8" t="n">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="BJ8" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="BK8" t="n">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="BL8" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="BM8" t="n">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="BN8" t="n">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="BO8" t="n">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="BP8" t="n">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="BQ8" t="n">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="BR8" t="n">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="BS8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BT8" t="n">
-        <v>1043.96</v>
+        <v>1138.24</v>
       </c>
       <c r="BU8" t="n">
-        <v>908.96</v>
+        <v>994.24</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.9768864975052385</v>
+        <v>0.9723778892949483</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.8381641429136938</v>
+        <v>0.8292587663294735</v>
       </c>
       <c r="BX8" t="n">
-        <v>112.4975467875901</v>
+        <v>111.6241583514135</v>
       </c>
       <c r="BY8" t="n">
-        <v>94.55467491312605</v>
+        <v>93.64278868151382</v>
       </c>
       <c r="BZ8" t="n">
-        <v>17.94287187446406</v>
+        <v>17.98136966989969</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.3628221481796532</v>
+        <v>0.3553142418919549</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.7329371046994038</v>
+        <v>0.725780581268571</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.558600385217771</v>
+        <v>0.5506075670466384</v>
       </c>
       <c r="CD8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -2616,166 +2616,166 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.8885859874681075</v>
+        <v>0.8743831858975031</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8944474668479624</v>
+        <v>0.8871317244136425</v>
       </c>
       <c r="E9" t="n">
-        <v>100.3890797684148</v>
+        <v>98.91306997899575</v>
       </c>
       <c r="F9" t="n">
-        <v>102.3404919058644</v>
+        <v>101.8519472883067</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.951412137449605</v>
+        <v>-2.938877309310904</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2912624145700503</v>
+        <v>0.2950500651704123</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6735912308277419</v>
+        <v>0.6671307425308836</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4784557459354568</v>
+        <v>0.477416168048935</v>
       </c>
       <c r="K9" t="n">
-        <v>4475</v>
+        <v>4675</v>
       </c>
       <c r="L9" t="n">
-        <v>1794</v>
+        <v>1845</v>
       </c>
       <c r="M9" t="n">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="N9" t="n">
-        <v>882</v>
+        <v>917</v>
       </c>
       <c r="O9" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P9" t="n">
-        <v>596</v>
+        <v>620</v>
       </c>
       <c r="Q9" t="n">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="R9" t="n">
-        <v>521</v>
+        <v>550</v>
       </c>
       <c r="S9" t="n">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="T9" t="n">
-        <v>534</v>
+        <v>555</v>
       </c>
       <c r="U9" t="n">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="V9" t="n">
+        <v>182</v>
+      </c>
+      <c r="W9" t="n">
+        <v>349</v>
+      </c>
+      <c r="X9" t="n">
+        <v>588</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>501</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1891</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2128</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1872</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2450</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>236</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>498</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>90</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>311</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>206</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>289</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>136</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>267</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>135</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>84</v>
+      </c>
+      <c r="AP9" t="n">
         <v>173</v>
       </c>
-      <c r="W9" t="n">
-        <v>330</v>
-      </c>
-      <c r="X9" t="n">
-        <v>563</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>481</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>37</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1823</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2037.24</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1795.24</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2250</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>224</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>463</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>88</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>287</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>185</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>260</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>122</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>246</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>128</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>154</v>
-      </c>
       <c r="AQ9" t="n">
-        <v>282</v>
+        <v>307</v>
       </c>
       <c r="AR9" t="n">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="AS9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AT9" t="n">
-        <v>1018.4</v>
+        <v>1109.16</v>
       </c>
       <c r="AU9" t="n">
-        <v>896.4</v>
+        <v>973.16</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.8924302470204059</v>
+        <v>0.8648878557140557</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.916204087882969</v>
+        <v>0.9003691964642723</v>
       </c>
       <c r="AX9" t="n">
-        <v>100.681634986238</v>
+        <v>97.82823662169959</v>
       </c>
       <c r="AY9" t="n">
-        <v>103.8540478338802</v>
+        <v>102.7915409895599</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-3.172412847642221</v>
+        <v>-4.963304367860325</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.2805952855821541</v>
+        <v>0.2887438766485061</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.6683499037971179</v>
+        <v>0.6564040784806914</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.4608105522848097</v>
+        <v>0.4602884608065301</v>
       </c>
       <c r="BD9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BE9" t="n">
         <v>2225</v>
@@ -2868,88 +2868,88 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.8157211956343801</v>
+        <v>0.8244978657817087</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8671414328768302</v>
+        <v>0.8627134383910202</v>
       </c>
       <c r="E10" t="n">
-        <v>92.25459836921318</v>
+        <v>93.14777181756794</v>
       </c>
       <c r="F10" t="n">
-        <v>96.88363240243056</v>
+        <v>96.44763743093011</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.629034033217362</v>
+        <v>-3.299865613362164</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2883204430301665</v>
+        <v>0.2873365030019487</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7270793257077512</v>
+        <v>0.7280343538032615</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4986549633153544</v>
+        <v>0.500313570613112</v>
       </c>
       <c r="K10" t="n">
-        <v>4675</v>
+        <v>4875</v>
       </c>
       <c r="L10" t="n">
-        <v>1727</v>
+        <v>1822</v>
       </c>
       <c r="M10" t="n">
-        <v>429</v>
+        <v>456</v>
       </c>
       <c r="N10" t="n">
-        <v>910</v>
+        <v>961</v>
       </c>
       <c r="O10" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="P10" t="n">
-        <v>592</v>
+        <v>612</v>
       </c>
       <c r="Q10" t="n">
-        <v>359</v>
+        <v>376</v>
       </c>
       <c r="R10" t="n">
-        <v>549</v>
+        <v>573</v>
       </c>
       <c r="S10" t="n">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="T10" t="n">
-        <v>573</v>
+        <v>606</v>
       </c>
       <c r="U10" t="n">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="V10" t="n">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="W10" t="n">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="X10" t="n">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="Y10" t="n">
-        <v>504</v>
+        <v>524</v>
       </c>
       <c r="Z10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA10" t="n">
-        <v>1804</v>
+        <v>1874</v>
       </c>
       <c r="AB10" t="n">
-        <v>2126.56</v>
+        <v>2219.12</v>
       </c>
       <c r="AC10" t="n">
-        <v>1876.56</v>
+        <v>1960.12</v>
       </c>
       <c r="AD10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE10" t="n">
         <v>2450</v>
@@ -3030,82 +3030,82 @@
         <v>12</v>
       </c>
       <c r="BE10" t="n">
-        <v>2225</v>
+        <v>2425</v>
       </c>
       <c r="BF10" t="n">
-        <v>215</v>
+        <v>242</v>
       </c>
       <c r="BG10" t="n">
-        <v>424</v>
+        <v>475</v>
       </c>
       <c r="BH10" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="BI10" t="n">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="BJ10" t="n">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="BK10" t="n">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="BL10" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="BM10" t="n">
-        <v>265</v>
+        <v>298</v>
       </c>
       <c r="BN10" t="n">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="BO10" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="BP10" t="n">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="BQ10" t="n">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="BR10" t="n">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="BS10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BT10" t="n">
-        <v>997.4400000000001</v>
+        <v>1090</v>
       </c>
       <c r="BU10" t="n">
-        <v>889.4400000000001</v>
+        <v>973</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.8465205284489834</v>
+        <v>0.8615072576757571</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.8704676334628471</v>
+        <v>0.8613344611090591</v>
       </c>
       <c r="BX10" t="n">
-        <v>94.88247286225192</v>
+        <v>96.44983021787486</v>
       </c>
       <c r="BY10" t="n">
-        <v>97.68099706225476</v>
+        <v>96.74256006426852</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-2.79852420000284</v>
+        <v>-0.292729846393654</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.276298375048375</v>
+        <v>0.2753323339904222</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.7065517336308411</v>
+        <v>0.7101724224949377</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.4883046462977463</v>
+        <v>0.4924843873113957</v>
       </c>
       <c r="CD10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -3120,166 +3120,166 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8651488600654045</v>
+        <v>0.8595718085586398</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8825698282773843</v>
+        <v>0.8842453853900665</v>
       </c>
       <c r="E11" t="n">
-        <v>98.90211241914531</v>
+        <v>98.26502607392173</v>
       </c>
       <c r="F11" t="n">
-        <v>99.12554737204009</v>
+        <v>99.24601979626637</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2234349528947509</v>
+        <v>-0.9809937223446218</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3152979987106205</v>
+        <v>0.3168664644506192</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7227668048483613</v>
+        <v>0.7229545516160432</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5175789749754031</v>
+        <v>0.5184012440529205</v>
       </c>
       <c r="K11" t="n">
-        <v>4625</v>
+        <v>4825</v>
       </c>
       <c r="L11" t="n">
-        <v>1790</v>
+        <v>1860</v>
       </c>
       <c r="M11" t="n">
-        <v>438</v>
+        <v>463</v>
       </c>
       <c r="N11" t="n">
-        <v>898</v>
+        <v>939</v>
       </c>
       <c r="O11" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P11" t="n">
-        <v>573</v>
+        <v>600</v>
       </c>
       <c r="Q11" t="n">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="R11" t="n">
-        <v>557</v>
+        <v>570</v>
       </c>
       <c r="S11" t="n">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="T11" t="n">
-        <v>568</v>
+        <v>592</v>
       </c>
       <c r="U11" t="n">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="V11" t="n">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="W11" t="n">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="X11" t="n">
-        <v>529</v>
+        <v>544</v>
       </c>
       <c r="Y11" t="n">
-        <v>498</v>
+        <v>513</v>
       </c>
       <c r="Z11" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AA11" t="n">
-        <v>1794</v>
+        <v>1881</v>
       </c>
       <c r="AB11" t="n">
-        <v>2062.08</v>
+        <v>2157.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>1807.08</v>
+        <v>1890.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE11" t="n">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="AF11" t="n">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="AG11" t="n">
-        <v>423</v>
+        <v>464</v>
       </c>
       <c r="AH11" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="AI11" t="n">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="AJ11" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="AK11" t="n">
+        <v>278</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>124</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>302</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>157</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>106</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>200</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>265</v>
       </c>
-      <c r="AL11" t="n">
-        <v>112</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>278</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>144</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>91</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>178</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>250</v>
-      </c>
       <c r="AR11" t="n">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="AS11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AT11" t="n">
-        <v>979.6</v>
+        <v>1075.32</v>
       </c>
       <c r="AU11" t="n">
-        <v>867.6</v>
+        <v>951.3199999999999</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.8548206842280048</v>
+        <v>0.8445272625342586</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.8645562443169893</v>
+        <v>0.8694084905390532</v>
       </c>
       <c r="AX11" t="n">
-        <v>96.5053428133982</v>
+        <v>95.43090092342997</v>
       </c>
       <c r="AY11" t="n">
-        <v>99.03797808924797</v>
+        <v>99.28622037793322</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-2.532635275849762</v>
+        <v>-3.855319454503253</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.2890379628790085</v>
+        <v>0.2943632306783068</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.6919336187785066</v>
+        <v>0.6948785444863583</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.4959883724417103</v>
+        <v>0.4994321274745528</v>
       </c>
       <c r="BD11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BE11" t="n">
         <v>2425</v>
@@ -3372,166 +3372,166 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.8436028722828236</v>
+        <v>0.8344884557429629</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8214187052075581</v>
+        <v>0.8258706688338877</v>
       </c>
       <c r="E12" t="n">
-        <v>95.10459624042015</v>
+        <v>93.86452312443944</v>
       </c>
       <c r="F12" t="n">
-        <v>95.21498729194369</v>
+        <v>95.4950585621211</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1103910515235201</v>
+        <v>-1.630535437681617</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2831648039047484</v>
+        <v>0.2764633888682166</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6785873196809266</v>
+        <v>0.6826238958438676</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4924975718879671</v>
+        <v>0.4915062413579238</v>
       </c>
       <c r="K12" t="n">
-        <v>4450</v>
+        <v>4650</v>
       </c>
       <c r="L12" t="n">
-        <v>1669</v>
+        <v>1722</v>
       </c>
       <c r="M12" t="n">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="N12" t="n">
-        <v>814</v>
+        <v>843</v>
       </c>
       <c r="O12" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="P12" t="n">
-        <v>566</v>
+        <v>587</v>
       </c>
       <c r="Q12" t="n">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="R12" t="n">
-        <v>606</v>
+        <v>621</v>
       </c>
       <c r="S12" t="n">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="T12" t="n">
-        <v>597</v>
+        <v>624</v>
       </c>
       <c r="U12" t="n">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="V12" t="n">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="W12" t="n">
-        <v>342</v>
+        <v>369</v>
       </c>
       <c r="X12" t="n">
-        <v>446</v>
+        <v>467</v>
       </c>
       <c r="Y12" t="n">
-        <v>494</v>
+        <v>514</v>
       </c>
       <c r="Z12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AA12" t="n">
-        <v>1677</v>
+        <v>1758</v>
       </c>
       <c r="AB12" t="n">
-        <v>1988.64</v>
+        <v>2072.24</v>
       </c>
       <c r="AC12" t="n">
-        <v>1757.64</v>
+        <v>1837.24</v>
       </c>
       <c r="AD12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE12" t="n">
-        <v>2225</v>
+        <v>2425</v>
       </c>
       <c r="AF12" t="n">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="AG12" t="n">
-        <v>409</v>
+        <v>438</v>
       </c>
       <c r="AH12" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AI12" t="n">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="AJ12" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="AK12" t="n">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="AL12" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="AM12" t="n">
-        <v>297</v>
+        <v>324</v>
       </c>
       <c r="AN12" t="n">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="AO12" t="n">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="AP12" t="n">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="AQ12" t="n">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="AR12" t="n">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="AS12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT12" t="n">
-        <v>992.08</v>
+        <v>1075.68</v>
       </c>
       <c r="AU12" t="n">
-        <v>875.08</v>
+        <v>954.6799999999999</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.8326150419113723</v>
+        <v>0.8160613960742603</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.8132670660103916</v>
+        <v>0.8224792995606204</v>
       </c>
       <c r="AX12" t="n">
-        <v>93.75148197408929</v>
+        <v>91.48743469065387</v>
       </c>
       <c r="AY12" t="n">
-        <v>94.77946658778515</v>
+        <v>95.3525632476384</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-1.027984613695842</v>
+        <v>-3.865128556984502</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.2698945497370477</v>
+        <v>0.2581560254310034</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.6739685297548448</v>
+        <v>0.6820901998943221</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.4802046638684241</v>
+        <v>0.4793290226874696</v>
       </c>
       <c r="BD12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BE12" t="n">
         <v>2225</v>
@@ -3624,166 +3624,166 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.7618110407067801</v>
+        <v>0.7674620764038266</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8365592782562316</v>
+        <v>0.8314247400423675</v>
       </c>
       <c r="E13" t="n">
-        <v>86.42742413597821</v>
+        <v>87.29471229001534</v>
       </c>
       <c r="F13" t="n">
-        <v>95.2560109870852</v>
+        <v>94.8558899011672</v>
       </c>
       <c r="G13" t="n">
-        <v>-8.828586851106968</v>
+        <v>-7.561177611151865</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2963292173609696</v>
+        <v>0.3022113333042626</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7196327602348679</v>
+        <v>0.7160708261193905</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5196044814376954</v>
+        <v>0.5207853449394354</v>
       </c>
       <c r="K13" t="n">
-        <v>4625</v>
+        <v>4825</v>
       </c>
       <c r="L13" t="n">
-        <v>1584</v>
+        <v>1661</v>
       </c>
       <c r="M13" t="n">
-        <v>418</v>
+        <v>442</v>
       </c>
       <c r="N13" t="n">
-        <v>927</v>
+        <v>970</v>
       </c>
       <c r="O13" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="P13" t="n">
-        <v>491</v>
+        <v>510</v>
       </c>
       <c r="Q13" t="n">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="R13" t="n">
-        <v>583</v>
+        <v>603</v>
       </c>
       <c r="S13" t="n">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="T13" t="n">
-        <v>669</v>
+        <v>695</v>
       </c>
       <c r="U13" t="n">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="V13" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="W13" t="n">
-        <v>397</v>
+        <v>412</v>
       </c>
       <c r="X13" t="n">
-        <v>499</v>
+        <v>519</v>
       </c>
       <c r="Y13" t="n">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="Z13" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AA13" t="n">
-        <v>1770</v>
+        <v>1834</v>
       </c>
       <c r="AB13" t="n">
-        <v>2071.52</v>
+        <v>2157.32</v>
       </c>
       <c r="AC13" t="n">
-        <v>1824.52</v>
+        <v>1896.32</v>
       </c>
       <c r="AD13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE13" t="n">
-        <v>2225</v>
+        <v>2425</v>
       </c>
       <c r="AF13" t="n">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="AG13" t="n">
-        <v>449</v>
+        <v>492</v>
       </c>
       <c r="AH13" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="AI13" t="n">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="AJ13" t="n">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="AK13" t="n">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="AL13" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="AM13" t="n">
-        <v>300</v>
+        <v>326</v>
       </c>
       <c r="AN13" t="n">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="AO13" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AP13" t="n">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="AQ13" t="n">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="AR13" t="n">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="AS13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="AT13" t="n">
-        <v>999.7600000000001</v>
+        <v>1085.56</v>
       </c>
       <c r="AU13" t="n">
-        <v>886.7600000000001</v>
+        <v>958.5600000000001</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.7533543401955403</v>
+        <v>0.7653611366322367</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.8970354519330868</v>
+        <v>0.8817266943656207</v>
       </c>
       <c r="AX13" t="n">
-        <v>84.79436881259511</v>
+        <v>86.6650330642846</v>
       </c>
       <c r="AY13" t="n">
-        <v>101.9322365993565</v>
+        <v>100.5756422931646</v>
       </c>
       <c r="AZ13" t="n">
-        <v>-17.1378677867614</v>
+        <v>-13.91060922887999</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.2771059079766087</v>
+        <v>0.2904720823118913</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.7035055059056577</v>
+        <v>0.6977255755354709</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.4931052979364868</v>
+        <v>0.4976752902317338</v>
       </c>
       <c r="BD13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BE13" t="n">
         <v>2400</v>
@@ -3876,88 +3876,88 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.8823809761212461</v>
+        <v>0.8841073466417416</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7971143611064209</v>
+        <v>0.7903167332214046</v>
       </c>
       <c r="E14" t="n">
-        <v>102.2072859175755</v>
+        <v>102.1843417754275</v>
       </c>
       <c r="F14" t="n">
-        <v>89.50199670239273</v>
+        <v>88.54703494699572</v>
       </c>
       <c r="G14" t="n">
-        <v>12.70528921518279</v>
+        <v>13.63730682843183</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3501456486476293</v>
+        <v>0.3450800561444543</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7240428266703186</v>
+        <v>0.7301646981397005</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5337452767970261</v>
+        <v>0.5336018498597763</v>
       </c>
       <c r="K14" t="n">
-        <v>4600</v>
+        <v>4800</v>
       </c>
       <c r="L14" t="n">
-        <v>1848</v>
+        <v>1929</v>
       </c>
       <c r="M14" t="n">
-        <v>443</v>
+        <v>462</v>
       </c>
       <c r="N14" t="n">
-        <v>916</v>
+        <v>955</v>
       </c>
       <c r="O14" t="n">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="P14" t="n">
+        <v>581</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>447</v>
+      </c>
+      <c r="R14" t="n">
+        <v>666</v>
+      </c>
+      <c r="S14" t="n">
+        <v>301</v>
+      </c>
+      <c r="T14" t="n">
+        <v>597</v>
+      </c>
+      <c r="U14" t="n">
+        <v>377</v>
+      </c>
+      <c r="V14" t="n">
+        <v>243</v>
+      </c>
+      <c r="W14" t="n">
+        <v>362</v>
+      </c>
+      <c r="X14" t="n">
+        <v>522</v>
+      </c>
+      <c r="Y14" t="n">
         <v>558</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>431</v>
-      </c>
-      <c r="R14" t="n">
-        <v>644</v>
-      </c>
-      <c r="S14" t="n">
-        <v>293</v>
-      </c>
-      <c r="T14" t="n">
-        <v>570</v>
-      </c>
-      <c r="U14" t="n">
-        <v>353</v>
-      </c>
-      <c r="V14" t="n">
-        <v>223</v>
-      </c>
-      <c r="W14" t="n">
-        <v>346</v>
-      </c>
-      <c r="X14" t="n">
-        <v>502</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>537</v>
       </c>
       <c r="Z14" t="n">
         <v>45</v>
       </c>
       <c r="AA14" t="n">
-        <v>1603</v>
+        <v>1656</v>
       </c>
       <c r="AB14" t="n">
-        <v>2103.36</v>
+        <v>2191.04</v>
       </c>
       <c r="AC14" t="n">
-        <v>1810.36</v>
+        <v>1890.04</v>
       </c>
       <c r="AD14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE14" t="n">
         <v>2400</v>
@@ -4038,82 +4038,82 @@
         <v>12</v>
       </c>
       <c r="BE14" t="n">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="BF14" t="n">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="BG14" t="n">
-        <v>452</v>
+        <v>491</v>
       </c>
       <c r="BH14" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="BI14" t="n">
-        <v>268</v>
+        <v>291</v>
       </c>
       <c r="BJ14" t="n">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="BK14" t="n">
-        <v>314</v>
+        <v>336</v>
       </c>
       <c r="BL14" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="BM14" t="n">
-        <v>289</v>
+        <v>316</v>
       </c>
       <c r="BN14" t="n">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="BO14" t="n">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="BP14" t="n">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="BQ14" t="n">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="BR14" t="n">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="BS14" t="n">
         <v>20</v>
       </c>
       <c r="BT14" t="n">
-        <v>1012.16</v>
+        <v>1099.84</v>
       </c>
       <c r="BU14" t="n">
-        <v>865.16</v>
+        <v>944.84</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.9090738204169039</v>
+        <v>0.9103021577665901</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.7938251880019677</v>
+        <v>0.7805040299906394</v>
       </c>
       <c r="BX14" t="n">
-        <v>105.5463807950597</v>
+        <v>105.2222346043068</v>
       </c>
       <c r="BY14" t="n">
-        <v>88.44489203794801</v>
+        <v>86.62306058252437</v>
       </c>
       <c r="BZ14" t="n">
-        <v>17.10148875711173</v>
+        <v>18.5991740217824</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.3621867654111532</v>
+        <v>0.3510521540078428</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.7516482164539725</v>
+        <v>0.7615915102440985</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.5579044519822681</v>
+        <v>0.5556043335089983</v>
       </c>
       <c r="CD14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -4128,166 +4128,166 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.880149129064686</v>
+        <v>0.8790411739577983</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8256619498203585</v>
+        <v>0.8280067815599695</v>
       </c>
       <c r="E15" t="n">
-        <v>100.0750519163378</v>
+        <v>99.91538486447435</v>
       </c>
       <c r="F15" t="n">
-        <v>93.68616920294927</v>
+        <v>93.63869925384647</v>
       </c>
       <c r="G15" t="n">
-        <v>6.388882713388553</v>
+        <v>6.276685610627879</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3273500617288446</v>
+        <v>0.325771879332248</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7044125039803929</v>
+        <v>0.7125619829812098</v>
       </c>
       <c r="J15" t="n">
-        <v>0.518617603891129</v>
+        <v>0.5221153746691695</v>
       </c>
       <c r="K15" t="n">
-        <v>4600</v>
+        <v>4800</v>
       </c>
       <c r="L15" t="n">
-        <v>1997</v>
+        <v>2080</v>
       </c>
       <c r="M15" t="n">
-        <v>534</v>
+        <v>555</v>
       </c>
       <c r="N15" t="n">
-        <v>1036</v>
+        <v>1075</v>
       </c>
       <c r="O15" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="P15" t="n">
-        <v>582</v>
+        <v>612</v>
       </c>
       <c r="Q15" t="n">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="R15" t="n">
-        <v>586</v>
+        <v>607</v>
       </c>
       <c r="S15" t="n">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="T15" t="n">
-        <v>624</v>
+        <v>660</v>
       </c>
       <c r="U15" t="n">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="V15" t="n">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="W15" t="n">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="X15" t="n">
-        <v>513</v>
+        <v>528</v>
       </c>
       <c r="Y15" t="n">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="Z15" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AA15" t="n">
-        <v>1850</v>
+        <v>1925</v>
       </c>
       <c r="AB15" t="n">
-        <v>2277.84</v>
+        <v>2375.08</v>
       </c>
       <c r="AC15" t="n">
-        <v>1999.84</v>
+        <v>2086.08</v>
       </c>
       <c r="AD15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE15" t="n">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="AF15" t="n">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="AG15" t="n">
-        <v>482</v>
+        <v>521</v>
       </c>
       <c r="AH15" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI15" t="n">
+        <v>303</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>221</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>313</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>139</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>331</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>177</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>106</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>207</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>267</v>
+      </c>
+      <c r="AR15" t="n">
         <v>273</v>
       </c>
-      <c r="AJ15" t="n">
-        <v>207</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>292</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>128</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>295</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>167</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>98</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>188</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>252</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>257</v>
-      </c>
       <c r="AS15" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="AT15" t="n">
-        <v>1071.48</v>
+        <v>1168.72</v>
       </c>
       <c r="AU15" t="n">
-        <v>943.48</v>
+        <v>1029.72</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.8417005746116856</v>
+        <v>0.842688710602327</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.8470073855075468</v>
+        <v>0.8499182626795033</v>
       </c>
       <c r="AX15" t="n">
-        <v>95.58730700069906</v>
+        <v>95.64195163994198</v>
       </c>
       <c r="AY15" t="n">
-        <v>95.04760365974967</v>
+        <v>94.839210890144</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.5397033409494014</v>
+        <v>0.8027407497979802</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.3078753317739781</v>
+        <v>0.3063418611436905</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.7223581563243425</v>
+        <v>0.737161643297314</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.5121215224769812</v>
+        <v>0.5196584041509079</v>
       </c>
       <c r="BD15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BE15" t="n">
         <v>2400</v>

--- a/data/3FEB_25_26/teams_25_26_3FEB.xlsx
+++ b/data/3FEB_25_26/teams_25_26_3FEB.xlsx
@@ -1356,166 +1356,166 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8552340941452962</v>
+        <v>0.8536788351285879</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8565393372336615</v>
+        <v>0.8577192244666079</v>
       </c>
       <c r="E4" t="n">
-        <v>96.45266167279361</v>
+        <v>96.39609639872283</v>
       </c>
       <c r="F4" t="n">
-        <v>96.18436661761011</v>
+        <v>96.27691719472472</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2682950551834975</v>
+        <v>0.1191792039981164</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2861350388654794</v>
+        <v>0.2874241276932389</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7238938050439468</v>
+        <v>0.7249815631671157</v>
       </c>
       <c r="J4" t="n">
-        <v>0.50535037336184</v>
+        <v>0.5059391294501182</v>
       </c>
       <c r="K4" t="n">
-        <v>4600</v>
+        <v>4800</v>
       </c>
       <c r="L4" t="n">
-        <v>1766</v>
+        <v>1842</v>
       </c>
       <c r="M4" t="n">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="N4" t="n">
-        <v>837</v>
+        <v>882</v>
       </c>
       <c r="O4" t="n">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="P4" t="n">
-        <v>611</v>
+        <v>637</v>
       </c>
       <c r="Q4" t="n">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="R4" t="n">
-        <v>580</v>
+        <v>598</v>
       </c>
       <c r="S4" t="n">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="T4" t="n">
-        <v>588</v>
+        <v>615</v>
       </c>
       <c r="U4" t="n">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="V4" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="W4" t="n">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="X4" t="n">
-        <v>573</v>
+        <v>599</v>
       </c>
       <c r="Y4" t="n">
-        <v>529</v>
+        <v>548</v>
       </c>
       <c r="Z4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AA4" t="n">
-        <v>1752</v>
+        <v>1831</v>
       </c>
       <c r="AB4" t="n">
-        <v>2065.2</v>
+        <v>2158.12</v>
       </c>
       <c r="AC4" t="n">
-        <v>1830.2</v>
+        <v>1910.12</v>
       </c>
       <c r="AD4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE4" t="n">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="AF4" t="n">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="AG4" t="n">
-        <v>404</v>
+        <v>449</v>
       </c>
       <c r="AH4" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI4" t="n">
-        <v>288</v>
+        <v>314</v>
       </c>
       <c r="AJ4" t="n">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="AK4" t="n">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="AL4" t="n">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="AM4" t="n">
-        <v>275</v>
+        <v>302</v>
       </c>
       <c r="AN4" t="n">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="AO4" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="AP4" t="n">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="AQ4" t="n">
-        <v>276</v>
+        <v>302</v>
       </c>
       <c r="AR4" t="n">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="AS4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT4" t="n">
-        <v>973.6</v>
+        <v>1066.52</v>
       </c>
       <c r="AU4" t="n">
-        <v>876.6</v>
+        <v>956.52</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.8112845099956398</v>
+        <v>0.8118364573080278</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.8427723790680651</v>
+        <v>0.8462794000477575</v>
       </c>
       <c r="AX4" t="n">
-        <v>90.0643309952619</v>
+        <v>90.48356133691466</v>
       </c>
       <c r="AY4" t="n">
-        <v>94.94027726900917</v>
+        <v>95.2290525356218</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-4.875946273747268</v>
+        <v>-4.745491198707133</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.2579706936183871</v>
+        <v>0.2628959000444971</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.7094003932538758</v>
+        <v>0.7127836938160529</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.4840333923164064</v>
+        <v>0.4869873195800825</v>
       </c>
       <c r="BD4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BE4" t="n">
         <v>2400</v>
@@ -1608,88 +1608,88 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8013209404971456</v>
+        <v>0.8049529270331121</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8463740428219602</v>
+        <v>0.8451363834707574</v>
       </c>
       <c r="E5" t="n">
-        <v>89.34702561525641</v>
+        <v>89.74087582626095</v>
       </c>
       <c r="F5" t="n">
-        <v>96.99888919837541</v>
+        <v>96.91611554171105</v>
       </c>
       <c r="G5" t="n">
-        <v>-7.65186358311898</v>
+        <v>-7.175239715450084</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2478142502256003</v>
+        <v>0.2479092828244873</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6938323219520928</v>
+        <v>0.6933581700962754</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4727511565272252</v>
+        <v>0.4730889097442798</v>
       </c>
       <c r="K5" t="n">
-        <v>4400</v>
+        <v>4600</v>
       </c>
       <c r="L5" t="n">
-        <v>1539</v>
+        <v>1618</v>
       </c>
       <c r="M5" t="n">
-        <v>413</v>
+        <v>438</v>
       </c>
       <c r="N5" t="n">
-        <v>864</v>
+        <v>905</v>
       </c>
       <c r="O5" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="P5" t="n">
-        <v>545</v>
+        <v>567</v>
       </c>
       <c r="Q5" t="n">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="R5" t="n">
-        <v>461</v>
+        <v>498</v>
       </c>
       <c r="S5" t="n">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="T5" t="n">
-        <v>568</v>
+        <v>596</v>
       </c>
       <c r="U5" t="n">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="V5" t="n">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="W5" t="n">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="X5" t="n">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="Y5" t="n">
-        <v>420</v>
+        <v>444</v>
       </c>
       <c r="Z5" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="AA5" t="n">
-        <v>1662</v>
+        <v>1738</v>
       </c>
       <c r="AB5" t="n">
-        <v>1928.84</v>
+        <v>2018.12</v>
       </c>
       <c r="AC5" t="n">
-        <v>1729.84</v>
+        <v>1810.12</v>
       </c>
       <c r="AD5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE5" t="n">
         <v>2400</v>
@@ -1770,82 +1770,82 @@
         <v>12</v>
       </c>
       <c r="BE5" t="n">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="BF5" t="n">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="BG5" t="n">
-        <v>399</v>
+        <v>440</v>
       </c>
       <c r="BH5" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="BI5" t="n">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="BJ5" t="n">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="BK5" t="n">
-        <v>200</v>
+        <v>237</v>
       </c>
       <c r="BL5" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="BM5" t="n">
-        <v>250</v>
+        <v>278</v>
       </c>
       <c r="BN5" t="n">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="BO5" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="BP5" t="n">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="BQ5" t="n">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="BR5" t="n">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="BS5" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="BT5" t="n">
-        <v>870</v>
+        <v>959.28</v>
       </c>
       <c r="BU5" t="n">
-        <v>776</v>
+        <v>856.28</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.8497493654267423</v>
+        <v>0.8529409350083451</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.8659530476704186</v>
+        <v>0.8615853049498621</v>
       </c>
       <c r="BX5" t="n">
-        <v>95.18769127030717</v>
+        <v>95.4802266519484</v>
       </c>
       <c r="BY5" t="n">
-        <v>99.52050065476222</v>
+        <v>99.11819105842883</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-4.332809384455037</v>
+        <v>-3.637964406480429</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.2753194409663689</v>
+        <v>0.2730176736057899</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.6797123057390178</v>
+        <v>0.68000453515077</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.4824204316939832</v>
+        <v>0.4822476179508466</v>
       </c>
       <c r="CD5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -1860,166 +1860,166 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8789396993117592</v>
+        <v>0.883412123218366</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8523930884133065</v>
+        <v>0.859311672565325</v>
       </c>
       <c r="E6" t="n">
-        <v>101.0512653000211</v>
+        <v>101.4996842612481</v>
       </c>
       <c r="F6" t="n">
-        <v>96.93093791543052</v>
+        <v>97.88500117332694</v>
       </c>
       <c r="G6" t="n">
-        <v>4.12032738459059</v>
+        <v>3.614683087921216</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3117755413645598</v>
+        <v>0.3102432271410364</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6911677743245737</v>
+        <v>0.6894524503943832</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4973924544778555</v>
+        <v>0.4959386022079449</v>
       </c>
       <c r="K6" t="n">
-        <v>4625</v>
+        <v>4825</v>
       </c>
       <c r="L6" t="n">
-        <v>1796</v>
+        <v>1888</v>
       </c>
       <c r="M6" t="n">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="N6" t="n">
-        <v>838</v>
+        <v>868</v>
       </c>
       <c r="O6" t="n">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="P6" t="n">
-        <v>640</v>
+        <v>672</v>
       </c>
       <c r="Q6" t="n">
-        <v>415</v>
+        <v>444</v>
       </c>
       <c r="R6" t="n">
-        <v>576</v>
+        <v>613</v>
       </c>
       <c r="S6" t="n">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="T6" t="n">
-        <v>562</v>
+        <v>588</v>
       </c>
       <c r="U6" t="n">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="V6" t="n">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="W6" t="n">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="X6" t="n">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="Y6" t="n">
-        <v>513</v>
+        <v>541</v>
       </c>
       <c r="Z6" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AA6" t="n">
-        <v>1762</v>
+        <v>1857</v>
       </c>
       <c r="AB6" t="n">
-        <v>2048.44</v>
+        <v>2141.72</v>
       </c>
       <c r="AC6" t="n">
-        <v>1779.44</v>
+        <v>1861.72</v>
       </c>
       <c r="AD6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE6" t="n">
-        <v>2225</v>
+        <v>2425</v>
       </c>
       <c r="AF6" t="n">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="AG6" t="n">
-        <v>402</v>
+        <v>432</v>
       </c>
       <c r="AH6" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="AI6" t="n">
-        <v>306</v>
+        <v>338</v>
       </c>
       <c r="AJ6" t="n">
-        <v>212</v>
+        <v>241</v>
       </c>
       <c r="AK6" t="n">
-        <v>286</v>
+        <v>323</v>
       </c>
       <c r="AL6" t="n">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="AM6" t="n">
-        <v>247</v>
+        <v>273</v>
       </c>
       <c r="AN6" t="n">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="AO6" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="AP6" t="n">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="AQ6" t="n">
-        <v>240</v>
+        <v>266</v>
       </c>
       <c r="AR6" t="n">
-        <v>251</v>
+        <v>279</v>
       </c>
       <c r="AS6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AT6" t="n">
-        <v>994.84</v>
+        <v>1088.12</v>
       </c>
       <c r="AU6" t="n">
-        <v>870.84</v>
+        <v>953.12</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.86869424566162</v>
+        <v>0.8784928812790121</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.9001813857681568</v>
+        <v>0.9100361959592895</v>
       </c>
       <c r="AX6" t="n">
-        <v>99.21282133313046</v>
+        <v>100.2628629194921</v>
       </c>
       <c r="AY6" t="n">
-        <v>103.2737218897539</v>
+        <v>104.6532830743532</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-4.060900556623451</v>
+        <v>-4.390420154861029</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.3023873469761691</v>
+        <v>0.3001050680614884</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.6554273861291534</v>
+        <v>0.654975103951724</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.4714508141145842</v>
+        <v>0.4707049129383689</v>
       </c>
       <c r="BD6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BE6" t="n">
         <v>2400</v>
@@ -2616,88 +2616,88 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.8743831858975031</v>
+        <v>0.88038551598768</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8871317244136425</v>
+        <v>0.8912628139410043</v>
       </c>
       <c r="E9" t="n">
-        <v>98.91306997899575</v>
+        <v>99.78454440091029</v>
       </c>
       <c r="F9" t="n">
-        <v>101.8519472883067</v>
+        <v>102.2670045000218</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.938877309310904</v>
+        <v>-2.482460099111517</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2950500651704123</v>
+        <v>0.2973396457883118</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6671307425308836</v>
+        <v>0.6695419615920967</v>
       </c>
       <c r="J9" t="n">
-        <v>0.477416168048935</v>
+        <v>0.479919661046896</v>
       </c>
       <c r="K9" t="n">
-        <v>4675</v>
+        <v>4875</v>
       </c>
       <c r="L9" t="n">
-        <v>1845</v>
+        <v>1940</v>
       </c>
       <c r="M9" t="n">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="N9" t="n">
-        <v>917</v>
+        <v>945</v>
       </c>
       <c r="O9" t="n">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="P9" t="n">
-        <v>620</v>
+        <v>655</v>
       </c>
       <c r="Q9" t="n">
-        <v>391</v>
+        <v>416</v>
       </c>
       <c r="R9" t="n">
-        <v>550</v>
+        <v>587</v>
       </c>
       <c r="S9" t="n">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="T9" t="n">
-        <v>555</v>
+        <v>584</v>
       </c>
       <c r="U9" t="n">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="V9" t="n">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="W9" t="n">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="X9" t="n">
-        <v>588</v>
+        <v>616</v>
       </c>
       <c r="Y9" t="n">
-        <v>501</v>
+        <v>526</v>
       </c>
       <c r="Z9" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AA9" t="n">
-        <v>1891</v>
+        <v>1983</v>
       </c>
       <c r="AB9" t="n">
-        <v>2128</v>
+        <v>2221.28</v>
       </c>
       <c r="AC9" t="n">
-        <v>1872</v>
+        <v>1951.28</v>
       </c>
       <c r="AD9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE9" t="n">
         <v>2450</v>
@@ -2778,82 +2778,82 @@
         <v>12</v>
       </c>
       <c r="BE9" t="n">
-        <v>2225</v>
+        <v>2425</v>
       </c>
       <c r="BF9" t="n">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="BG9" t="n">
-        <v>419</v>
+        <v>447</v>
       </c>
       <c r="BH9" t="n">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="BI9" t="n">
+        <v>344</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>210</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>298</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>134</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>317</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>138</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>107</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>190</v>
+      </c>
+      <c r="BQ9" t="n">
         <v>309</v>
       </c>
-      <c r="BJ9" t="n">
-        <v>185</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>261</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>120</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>288</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>125</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>98</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>176</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>281</v>
-      </c>
       <c r="BR9" t="n">
-        <v>247</v>
+        <v>272</v>
       </c>
       <c r="BS9" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BT9" t="n">
-        <v>1018.84</v>
+        <v>1112.12</v>
       </c>
       <c r="BU9" t="n">
-        <v>898.8399999999999</v>
+        <v>978.12</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.8847417279158093</v>
+        <v>0.8958831762613042</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.8726908458129556</v>
+        <v>0.8821564314177365</v>
       </c>
       <c r="BX9" t="n">
-        <v>100.0965245505916</v>
+        <v>101.740852180121</v>
       </c>
       <c r="BY9" t="n">
-        <v>100.8269359778485</v>
+        <v>101.7424680104837</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0.7304114272569897</v>
+        <v>-0.001615830362708219</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.3019295435579464</v>
+        <v>0.3059354149281175</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.6788325578583657</v>
+        <v>0.682679844703502</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.496100939586104</v>
+        <v>0.4995508612872619</v>
       </c>
       <c r="CD9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">

--- a/data/3FEB_25_26/teams_25_26_3FEB.xlsx
+++ b/data/3FEB_25_26/teams_25_26_3FEB.xlsx
@@ -852,88 +852,88 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7928294889524842</v>
+        <v>0.7976626775990445</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8986599544797419</v>
+        <v>0.895271695835436</v>
       </c>
       <c r="E2" t="n">
-        <v>87.60007049650642</v>
+        <v>88.11818934582665</v>
       </c>
       <c r="F2" t="n">
-        <v>103.77011001493</v>
+        <v>103.1193056143328</v>
       </c>
       <c r="G2" t="n">
-        <v>-16.1700395184236</v>
+        <v>-15.00111626850616</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2296314275164409</v>
+        <v>0.2282510484645638</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6406535135261598</v>
+        <v>0.6464559444136849</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4298006004259114</v>
+        <v>0.429999880756701</v>
       </c>
       <c r="K2" t="n">
-        <v>4975</v>
+        <v>5175</v>
       </c>
       <c r="L2" t="n">
-        <v>1773</v>
+        <v>1853</v>
       </c>
       <c r="M2" t="n">
-        <v>468</v>
+        <v>488</v>
       </c>
       <c r="N2" t="n">
-        <v>1011</v>
+        <v>1046</v>
       </c>
       <c r="O2" t="n">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="P2" t="n">
-        <v>579</v>
+        <v>613</v>
       </c>
       <c r="Q2" t="n">
-        <v>369</v>
+        <v>385</v>
       </c>
       <c r="R2" t="n">
-        <v>567</v>
+        <v>591</v>
       </c>
       <c r="S2" t="n">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="T2" t="n">
-        <v>565</v>
+        <v>587</v>
       </c>
       <c r="U2" t="n">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="V2" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="W2" t="n">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="X2" t="n">
-        <v>571</v>
+        <v>597</v>
       </c>
       <c r="Y2" t="n">
-        <v>501</v>
+        <v>526</v>
       </c>
       <c r="Z2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="AA2" t="n">
-        <v>2115</v>
+        <v>2185</v>
       </c>
       <c r="AB2" t="n">
-        <v>2243.48</v>
+        <v>2331.04</v>
       </c>
       <c r="AC2" t="n">
-        <v>2022.48</v>
+        <v>2102.04</v>
       </c>
       <c r="AD2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE2" t="n">
         <v>2475</v>
@@ -1014,82 +1014,82 @@
         <v>12</v>
       </c>
       <c r="BE2" t="n">
-        <v>2500</v>
+        <v>2700</v>
       </c>
       <c r="BF2" t="n">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="BG2" t="n">
-        <v>489</v>
+        <v>524</v>
       </c>
       <c r="BH2" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="BI2" t="n">
-        <v>302</v>
+        <v>336</v>
       </c>
       <c r="BJ2" t="n">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="BK2" t="n">
-        <v>267</v>
+        <v>291</v>
       </c>
       <c r="BL2" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="BM2" t="n">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="BN2" t="n">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="BO2" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="BP2" t="n">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="BQ2" t="n">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="BR2" t="n">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="BS2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BT2" t="n">
-        <v>1133.48</v>
+        <v>1221.04</v>
       </c>
       <c r="BU2" t="n">
-        <v>1016.48</v>
+        <v>1096.04</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.7590553891169501</v>
+        <v>0.7709479903476841</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.8568833269903194</v>
+        <v>0.8535810317119943</v>
       </c>
       <c r="BX2" t="n">
-        <v>84.28774112961786</v>
+        <v>85.53891809884051</v>
       </c>
       <c r="BY2" t="n">
-        <v>98.5874408903622</v>
+        <v>97.7345608218728</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-14.29969976074433</v>
+        <v>-12.19564272303228</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.2455749842138355</v>
+        <v>0.2416939816758107</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.6486439510337686</v>
+        <v>0.65918782293227</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.4414423586844773</v>
+        <v>0.4409300702237984</v>
       </c>
       <c r="CD2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -1104,166 +1104,166 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7761132237011646</v>
+        <v>0.7701922532374672</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8752694388958985</v>
+        <v>0.8813979018463917</v>
       </c>
       <c r="E3" t="n">
-        <v>88.2741821754877</v>
+        <v>87.64383305299506</v>
       </c>
       <c r="F3" t="n">
-        <v>100.1415291687097</v>
+        <v>100.6032219538514</v>
       </c>
       <c r="G3" t="n">
-        <v>-11.86734699322201</v>
+        <v>-12.9593889008563</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2860106476679811</v>
+        <v>0.2869511741422142</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6890651353382878</v>
+        <v>0.6911321595543859</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4863054415990148</v>
+        <v>0.4859836587176629</v>
       </c>
       <c r="K3" t="n">
-        <v>4900</v>
+        <v>5100</v>
       </c>
       <c r="L3" t="n">
-        <v>1756</v>
+        <v>1817</v>
       </c>
       <c r="M3" t="n">
-        <v>473</v>
+        <v>486</v>
       </c>
       <c r="N3" t="n">
-        <v>1030</v>
+        <v>1069</v>
       </c>
       <c r="O3" t="n">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="P3" t="n">
-        <v>555</v>
+        <v>580</v>
       </c>
       <c r="Q3" t="n">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="R3" t="n">
-        <v>620</v>
+        <v>643</v>
       </c>
       <c r="S3" t="n">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="T3" t="n">
-        <v>650</v>
+        <v>670</v>
       </c>
       <c r="U3" t="n">
+        <v>297</v>
+      </c>
+      <c r="V3" t="n">
+        <v>183</v>
+      </c>
+      <c r="W3" t="n">
+        <v>423</v>
+      </c>
+      <c r="X3" t="n">
+        <v>574</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>563</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2096</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2354.92</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2068.92</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2625</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>238</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>559</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>71</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>303</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>205</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>314</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>154</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>318</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>129</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>94</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>218</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>287</v>
       </c>
-      <c r="V3" t="n">
-        <v>177</v>
-      </c>
-      <c r="W3" t="n">
-        <v>400</v>
-      </c>
-      <c r="X3" t="n">
-        <v>556</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>545</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>41</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2005</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2257.8</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1984.8</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2425</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>225</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>520</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>64</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>278</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>191</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>291</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>141</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>298</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>119</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>88</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>195</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>269</v>
-      </c>
       <c r="AR3" t="n">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="AS3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT3" t="n">
-        <v>1121.04</v>
+        <v>1218.16</v>
       </c>
       <c r="AU3" t="n">
-        <v>980.04</v>
+        <v>1064.16</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.7447167418509636</v>
+        <v>0.7357453741784841</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.9173596606819795</v>
+        <v>0.9259074569878447</v>
       </c>
       <c r="AX3" t="n">
-        <v>85.18072152433017</v>
+        <v>84.20647018501028</v>
       </c>
       <c r="AY3" t="n">
-        <v>105.3200257751431</v>
+        <v>105.8095506229975</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-20.1393042508129</v>
+        <v>-21.60308043798723</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.2893831029863625</v>
+        <v>0.2909323881046276</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.664883229227427</v>
+        <v>0.6707184224207589</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.4699609216836479</v>
+        <v>0.4705993792129994</v>
       </c>
       <c r="BD3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BE3" t="n">
         <v>2475</v>
@@ -1356,166 +1356,166 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8552340941452962</v>
+        <v>0.8502881239512082</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8565393372336615</v>
+        <v>0.8696507320652987</v>
       </c>
       <c r="E4" t="n">
-        <v>96.45266167279361</v>
+        <v>96.32348362661851</v>
       </c>
       <c r="F4" t="n">
-        <v>96.18436661761011</v>
+        <v>97.73865083464179</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2682950551834975</v>
+        <v>-1.415167208023286</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2861350388654794</v>
+        <v>0.2922907989491457</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7238938050439468</v>
+        <v>0.7222680149261455</v>
       </c>
       <c r="J4" t="n">
-        <v>0.50535037336184</v>
+        <v>0.5064610579429996</v>
       </c>
       <c r="K4" t="n">
-        <v>4600</v>
+        <v>5000</v>
       </c>
       <c r="L4" t="n">
-        <v>1766</v>
+        <v>1916</v>
       </c>
       <c r="M4" t="n">
-        <v>396</v>
+        <v>434</v>
       </c>
       <c r="N4" t="n">
-        <v>837</v>
+        <v>922</v>
       </c>
       <c r="O4" t="n">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="P4" t="n">
-        <v>611</v>
+        <v>666</v>
       </c>
       <c r="Q4" t="n">
-        <v>398</v>
+        <v>421</v>
       </c>
       <c r="R4" t="n">
-        <v>580</v>
+        <v>619</v>
       </c>
       <c r="S4" t="n">
-        <v>235</v>
+        <v>266</v>
       </c>
       <c r="T4" t="n">
-        <v>588</v>
+        <v>638</v>
       </c>
       <c r="U4" t="n">
-        <v>320</v>
+        <v>353</v>
       </c>
       <c r="V4" t="n">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="W4" t="n">
-        <v>362</v>
+        <v>394</v>
       </c>
       <c r="X4" t="n">
-        <v>573</v>
+        <v>618</v>
       </c>
       <c r="Y4" t="n">
-        <v>529</v>
+        <v>567</v>
       </c>
       <c r="Z4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA4" t="n">
-        <v>1752</v>
+        <v>1938</v>
       </c>
       <c r="AB4" t="n">
-        <v>2065.2</v>
+        <v>2254.36</v>
       </c>
       <c r="AC4" t="n">
-        <v>1830.2</v>
+        <v>1988.36</v>
       </c>
       <c r="AD4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE4" t="n">
-        <v>2200</v>
+        <v>2600</v>
       </c>
       <c r="AF4" t="n">
-        <v>194</v>
+        <v>232</v>
       </c>
       <c r="AG4" t="n">
-        <v>404</v>
+        <v>489</v>
       </c>
       <c r="AH4" t="n">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AI4" t="n">
+        <v>343</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>193</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>304</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>128</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>325</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>173</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>102</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>197</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>321</v>
+      </c>
+      <c r="AR4" t="n">
         <v>288</v>
       </c>
-      <c r="AJ4" t="n">
-        <v>170</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>265</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>97</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>275</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>140</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>165</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>276</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>250</v>
-      </c>
       <c r="AS4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AT4" t="n">
-        <v>973.6</v>
+        <v>1162.76</v>
       </c>
       <c r="AU4" t="n">
-        <v>876.6</v>
+        <v>1034.76</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.8112845099956398</v>
+        <v>0.8085345033377256</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.8427723790680651</v>
+        <v>0.8701045934620747</v>
       </c>
       <c r="AX4" t="n">
-        <v>90.0643309952619</v>
+        <v>90.79873177993005</v>
       </c>
       <c r="AY4" t="n">
-        <v>94.94027726900917</v>
+        <v>98.1206837400087</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-4.875946273747268</v>
+        <v>-7.321951960078656</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.2579706936183871</v>
+        <v>0.2741416699711442</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.7094003932538758</v>
+        <v>0.7085036294565762</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.4840333923164064</v>
+        <v>0.4894488597487033</v>
       </c>
       <c r="BD4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BE4" t="n">
         <v>2400</v>
@@ -1608,244 +1608,244 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8013209404971456</v>
+        <v>0.8069335209957328</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8463740428219602</v>
+        <v>0.8537016710933328</v>
       </c>
       <c r="E5" t="n">
-        <v>89.34702561525641</v>
+        <v>90.04890825400949</v>
       </c>
       <c r="F5" t="n">
-        <v>96.99888919837541</v>
+        <v>97.72009231311003</v>
       </c>
       <c r="G5" t="n">
-        <v>-7.65186358311898</v>
+        <v>-7.671184059100511</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2478142502256003</v>
+        <v>0.2493635414855296</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6938323219520928</v>
+        <v>0.6960713346703916</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4727511565272252</v>
+        <v>0.4740848304744376</v>
       </c>
       <c r="K5" t="n">
-        <v>4400</v>
+        <v>5000</v>
       </c>
       <c r="L5" t="n">
-        <v>1539</v>
+        <v>1771</v>
       </c>
       <c r="M5" t="n">
-        <v>413</v>
+        <v>479</v>
       </c>
       <c r="N5" t="n">
-        <v>864</v>
+        <v>989</v>
       </c>
       <c r="O5" t="n">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="P5" t="n">
-        <v>545</v>
+        <v>619</v>
       </c>
       <c r="Q5" t="n">
+        <v>333</v>
+      </c>
+      <c r="R5" t="n">
+        <v>543</v>
+      </c>
+      <c r="S5" t="n">
+        <v>229</v>
+      </c>
+      <c r="T5" t="n">
+        <v>648</v>
+      </c>
+      <c r="U5" t="n">
+        <v>336</v>
+      </c>
+      <c r="V5" t="n">
+        <v>207</v>
+      </c>
+      <c r="W5" t="n">
+        <v>356</v>
+      </c>
+      <c r="X5" t="n">
+        <v>553</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>485</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1904</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2202.92</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1973.92</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2600</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>241</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>509</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>76</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>330</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>168</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>287</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>116</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>344</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>162</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>117</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>189</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>281</v>
       </c>
-      <c r="R5" t="n">
-        <v>461</v>
-      </c>
-      <c r="S5" t="n">
-        <v>199</v>
-      </c>
-      <c r="T5" t="n">
-        <v>568</v>
-      </c>
-      <c r="U5" t="n">
-        <v>293</v>
-      </c>
-      <c r="V5" t="n">
-        <v>186</v>
-      </c>
-      <c r="W5" t="n">
-        <v>317</v>
-      </c>
-      <c r="X5" t="n">
-        <v>487</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>420</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1662</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1928.84</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1729.84</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE5" t="n">
+      <c r="AR5" t="n">
+        <v>254</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1154.28</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1038.28</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.7620710216485297</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.8321324520577057</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>84.72260324700484</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>95.22677752495207</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-10.50417427794725</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0.2277402967080216</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0.702604207094041</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.4640854807781472</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BE5" t="n">
         <v>2400</v>
       </c>
-      <c r="AF5" t="n">
-        <v>218</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>465</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>72</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>306</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>152</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>261</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>105</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>318</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>150</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>108</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>173</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>261</v>
-      </c>
-      <c r="AR5" t="n">
+      <c r="BF5" t="n">
+        <v>238</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>480</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>84</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>289</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>165</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>256</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>113</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>304</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>174</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>90</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>167</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>272</v>
+      </c>
+      <c r="BR5" t="n">
         <v>231</v>
       </c>
-      <c r="AS5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1058.84</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>953.84</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.7609639197224817</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.8300582054482447</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>84.47980423604744</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>94.89754631805302</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-10.4177420820056</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0.2248932579416265</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0.7055990021296555</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0.4646934272215936</v>
-      </c>
-      <c r="BD5" t="n">
+      <c r="BS5" t="n">
+        <v>37</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>1048.64</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>935.64</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0.8555345619552027</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0.8770683250485956</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>95.81907201159787</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>100.4211833336144</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>-4.602111322016543</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0.2727887233278299</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>0.6889940562114382</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0.4849174593120856</v>
+      </c>
+      <c r="CD5" t="n">
         <v>12</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>2000</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>195</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>399</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>72</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>239</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>129</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>200</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>94</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>250</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>143</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>78</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>144</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>226</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>189</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>34</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>870</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>776</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>0.8497493654267423</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>0.8659530476704186</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>95.18769127030717</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>99.52050065476222</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>-4.332809384455037</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>0.2753194409663689</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>0.6797123057390178</v>
-      </c>
-      <c r="CC5" t="n">
-        <v>0.4824204316939832</v>
-      </c>
-      <c r="CD5" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -1860,166 +1860,166 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8789396993117592</v>
+        <v>0.8806337778245151</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8523930884133065</v>
+        <v>0.8614855738673717</v>
       </c>
       <c r="E6" t="n">
-        <v>101.0512653000211</v>
+        <v>100.9396968907982</v>
       </c>
       <c r="F6" t="n">
-        <v>96.93093791543052</v>
+        <v>97.99172279557435</v>
       </c>
       <c r="G6" t="n">
-        <v>4.12032738459059</v>
+        <v>2.947974095223874</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3117755413645598</v>
+        <v>0.3064049266268236</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6911677743245737</v>
+        <v>0.6940694743298274</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4973924544778555</v>
+        <v>0.498709753771801</v>
       </c>
       <c r="K6" t="n">
-        <v>4625</v>
+        <v>5025</v>
       </c>
       <c r="L6" t="n">
-        <v>1796</v>
+        <v>1958</v>
       </c>
       <c r="M6" t="n">
-        <v>398</v>
+        <v>433</v>
       </c>
       <c r="N6" t="n">
-        <v>838</v>
+        <v>900</v>
       </c>
       <c r="O6" t="n">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="P6" t="n">
-        <v>640</v>
+        <v>693</v>
       </c>
       <c r="Q6" t="n">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="R6" t="n">
-        <v>576</v>
+        <v>638</v>
       </c>
       <c r="S6" t="n">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="T6" t="n">
-        <v>562</v>
+        <v>621</v>
       </c>
       <c r="U6" t="n">
+        <v>330</v>
+      </c>
+      <c r="V6" t="n">
+        <v>213</v>
+      </c>
+      <c r="W6" t="n">
+        <v>354</v>
+      </c>
+      <c r="X6" t="n">
+        <v>528</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>565</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>83</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1937</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2227.72</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1941.72</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2625</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>228</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>464</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>104</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>359</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>256</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>348</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>141</v>
+      </c>
+      <c r="AM6" t="n">
         <v>306</v>
       </c>
-      <c r="V6" t="n">
-        <v>205</v>
-      </c>
-      <c r="W6" t="n">
-        <v>317</v>
-      </c>
-      <c r="X6" t="n">
-        <v>475</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>513</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>77</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1762</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2048.44</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1779.44</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2225</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>193</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>402</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>88</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>306</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>212</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>286</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>124</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>247</v>
-      </c>
       <c r="AN6" t="n">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="AO6" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="AP6" t="n">
-        <v>161</v>
+        <v>198</v>
       </c>
       <c r="AQ6" t="n">
-        <v>240</v>
+        <v>293</v>
       </c>
       <c r="AR6" t="n">
-        <v>251</v>
+        <v>303</v>
       </c>
       <c r="AS6" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AT6" t="n">
-        <v>994.84</v>
+        <v>1174.12</v>
       </c>
       <c r="AU6" t="n">
-        <v>870.84</v>
+        <v>1033.12</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.86869424566162</v>
+        <v>0.8735283125938645</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.9001813857681568</v>
+        <v>0.910314888971382</v>
       </c>
       <c r="AX6" t="n">
-        <v>99.21282133313046</v>
+        <v>99.28110423337732</v>
       </c>
       <c r="AY6" t="n">
-        <v>103.2737218897539</v>
+        <v>104.3378798939808</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-4.060900556623451</v>
+        <v>-5.056775660603435</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.3023873469761691</v>
+        <v>0.2935035793095058</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.6554273861291534</v>
+        <v>0.6665060997077827</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.4714508141145842</v>
+        <v>0.4779751035819058</v>
       </c>
       <c r="BD6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BE6" t="n">
         <v>2400</v>
@@ -2112,166 +2112,166 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.8828071603471722</v>
+        <v>0.8813613606340612</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7480008392960273</v>
+        <v>0.7495306764944965</v>
       </c>
       <c r="E7" t="n">
-        <v>103.1750037849061</v>
+        <v>102.7521256128761</v>
       </c>
       <c r="F7" t="n">
-        <v>85.65952282289264</v>
+        <v>85.9026509234902</v>
       </c>
       <c r="G7" t="n">
-        <v>17.51548096201343</v>
+        <v>16.84947468938592</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3591586515658247</v>
+        <v>0.3517108079254072</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6909909001528111</v>
+        <v>0.6918099082388661</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5231941132847586</v>
+        <v>0.5209576318410256</v>
       </c>
       <c r="K7" t="n">
-        <v>4650</v>
+        <v>5075</v>
       </c>
       <c r="L7" t="n">
-        <v>1850</v>
+        <v>2003</v>
       </c>
       <c r="M7" t="n">
-        <v>454</v>
+        <v>490</v>
       </c>
       <c r="N7" t="n">
-        <v>914</v>
+        <v>994</v>
       </c>
       <c r="O7" t="n">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="P7" t="n">
-        <v>632</v>
+        <v>688</v>
       </c>
       <c r="Q7" t="n">
-        <v>375</v>
+        <v>402</v>
       </c>
       <c r="R7" t="n">
-        <v>589</v>
+        <v>633</v>
       </c>
       <c r="S7" t="n">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="T7" t="n">
-        <v>572</v>
+        <v>636</v>
       </c>
       <c r="U7" t="n">
-        <v>342</v>
+        <v>371</v>
       </c>
       <c r="V7" t="n">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="W7" t="n">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="X7" t="n">
-        <v>538</v>
+        <v>582</v>
       </c>
       <c r="Y7" t="n">
-        <v>509</v>
+        <v>554</v>
       </c>
       <c r="Z7" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="AA7" t="n">
-        <v>1524</v>
+        <v>1674</v>
       </c>
       <c r="AB7" t="n">
-        <v>2101.16</v>
+        <v>2282.52</v>
       </c>
       <c r="AC7" t="n">
-        <v>1794.16</v>
+        <v>1952.52</v>
       </c>
       <c r="AD7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE7" t="n">
-        <v>2225</v>
+        <v>2650</v>
       </c>
       <c r="AF7" t="n">
-        <v>203</v>
+        <v>239</v>
       </c>
       <c r="AG7" t="n">
-        <v>423</v>
+        <v>503</v>
       </c>
       <c r="AH7" t="n">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="AI7" t="n">
-        <v>311</v>
+        <v>367</v>
       </c>
       <c r="AJ7" t="n">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="AK7" t="n">
-        <v>307</v>
+        <v>351</v>
       </c>
       <c r="AL7" t="n">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="AM7" t="n">
-        <v>266</v>
+        <v>330</v>
       </c>
       <c r="AN7" t="n">
-        <v>162</v>
+        <v>191</v>
       </c>
       <c r="AO7" t="n">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="AP7" t="n">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="AQ7" t="n">
-        <v>266</v>
+        <v>310</v>
       </c>
       <c r="AR7" t="n">
-        <v>257</v>
+        <v>302</v>
       </c>
       <c r="AS7" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="AT7" t="n">
-        <v>1004.08</v>
+        <v>1185.44</v>
       </c>
       <c r="AU7" t="n">
-        <v>855.08</v>
+        <v>1013.44</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.9090901349216334</v>
+        <v>0.9022662163080415</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.7725100510678167</v>
+        <v>0.7716813977153668</v>
       </c>
       <c r="AX7" t="n">
-        <v>106.5743399536909</v>
+        <v>105.2381379045895</v>
       </c>
       <c r="AY7" t="n">
-        <v>90.05926312319251</v>
+        <v>89.84993403968014</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16.51507683049837</v>
+        <v>15.38820386490931</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.3660971155739813</v>
+        <v>0.3507068833411544</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.6584750752269134</v>
+        <v>0.6650525253810038</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.5141991181747219</v>
+        <v>0.5112820377229331</v>
       </c>
       <c r="BD7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BE7" t="n">
         <v>2425</v>
@@ -2364,244 +2364,244 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9498924400998298</v>
+        <v>0.9567161923814189</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8675705963652832</v>
+        <v>0.8709161415399924</v>
       </c>
       <c r="E8" t="n">
-        <v>108.6539176433104</v>
+        <v>109.5265406225832</v>
       </c>
       <c r="F8" t="n">
-        <v>97.83594119831035</v>
+        <v>98.45023002850263</v>
       </c>
       <c r="G8" t="n">
-        <v>10.81797644500007</v>
+        <v>11.07631059408054</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3331446662062285</v>
+        <v>0.3346518230684604</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7044592023015666</v>
+        <v>0.7001259265279984</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5193890115807258</v>
+        <v>0.5179739193714414</v>
       </c>
       <c r="K8" t="n">
-        <v>4600</v>
+        <v>5000</v>
       </c>
       <c r="L8" t="n">
-        <v>2043</v>
+        <v>2235</v>
       </c>
       <c r="M8" t="n">
-        <v>505</v>
+        <v>553</v>
       </c>
       <c r="N8" t="n">
-        <v>914</v>
+        <v>990</v>
       </c>
       <c r="O8" t="n">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="P8" t="n">
-        <v>656</v>
+        <v>718</v>
       </c>
       <c r="Q8" t="n">
-        <v>346</v>
+        <v>376</v>
       </c>
       <c r="R8" t="n">
-        <v>546</v>
+        <v>604</v>
       </c>
       <c r="S8" t="n">
-        <v>268</v>
+        <v>293</v>
       </c>
       <c r="T8" t="n">
-        <v>569</v>
+        <v>617</v>
       </c>
       <c r="U8" t="n">
-        <v>365</v>
+        <v>409</v>
       </c>
       <c r="V8" t="n">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="W8" t="n">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="X8" t="n">
-        <v>516</v>
+        <v>558</v>
       </c>
       <c r="Y8" t="n">
-        <v>496</v>
+        <v>541</v>
       </c>
       <c r="Z8" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AA8" t="n">
-        <v>1803</v>
+        <v>1973</v>
       </c>
       <c r="AB8" t="n">
-        <v>2147.24</v>
+        <v>2332.76</v>
       </c>
       <c r="AC8" t="n">
-        <v>1879.24</v>
+        <v>2039.76</v>
       </c>
       <c r="AD8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE8" t="n">
-        <v>2200</v>
+        <v>2400</v>
       </c>
       <c r="AF8" t="n">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="AG8" t="n">
-        <v>430</v>
+        <v>468</v>
       </c>
       <c r="AH8" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="AI8" t="n">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="AJ8" t="n">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="AK8" t="n">
-        <v>275</v>
+        <v>309</v>
       </c>
       <c r="AL8" t="n">
+        <v>137</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>258</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>188</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>116</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>156</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>270</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>278</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>39</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1101.96</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>964.96</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.9244469352968511</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.9210739405710027</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>105.4877797629138</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>103.5801257865238</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.90765397639003</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0.3133056275959089</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0.6835726747556681</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0.488420376791544</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>2600</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>306</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>522</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>136</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>376</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>195</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>295</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>156</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>359</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>221</v>
+      </c>
+      <c r="BO8" t="n">
         <v>124</v>
       </c>
-      <c r="AM8" t="n">
-        <v>236</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>172</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>111</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>142</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>249</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>252</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1009</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>885</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0.9253628591597004</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0.9093653200407121</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>105.4136550526525</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>102.410289398452</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>3.003365654200495</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0.3089596745490724</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0.6811995161557435</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0.4853324056179123</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>11</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>2400</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>280</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>484</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>122</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>340</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>182</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>271</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>144</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>333</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>193</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>113</v>
-      </c>
       <c r="BP8" t="n">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="BQ8" t="n">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="BR8" t="n">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="BS8" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="BT8" t="n">
-        <v>1138.24</v>
+        <v>1230.8</v>
       </c>
       <c r="BU8" t="n">
-        <v>994.24</v>
+        <v>1074.8</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.9723778892949483</v>
+        <v>0.9865031989210201</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.8292587663294735</v>
+        <v>0.8246166347421369</v>
       </c>
       <c r="BX8" t="n">
-        <v>111.6241583514135</v>
+        <v>113.2546275699703</v>
       </c>
       <c r="BY8" t="n">
-        <v>93.64278868151382</v>
+        <v>93.71494163648312</v>
       </c>
       <c r="BZ8" t="n">
-        <v>17.98136966989969</v>
+        <v>19.53968593348717</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.3553142418919549</v>
+        <v>0.3543560035046616</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.725780581268571</v>
+        <v>0.7154058512409188</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.5506075670466384</v>
+        <v>0.5452541125221161</v>
       </c>
       <c r="CD8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -2616,88 +2616,88 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.8743831858975031</v>
+        <v>0.8794510318030223</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8871317244136425</v>
+        <v>0.8866265511738084</v>
       </c>
       <c r="E9" t="n">
-        <v>98.91306997899575</v>
+        <v>99.76026470518349</v>
       </c>
       <c r="F9" t="n">
-        <v>101.8519472883067</v>
+        <v>101.6817719751607</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.938877309310904</v>
+        <v>-1.921507269977174</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2950500651704123</v>
+        <v>0.2987793932901127</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6671307425308836</v>
+        <v>0.6722840926522222</v>
       </c>
       <c r="J9" t="n">
-        <v>0.477416168048935</v>
+        <v>0.4824512696667486</v>
       </c>
       <c r="K9" t="n">
-        <v>4675</v>
+        <v>5075</v>
       </c>
       <c r="L9" t="n">
-        <v>1845</v>
+        <v>2022</v>
       </c>
       <c r="M9" t="n">
-        <v>445</v>
+        <v>478</v>
       </c>
       <c r="N9" t="n">
-        <v>917</v>
+        <v>989</v>
       </c>
       <c r="O9" t="n">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="P9" t="n">
-        <v>620</v>
+        <v>683</v>
       </c>
       <c r="Q9" t="n">
-        <v>391</v>
+        <v>430</v>
       </c>
       <c r="R9" t="n">
-        <v>550</v>
+        <v>609</v>
       </c>
       <c r="S9" t="n">
-        <v>256</v>
+        <v>283</v>
       </c>
       <c r="T9" t="n">
-        <v>555</v>
+        <v>615</v>
       </c>
       <c r="U9" t="n">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="V9" t="n">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="W9" t="n">
-        <v>349</v>
+        <v>377</v>
       </c>
       <c r="X9" t="n">
-        <v>588</v>
+        <v>640</v>
       </c>
       <c r="Y9" t="n">
-        <v>501</v>
+        <v>546</v>
       </c>
       <c r="Z9" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AA9" t="n">
-        <v>1891</v>
+        <v>2057</v>
       </c>
       <c r="AB9" t="n">
-        <v>2128</v>
+        <v>2316.96</v>
       </c>
       <c r="AC9" t="n">
-        <v>1872</v>
+        <v>2033.96</v>
       </c>
       <c r="AD9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE9" t="n">
         <v>2450</v>
@@ -2778,82 +2778,82 @@
         <v>12</v>
       </c>
       <c r="BE9" t="n">
-        <v>2225</v>
+        <v>2625</v>
       </c>
       <c r="BF9" t="n">
-        <v>209</v>
+        <v>242</v>
       </c>
       <c r="BG9" t="n">
-        <v>419</v>
+        <v>491</v>
       </c>
       <c r="BH9" t="n">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="BI9" t="n">
-        <v>309</v>
+        <v>372</v>
       </c>
       <c r="BJ9" t="n">
-        <v>185</v>
+        <v>224</v>
       </c>
       <c r="BK9" t="n">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="BL9" t="n">
+        <v>147</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>348</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>152</v>
+      </c>
+      <c r="BO9" t="n">
         <v>120</v>
       </c>
-      <c r="BM9" t="n">
-        <v>288</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>125</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>98</v>
-      </c>
       <c r="BP9" t="n">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="BQ9" t="n">
-        <v>281</v>
+        <v>333</v>
       </c>
       <c r="BR9" t="n">
-        <v>247</v>
+        <v>292</v>
       </c>
       <c r="BS9" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="BT9" t="n">
-        <v>1018.84</v>
+        <v>1207.8</v>
       </c>
       <c r="BU9" t="n">
-        <v>898.8399999999999</v>
+        <v>1060.8</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.8847417279158093</v>
+        <v>0.8928939635774529</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.8726908458129556</v>
+        <v>0.8739410324441496</v>
       </c>
       <c r="BX9" t="n">
-        <v>100.0965245505916</v>
+        <v>101.543675243784</v>
       </c>
       <c r="BY9" t="n">
-        <v>100.8269359778485</v>
+        <v>100.6573698080229</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0.7304114272569897</v>
+        <v>0.8863054357611205</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.3019295435579464</v>
+        <v>0.3080429471131341</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.6788325578583657</v>
+        <v>0.6869425672720971</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.496100939586104</v>
+        <v>0.502909247076181</v>
       </c>
       <c r="CD9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -2868,166 +2868,166 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.8244978657817087</v>
+        <v>0.814134359132702</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8627134383910202</v>
+        <v>0.8555538201319564</v>
       </c>
       <c r="E10" t="n">
-        <v>93.14777181756794</v>
+        <v>92.06434799149734</v>
       </c>
       <c r="F10" t="n">
-        <v>96.44763743093011</v>
+        <v>95.8666875362299</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.299865613362164</v>
+        <v>-3.802339544732551</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2873365030019487</v>
+        <v>0.2860391213132434</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7280343538032615</v>
+        <v>0.7222463129844644</v>
       </c>
       <c r="J10" t="n">
-        <v>0.500313570613112</v>
+        <v>0.4959332116966336</v>
       </c>
       <c r="K10" t="n">
-        <v>4875</v>
+        <v>5075</v>
       </c>
       <c r="L10" t="n">
-        <v>1822</v>
+        <v>1873</v>
       </c>
       <c r="M10" t="n">
-        <v>456</v>
+        <v>469</v>
       </c>
       <c r="N10" t="n">
-        <v>961</v>
+        <v>1002</v>
       </c>
       <c r="O10" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="P10" t="n">
-        <v>612</v>
+        <v>638</v>
       </c>
       <c r="Q10" t="n">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="R10" t="n">
-        <v>573</v>
+        <v>603</v>
       </c>
       <c r="S10" t="n">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="T10" t="n">
-        <v>606</v>
+        <v>627</v>
       </c>
       <c r="U10" t="n">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="V10" t="n">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="W10" t="n">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="X10" t="n">
-        <v>532</v>
+        <v>556</v>
       </c>
       <c r="Y10" t="n">
-        <v>524</v>
+        <v>549</v>
       </c>
       <c r="Z10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AA10" t="n">
-        <v>1874</v>
+        <v>1936</v>
       </c>
       <c r="AB10" t="n">
-        <v>2219.12</v>
+        <v>2309.32</v>
       </c>
       <c r="AC10" t="n">
-        <v>1960.12</v>
+        <v>2037.32</v>
       </c>
       <c r="AD10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE10" t="n">
-        <v>2450</v>
+        <v>2650</v>
       </c>
       <c r="AF10" t="n">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="AG10" t="n">
-        <v>486</v>
+        <v>527</v>
       </c>
       <c r="AH10" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="AI10" t="n">
-        <v>299</v>
+        <v>325</v>
       </c>
       <c r="AJ10" t="n">
+        <v>207</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>328</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>155</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>329</v>
+      </c>
+      <c r="AN10" t="n">
         <v>194</v>
       </c>
-      <c r="AK10" t="n">
-        <v>298</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>142</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>308</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>185</v>
-      </c>
       <c r="AO10" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="AP10" t="n">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="AQ10" t="n">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="AR10" t="n">
-        <v>265</v>
+        <v>290</v>
       </c>
       <c r="AS10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT10" t="n">
-        <v>1129.12</v>
+        <v>1219.32</v>
       </c>
       <c r="AU10" t="n">
-        <v>987.12</v>
+        <v>1064.32</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.7874884738876604</v>
+        <v>0.7704055297083436</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.8640924156729811</v>
+        <v>0.8502178438453998</v>
       </c>
       <c r="AX10" t="n">
-        <v>89.845713417261</v>
+        <v>88.01621055176426</v>
       </c>
       <c r="AY10" t="n">
-        <v>96.15271479759168</v>
+        <v>95.0581898180404</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-6.307001380330674</v>
+        <v>-7.041979266276147</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.2993406720134754</v>
+        <v>0.2959223096112322</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.7458962851115857</v>
+        <v>0.7333914426671048</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.5081427539148284</v>
+        <v>0.4991167418983916</v>
       </c>
       <c r="BD10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BE10" t="n">
         <v>2425</v>
@@ -3120,88 +3120,88 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8595718085586398</v>
+        <v>0.854101281328731</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8842453853900665</v>
+        <v>0.8830719549280545</v>
       </c>
       <c r="E11" t="n">
-        <v>98.26502607392173</v>
+        <v>97.47813760581515</v>
       </c>
       <c r="F11" t="n">
-        <v>99.24601979626637</v>
+        <v>98.91821854655932</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9809937223446218</v>
+        <v>-1.440080940744138</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3168664644506192</v>
+        <v>0.3141918058725944</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7229545516160432</v>
+        <v>0.7275847566481757</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5184012440529205</v>
+        <v>0.5200380756467359</v>
       </c>
       <c r="K11" t="n">
-        <v>4825</v>
+        <v>5025</v>
       </c>
       <c r="L11" t="n">
-        <v>1860</v>
+        <v>1923</v>
       </c>
       <c r="M11" t="n">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="N11" t="n">
-        <v>939</v>
+        <v>975</v>
       </c>
       <c r="O11" t="n">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="P11" t="n">
-        <v>600</v>
+        <v>626</v>
       </c>
       <c r="Q11" t="n">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="R11" t="n">
-        <v>570</v>
+        <v>584</v>
       </c>
       <c r="S11" t="n">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="T11" t="n">
-        <v>592</v>
+        <v>618</v>
       </c>
       <c r="U11" t="n">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="V11" t="n">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="W11" t="n">
-        <v>368</v>
+        <v>387</v>
       </c>
       <c r="X11" t="n">
-        <v>544</v>
+        <v>567</v>
       </c>
       <c r="Y11" t="n">
-        <v>513</v>
+        <v>532</v>
       </c>
       <c r="Z11" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AA11" t="n">
-        <v>1881</v>
+        <v>1951</v>
       </c>
       <c r="AB11" t="n">
-        <v>2157.8</v>
+        <v>2244.96</v>
       </c>
       <c r="AC11" t="n">
-        <v>1890.8</v>
+        <v>1970.96</v>
       </c>
       <c r="AD11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE11" t="n">
         <v>2400</v>
@@ -3282,82 +3282,82 @@
         <v>12</v>
       </c>
       <c r="BE11" t="n">
-        <v>2425</v>
+        <v>2625</v>
       </c>
       <c r="BF11" t="n">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="BG11" t="n">
-        <v>475</v>
+        <v>511</v>
       </c>
       <c r="BH11" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="BI11" t="n">
-        <v>311</v>
+        <v>337</v>
       </c>
       <c r="BJ11" t="n">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="BK11" t="n">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="BL11" t="n">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="BM11" t="n">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="BN11" t="n">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="BO11" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="BP11" t="n">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="BQ11" t="n">
-        <v>279</v>
+        <v>302</v>
       </c>
       <c r="BR11" t="n">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="BS11" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BT11" t="n">
-        <v>1082.48</v>
+        <v>1169.64</v>
       </c>
       <c r="BU11" t="n">
-        <v>939.48</v>
+        <v>1019.64</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.8746163545830208</v>
+        <v>0.8629388371390133</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.8990822802410793</v>
+        <v>0.8956843835948244</v>
       </c>
       <c r="BX11" t="n">
-        <v>101.0991512244135</v>
+        <v>99.36789454340149</v>
       </c>
       <c r="BY11" t="n">
-        <v>99.20581921459949</v>
+        <v>98.57852454836799</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.893332009814009</v>
+        <v>0.7893699950335061</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.3393696982229317</v>
+        <v>0.3324951060519369</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.7510305587457284</v>
+        <v>0.7577751063360073</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.537370360631288</v>
+        <v>0.539058950882597</v>
       </c>
       <c r="CD11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -3372,88 +3372,88 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.8344884557429629</v>
+        <v>0.850863370446023</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8258706688338877</v>
+        <v>0.8214994447237463</v>
       </c>
       <c r="E12" t="n">
-        <v>93.86452312443944</v>
+        <v>95.48064826858685</v>
       </c>
       <c r="F12" t="n">
-        <v>95.4950585621211</v>
+        <v>95.00819810470979</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.630535437681617</v>
+        <v>0.4724501638770835</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2764633888682166</v>
+        <v>0.2763295913549361</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6826238958438676</v>
+        <v>0.6811885873509614</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4915062413579238</v>
+        <v>0.4921597848786214</v>
       </c>
       <c r="K12" t="n">
-        <v>4650</v>
+        <v>5050</v>
       </c>
       <c r="L12" t="n">
-        <v>1722</v>
+        <v>1909</v>
       </c>
       <c r="M12" t="n">
-        <v>406</v>
+        <v>454</v>
       </c>
       <c r="N12" t="n">
-        <v>843</v>
+        <v>933</v>
       </c>
       <c r="O12" t="n">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="P12" t="n">
-        <v>587</v>
+        <v>635</v>
       </c>
       <c r="Q12" t="n">
-        <v>397</v>
+        <v>425</v>
       </c>
       <c r="R12" t="n">
-        <v>621</v>
+        <v>664</v>
       </c>
       <c r="S12" t="n">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="T12" t="n">
-        <v>624</v>
+        <v>676</v>
       </c>
       <c r="U12" t="n">
-        <v>362</v>
+        <v>409</v>
       </c>
       <c r="V12" t="n">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="W12" t="n">
-        <v>369</v>
+        <v>392</v>
       </c>
       <c r="X12" t="n">
-        <v>467</v>
+        <v>511</v>
       </c>
       <c r="Y12" t="n">
-        <v>514</v>
+        <v>553</v>
       </c>
       <c r="Z12" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AA12" t="n">
-        <v>1758</v>
+        <v>1904</v>
       </c>
       <c r="AB12" t="n">
-        <v>2072.24</v>
+        <v>2252.16</v>
       </c>
       <c r="AC12" t="n">
-        <v>1837.24</v>
+        <v>2001.16</v>
       </c>
       <c r="AD12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE12" t="n">
         <v>2425</v>
@@ -3534,82 +3534,82 @@
         <v>12</v>
       </c>
       <c r="BE12" t="n">
-        <v>2225</v>
+        <v>2625</v>
       </c>
       <c r="BF12" t="n">
-        <v>205</v>
+        <v>253</v>
       </c>
       <c r="BG12" t="n">
-        <v>405</v>
+        <v>495</v>
       </c>
       <c r="BH12" t="n">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="BI12" t="n">
-        <v>290</v>
+        <v>338</v>
       </c>
       <c r="BJ12" t="n">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="BK12" t="n">
-        <v>274</v>
+        <v>317</v>
       </c>
       <c r="BL12" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="BM12" t="n">
-        <v>300</v>
+        <v>352</v>
       </c>
       <c r="BN12" t="n">
-        <v>181</v>
+        <v>228</v>
       </c>
       <c r="BO12" t="n">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="BP12" t="n">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="BQ12" t="n">
-        <v>232</v>
+        <v>276</v>
       </c>
       <c r="BR12" t="n">
-        <v>230</v>
+        <v>269</v>
       </c>
       <c r="BS12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BT12" t="n">
-        <v>996.5599999999999</v>
+        <v>1176.48</v>
       </c>
       <c r="BU12" t="n">
-        <v>882.5599999999999</v>
+        <v>1046.48</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.8545907026542751</v>
+        <v>0.8829882698661117</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.8295703444047248</v>
+        <v>0.8205949633358625</v>
       </c>
       <c r="BX12" t="n">
-        <v>96.45771050675101</v>
+        <v>99.16669157129422</v>
       </c>
       <c r="BY12" t="n">
-        <v>95.65050799610221</v>
+        <v>94.6903225881603</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.8072025106488018</v>
+        <v>4.476368983133932</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.2964350580724492</v>
+        <v>0.2931051906693355</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.6832061096070086</v>
+        <v>0.6803563296186286</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.5047904799075101</v>
+        <v>0.5040035653627617</v>
       </c>
       <c r="CD12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -3624,88 +3624,88 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.7674620764038266</v>
+        <v>0.7641125126242505</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8314247400423675</v>
+        <v>0.8207841584229345</v>
       </c>
       <c r="E13" t="n">
-        <v>87.29471229001534</v>
+        <v>87.07987940095173</v>
       </c>
       <c r="F13" t="n">
-        <v>94.8558899011672</v>
+        <v>93.70414135175264</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.561177611151865</v>
+        <v>-6.624261950800917</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3022113333042626</v>
+        <v>0.3067895466387587</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7160708261193905</v>
+        <v>0.7172319146432424</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5207853449394354</v>
+        <v>0.524321747233812</v>
       </c>
       <c r="K13" t="n">
-        <v>4825</v>
+        <v>5025</v>
       </c>
       <c r="L13" t="n">
-        <v>1661</v>
+        <v>1723</v>
       </c>
       <c r="M13" t="n">
-        <v>442</v>
+        <v>462</v>
       </c>
       <c r="N13" t="n">
-        <v>970</v>
+        <v>1007</v>
       </c>
       <c r="O13" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="P13" t="n">
-        <v>510</v>
+        <v>537</v>
       </c>
       <c r="Q13" t="n">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="R13" t="n">
-        <v>603</v>
+        <v>625</v>
       </c>
       <c r="S13" t="n">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="T13" t="n">
-        <v>695</v>
+        <v>733</v>
       </c>
       <c r="U13" t="n">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="V13" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="W13" t="n">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="X13" t="n">
-        <v>519</v>
+        <v>544</v>
       </c>
       <c r="Y13" t="n">
-        <v>544</v>
+        <v>567</v>
       </c>
       <c r="Z13" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AA13" t="n">
-        <v>1834</v>
+        <v>1885</v>
       </c>
       <c r="AB13" t="n">
-        <v>2157.32</v>
+        <v>2248</v>
       </c>
       <c r="AC13" t="n">
-        <v>1896.32</v>
+        <v>1972</v>
       </c>
       <c r="AD13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE13" t="n">
         <v>2425</v>
@@ -3786,82 +3786,82 @@
         <v>12</v>
       </c>
       <c r="BE13" t="n">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="BF13" t="n">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="BG13" t="n">
-        <v>478</v>
+        <v>515</v>
       </c>
       <c r="BH13" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="BI13" t="n">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="BJ13" t="n">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="BK13" t="n">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="BL13" t="n">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="BM13" t="n">
-        <v>369</v>
+        <v>407</v>
       </c>
       <c r="BN13" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="BO13" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="BP13" t="n">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="BQ13" t="n">
-        <v>270</v>
+        <v>295</v>
       </c>
       <c r="BR13" t="n">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="BS13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BT13" t="n">
-        <v>1071.76</v>
+        <v>1162.44</v>
       </c>
       <c r="BU13" t="n">
-        <v>937.76</v>
+        <v>1013.44</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.7695630161754164</v>
+        <v>0.7629599366168786</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.7811227857191141</v>
+        <v>0.7645295098604545</v>
       </c>
       <c r="BX13" t="n">
-        <v>87.92439151574608</v>
+        <v>87.46281448095215</v>
       </c>
       <c r="BY13" t="n">
-        <v>89.13613750916981</v>
+        <v>87.36121740583391</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-1.211745993423738</v>
+        <v>0.1015970751182286</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.3139505842966339</v>
+        <v>0.321851821402021</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.7344160767033108</v>
+        <v>0.7352377661273397</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.5438953996471366</v>
+        <v>0.5489184767741915</v>
       </c>
       <c r="CD13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -3876,166 +3876,166 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.8841073466417416</v>
+        <v>0.8829394377296625</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7903167332214046</v>
+        <v>0.7876164090049853</v>
       </c>
       <c r="E14" t="n">
-        <v>102.1843417754275</v>
+        <v>101.739007646554</v>
       </c>
       <c r="F14" t="n">
-        <v>88.54703494699572</v>
+        <v>88.1488661239662</v>
       </c>
       <c r="G14" t="n">
-        <v>13.63730682843183</v>
+        <v>13.59014152258786</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3450800561444543</v>
+        <v>0.3377284668019019</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7301646981397005</v>
+        <v>0.7309581102141125</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5336018498597763</v>
+        <v>0.5298848945094531</v>
       </c>
       <c r="K14" t="n">
-        <v>4800</v>
+        <v>5000</v>
       </c>
       <c r="L14" t="n">
-        <v>1929</v>
+        <v>1999</v>
       </c>
       <c r="M14" t="n">
-        <v>462</v>
+        <v>477</v>
       </c>
       <c r="N14" t="n">
-        <v>955</v>
+        <v>990</v>
       </c>
       <c r="O14" t="n">
+        <v>192</v>
+      </c>
+      <c r="P14" t="n">
+        <v>603</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>469</v>
+      </c>
+      <c r="R14" t="n">
+        <v>693</v>
+      </c>
+      <c r="S14" t="n">
+        <v>306</v>
+      </c>
+      <c r="T14" t="n">
+        <v>618</v>
+      </c>
+      <c r="U14" t="n">
+        <v>385</v>
+      </c>
+      <c r="V14" t="n">
+        <v>253</v>
+      </c>
+      <c r="W14" t="n">
+        <v>375</v>
+      </c>
+      <c r="X14" t="n">
+        <v>541</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>581</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1719</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2272.92</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1966.92</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2600</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>242</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>499</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>93</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>312</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>242</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>357</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>151</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>302</v>
+      </c>
+      <c r="AN14" t="n">
         <v>186</v>
       </c>
-      <c r="P14" t="n">
-        <v>581</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>447</v>
-      </c>
-      <c r="R14" t="n">
-        <v>666</v>
-      </c>
-      <c r="S14" t="n">
-        <v>301</v>
-      </c>
-      <c r="T14" t="n">
-        <v>597</v>
-      </c>
-      <c r="U14" t="n">
-        <v>377</v>
-      </c>
-      <c r="V14" t="n">
-        <v>243</v>
-      </c>
-      <c r="W14" t="n">
-        <v>362</v>
-      </c>
-      <c r="X14" t="n">
-        <v>522</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>558</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1656</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2191.04</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1890.04</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2400</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>227</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>464</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>87</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>290</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>220</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>330</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>146</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>281</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>178</v>
-      </c>
       <c r="AO14" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="AP14" t="n">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="AQ14" t="n">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="AR14" t="n">
-        <v>275</v>
+        <v>298</v>
       </c>
       <c r="AS14" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AT14" t="n">
-        <v>1091.2</v>
+        <v>1173.08</v>
       </c>
       <c r="AU14" t="n">
-        <v>945.2</v>
+        <v>1022.08</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.8579125355168932</v>
+        <v>0.8576815423109602</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.8001294364521695</v>
+        <v>0.7941816819413042</v>
       </c>
       <c r="AX14" t="n">
-        <v>99.14644894654832</v>
+        <v>98.52372122401306</v>
       </c>
       <c r="AY14" t="n">
-        <v>90.47100931146706</v>
+        <v>89.55730200837401</v>
       </c>
       <c r="AZ14" t="n">
-        <v>8.675439635081265</v>
+        <v>8.966419215639053</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.3391079582810658</v>
+        <v>0.3254296786118027</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.6987378860353025</v>
+        <v>0.7026811255710486</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.5115993662105542</v>
+        <v>0.5061438738944881</v>
       </c>
       <c r="BD14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BE14" t="n">
         <v>2400</v>
@@ -4128,88 +4128,88 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.8790411739577983</v>
+        <v>0.8698868530068125</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8280067815599695</v>
+        <v>0.8221700215668472</v>
       </c>
       <c r="E15" t="n">
-        <v>99.91538486447435</v>
+        <v>99.03280455761467</v>
       </c>
       <c r="F15" t="n">
-        <v>93.63869925384647</v>
+        <v>93.13410948002891</v>
       </c>
       <c r="G15" t="n">
-        <v>6.276685610627879</v>
+        <v>5.898695077585753</v>
       </c>
       <c r="H15" t="n">
-        <v>0.325771879332248</v>
+        <v>0.3258319132498672</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7125619829812098</v>
+        <v>0.7112595036619613</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5221153746691695</v>
+        <v>0.5210402834919265</v>
       </c>
       <c r="K15" t="n">
-        <v>4800</v>
+        <v>5025</v>
       </c>
       <c r="L15" t="n">
-        <v>2080</v>
+        <v>2151</v>
       </c>
       <c r="M15" t="n">
-        <v>555</v>
+        <v>570</v>
       </c>
       <c r="N15" t="n">
-        <v>1075</v>
+        <v>1123</v>
       </c>
       <c r="O15" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="P15" t="n">
-        <v>612</v>
+        <v>643</v>
       </c>
       <c r="Q15" t="n">
-        <v>424</v>
+        <v>447</v>
       </c>
       <c r="R15" t="n">
-        <v>607</v>
+        <v>637</v>
       </c>
       <c r="S15" t="n">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="T15" t="n">
-        <v>660</v>
+        <v>694</v>
       </c>
       <c r="U15" t="n">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="V15" t="n">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="W15" t="n">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="X15" t="n">
-        <v>528</v>
+        <v>548</v>
       </c>
       <c r="Y15" t="n">
-        <v>541</v>
+        <v>566</v>
       </c>
       <c r="Z15" t="n">
         <v>83</v>
       </c>
       <c r="AA15" t="n">
-        <v>1925</v>
+        <v>1994</v>
       </c>
       <c r="AB15" t="n">
-        <v>2375.08</v>
+        <v>2484.28</v>
       </c>
       <c r="AC15" t="n">
-        <v>2086.08</v>
+        <v>2177.28</v>
       </c>
       <c r="AD15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE15" t="n">
         <v>2400</v>
@@ -4290,82 +4290,82 @@
         <v>12</v>
       </c>
       <c r="BE15" t="n">
-        <v>2400</v>
+        <v>2625</v>
       </c>
       <c r="BF15" t="n">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="BG15" t="n">
-        <v>554</v>
+        <v>602</v>
       </c>
       <c r="BH15" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="BI15" t="n">
-        <v>309</v>
+        <v>340</v>
       </c>
       <c r="BJ15" t="n">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="BK15" t="n">
-        <v>294</v>
+        <v>324</v>
       </c>
       <c r="BL15" t="n">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="BM15" t="n">
-        <v>329</v>
+        <v>363</v>
       </c>
       <c r="BN15" t="n">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="BO15" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="BP15" t="n">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="BQ15" t="n">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="BR15" t="n">
-        <v>268</v>
+        <v>293</v>
       </c>
       <c r="BS15" t="n">
         <v>36</v>
       </c>
       <c r="BT15" t="n">
-        <v>1206.36</v>
+        <v>1315.56</v>
       </c>
       <c r="BU15" t="n">
-        <v>1056.36</v>
+        <v>1147.56</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.9153936373132697</v>
+        <v>0.8949928306109529</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.8060953004404361</v>
+        <v>0.7965562605397802</v>
       </c>
       <c r="BX15" t="n">
-        <v>104.1888180890067</v>
+        <v>102.1628226354664</v>
       </c>
       <c r="BY15" t="n">
-        <v>92.43818761754891</v>
+        <v>91.56016971684572</v>
       </c>
       <c r="BZ15" t="n">
-        <v>11.75063047145778</v>
+        <v>10.60265291862062</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.3452018975208058</v>
+        <v>0.3438227305786459</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.6879623226651059</v>
+        <v>0.6873498363062516</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.5245723451874311</v>
+        <v>0.5223158644220975</v>
       </c>
       <c r="CD15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/data/3FEB_25_26/teams_25_26_3FEB.xlsx
+++ b/data/3FEB_25_26/teams_25_26_3FEB.xlsx
@@ -852,166 +852,166 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7976626775990445</v>
+        <v>0.8001833169490543</v>
       </c>
       <c r="D2" t="n">
-        <v>0.895271695835436</v>
+        <v>0.8953743731225363</v>
       </c>
       <c r="E2" t="n">
-        <v>88.11818934582665</v>
+        <v>88.20076215048373</v>
       </c>
       <c r="F2" t="n">
-        <v>103.1193056143328</v>
+        <v>102.9383994952986</v>
       </c>
       <c r="G2" t="n">
-        <v>-15.00111626850616</v>
+        <v>-14.73763734481487</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2282510484645638</v>
+        <v>0.2247772017729559</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6464559444136849</v>
+        <v>0.6517377843894578</v>
       </c>
       <c r="J2" t="n">
-        <v>0.429999880756701</v>
+        <v>0.4326921930352894</v>
       </c>
       <c r="K2" t="n">
-        <v>5175</v>
+        <v>5375</v>
       </c>
       <c r="L2" t="n">
-        <v>1853</v>
+        <v>1932</v>
       </c>
       <c r="M2" t="n">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="N2" t="n">
-        <v>1046</v>
+        <v>1082</v>
       </c>
       <c r="O2" t="n">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="P2" t="n">
-        <v>613</v>
+        <v>633</v>
       </c>
       <c r="Q2" t="n">
-        <v>385</v>
+        <v>405</v>
       </c>
       <c r="R2" t="n">
-        <v>591</v>
+        <v>624</v>
       </c>
       <c r="S2" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="T2" t="n">
-        <v>587</v>
+        <v>616</v>
       </c>
       <c r="U2" t="n">
+        <v>347</v>
+      </c>
+      <c r="V2" t="n">
+        <v>215</v>
+      </c>
+      <c r="W2" t="n">
+        <v>433</v>
+      </c>
+      <c r="X2" t="n">
+        <v>620</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>549</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2267</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2422.56</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2189.56</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>2675</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>269</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>558</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>82</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>297</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>210</v>
+      </c>
+      <c r="AK2" t="n">
         <v>333</v>
       </c>
-      <c r="V2" t="n">
-        <v>211</v>
-      </c>
-      <c r="W2" t="n">
-        <v>412</v>
-      </c>
-      <c r="X2" t="n">
-        <v>597</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>526</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>33</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2185</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2331.04</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2102.04</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2475</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>250</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>522</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>75</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>277</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>190</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>300</v>
-      </c>
       <c r="AL2" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="AM2" t="n">
-        <v>277</v>
+        <v>306</v>
       </c>
       <c r="AN2" t="n">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="AO2" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="AP2" t="n">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="AQ2" t="n">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="AR2" t="n">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="AS2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT2" t="n">
-        <v>1110</v>
+        <v>1201.52</v>
       </c>
       <c r="AU2" t="n">
-        <v>1006</v>
+        <v>1093.52</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.8266035887880183</v>
+        <v>0.8294186435504246</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.9404365819691645</v>
+        <v>0.9371677145330783</v>
       </c>
       <c r="AX2" t="n">
-        <v>90.91239986339498</v>
+        <v>90.86260620212694</v>
       </c>
       <c r="AY2" t="n">
-        <v>108.9527791394979</v>
+        <v>108.1422381687244</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-18.04037927610286</v>
+        <v>-17.27963196659747</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.2136878708190465</v>
+        <v>0.2078604218701013</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.6326630760185513</v>
+        <v>0.6442877458466462</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.4181588421673454</v>
+        <v>0.4244543158467804</v>
       </c>
       <c r="BD2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BE2" t="n">
         <v>2700</v>
@@ -1104,88 +1104,88 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7701922532374672</v>
+        <v>0.7723078428252476</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8813979018463917</v>
+        <v>0.883110518157143</v>
       </c>
       <c r="E3" t="n">
-        <v>87.64383305299506</v>
+        <v>87.77210813310401</v>
       </c>
       <c r="F3" t="n">
-        <v>100.6032219538514</v>
+        <v>100.6535761402495</v>
       </c>
       <c r="G3" t="n">
-        <v>-12.9593889008563</v>
+        <v>-12.88146800714543</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2869511741422142</v>
+        <v>0.2832405978473672</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6911321595543859</v>
+        <v>0.6939619181235611</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4859836587176629</v>
+        <v>0.4844984572690079</v>
       </c>
       <c r="K3" t="n">
-        <v>5100</v>
+        <v>5300</v>
       </c>
       <c r="L3" t="n">
-        <v>1817</v>
+        <v>1888</v>
       </c>
       <c r="M3" t="n">
-        <v>486</v>
+        <v>505</v>
       </c>
       <c r="N3" t="n">
-        <v>1069</v>
+        <v>1111</v>
       </c>
       <c r="O3" t="n">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="P3" t="n">
-        <v>580</v>
+        <v>611</v>
       </c>
       <c r="Q3" t="n">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="R3" t="n">
-        <v>643</v>
+        <v>659</v>
       </c>
       <c r="S3" t="n">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="T3" t="n">
-        <v>670</v>
+        <v>696</v>
       </c>
       <c r="U3" t="n">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="V3" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="W3" t="n">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="X3" t="n">
-        <v>574</v>
+        <v>591</v>
       </c>
       <c r="Y3" t="n">
-        <v>563</v>
+        <v>583</v>
       </c>
       <c r="Z3" t="n">
         <v>43</v>
       </c>
       <c r="AA3" t="n">
-        <v>2096</v>
+        <v>2177</v>
       </c>
       <c r="AB3" t="n">
-        <v>2354.92</v>
+        <v>2440.96</v>
       </c>
       <c r="AC3" t="n">
-        <v>2068.92</v>
+        <v>2146.96</v>
       </c>
       <c r="AD3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE3" t="n">
         <v>2625</v>
@@ -1266,82 +1266,82 @@
         <v>13</v>
       </c>
       <c r="BE3" t="n">
-        <v>2475</v>
+        <v>2675</v>
       </c>
       <c r="BF3" t="n">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="BG3" t="n">
-        <v>510</v>
+        <v>552</v>
       </c>
       <c r="BH3" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="BI3" t="n">
-        <v>277</v>
+        <v>308</v>
       </c>
       <c r="BJ3" t="n">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="BK3" t="n">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="BL3" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="BM3" t="n">
-        <v>352</v>
+        <v>378</v>
       </c>
       <c r="BN3" t="n">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="BO3" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="BP3" t="n">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="BQ3" t="n">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="BR3" t="n">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="BS3" t="n">
         <v>23</v>
       </c>
       <c r="BT3" t="n">
-        <v>1136.76</v>
+        <v>1222.8</v>
       </c>
       <c r="BU3" t="n">
-        <v>1004.76</v>
+        <v>1082.8</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.8075097055513655</v>
+        <v>0.808870311472011</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.8331792171098171</v>
+        <v>0.8403135793264409</v>
       </c>
       <c r="BX3" t="n">
-        <v>91.36764282664525</v>
+        <v>91.33774608119776</v>
       </c>
       <c r="BY3" t="n">
-        <v>94.96303256227638</v>
+        <v>95.49760165750136</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-3.595389735631134</v>
+        <v>-4.159855576303626</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.2826381923495995</v>
+        <v>0.2755488075901065</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.7132470414491486</v>
+        <v>0.7172054138263635</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.5026499615143817</v>
+        <v>0.4983975353250163</v>
       </c>
       <c r="CD3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -1356,88 +1356,88 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8502881239512082</v>
+        <v>0.8503861259577228</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8696507320652987</v>
+        <v>0.8756891343622798</v>
       </c>
       <c r="E4" t="n">
-        <v>96.32348362661851</v>
+        <v>96.42768440340714</v>
       </c>
       <c r="F4" t="n">
-        <v>97.73865083464179</v>
+        <v>98.58153994949302</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.415167208023286</v>
+        <v>-2.153855546085888</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2922907989491457</v>
+        <v>0.2960061101006743</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7222680149261455</v>
+        <v>0.7194365008385494</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5064610579429996</v>
+        <v>0.5070028612992488</v>
       </c>
       <c r="K4" t="n">
-        <v>5000</v>
+        <v>5200</v>
       </c>
       <c r="L4" t="n">
-        <v>1916</v>
+        <v>2002</v>
       </c>
       <c r="M4" t="n">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="N4" t="n">
-        <v>922</v>
+        <v>962</v>
       </c>
       <c r="O4" t="n">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="P4" t="n">
-        <v>666</v>
+        <v>694</v>
       </c>
       <c r="Q4" t="n">
-        <v>421</v>
+        <v>442</v>
       </c>
       <c r="R4" t="n">
-        <v>619</v>
+        <v>655</v>
       </c>
       <c r="S4" t="n">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="T4" t="n">
-        <v>638</v>
+        <v>662</v>
       </c>
       <c r="U4" t="n">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="V4" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="W4" t="n">
-        <v>394</v>
+        <v>411</v>
       </c>
       <c r="X4" t="n">
-        <v>618</v>
+        <v>639</v>
       </c>
       <c r="Y4" t="n">
-        <v>567</v>
+        <v>593</v>
       </c>
       <c r="Z4" t="n">
         <v>32</v>
       </c>
       <c r="AA4" t="n">
-        <v>1938</v>
+        <v>2032</v>
       </c>
       <c r="AB4" t="n">
-        <v>2254.36</v>
+        <v>2355.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>1988.36</v>
+        <v>2075.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE4" t="n">
         <v>2600</v>
@@ -1518,82 +1518,82 @@
         <v>13</v>
       </c>
       <c r="BE4" t="n">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="BF4" t="n">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="BG4" t="n">
-        <v>433</v>
+        <v>473</v>
       </c>
       <c r="BH4" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="BI4" t="n">
-        <v>323</v>
+        <v>351</v>
       </c>
       <c r="BJ4" t="n">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="BK4" t="n">
-        <v>315</v>
+        <v>351</v>
       </c>
       <c r="BL4" t="n">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="BM4" t="n">
-        <v>313</v>
+        <v>337</v>
       </c>
       <c r="BN4" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="BO4" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="BP4" t="n">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="BQ4" t="n">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="BR4" t="n">
-        <v>279</v>
+        <v>305</v>
       </c>
       <c r="BS4" t="n">
         <v>15</v>
       </c>
       <c r="BT4" t="n">
-        <v>1091.6</v>
+        <v>1192.44</v>
       </c>
       <c r="BU4" t="n">
-        <v>953.6</v>
+        <v>1040.44</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.8955212129491478</v>
+        <v>0.89223774857772</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.8691590488854583</v>
+        <v>0.881273675262485</v>
       </c>
       <c r="BX4" t="n">
-        <v>102.308631460531</v>
+        <v>102.0566370268842</v>
       </c>
       <c r="BY4" t="n">
-        <v>97.32478185382764</v>
+        <v>99.04239615897737</v>
       </c>
       <c r="BZ4" t="n">
-        <v>4.983849606703366</v>
+        <v>3.014240867906881</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.3119523553419807</v>
+        <v>0.3178705502302044</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.7371794325181783</v>
+        <v>0.7303693722205222</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.5248909393201541</v>
+        <v>0.5245568628497945</v>
       </c>
       <c r="CD4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -1608,88 +1608,88 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8069335209957328</v>
+        <v>0.8093353406194697</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8537016710933328</v>
+        <v>0.8609966653626249</v>
       </c>
       <c r="E5" t="n">
-        <v>90.04890825400949</v>
+        <v>90.11644051259223</v>
       </c>
       <c r="F5" t="n">
-        <v>97.72009231311003</v>
+        <v>98.64533892791329</v>
       </c>
       <c r="G5" t="n">
-        <v>-7.671184059100511</v>
+        <v>-8.528898415321011</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2493635414855296</v>
+        <v>0.2457822514283938</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6960713346703916</v>
+        <v>0.6928036337642655</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4740848304744376</v>
+        <v>0.4711222917457827</v>
       </c>
       <c r="K5" t="n">
-        <v>5000</v>
+        <v>5200</v>
       </c>
       <c r="L5" t="n">
-        <v>1771</v>
+        <v>1853</v>
       </c>
       <c r="M5" t="n">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="N5" t="n">
-        <v>989</v>
+        <v>1024</v>
       </c>
       <c r="O5" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="P5" t="n">
-        <v>619</v>
+        <v>642</v>
       </c>
       <c r="Q5" t="n">
-        <v>333</v>
+        <v>358</v>
       </c>
       <c r="R5" t="n">
-        <v>543</v>
+        <v>571</v>
       </c>
       <c r="S5" t="n">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="T5" t="n">
-        <v>648</v>
+        <v>670</v>
       </c>
       <c r="U5" t="n">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="V5" t="n">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="W5" t="n">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="X5" t="n">
-        <v>553</v>
+        <v>581</v>
       </c>
       <c r="Y5" t="n">
-        <v>485</v>
+        <v>511</v>
       </c>
       <c r="Z5" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AA5" t="n">
-        <v>1904</v>
+        <v>2006</v>
       </c>
       <c r="AB5" t="n">
-        <v>2202.92</v>
+        <v>2297.24</v>
       </c>
       <c r="AC5" t="n">
-        <v>1973.92</v>
+        <v>2063.24</v>
       </c>
       <c r="AD5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE5" t="n">
         <v>2600</v>
@@ -1770,82 +1770,82 @@
         <v>13</v>
       </c>
       <c r="BE5" t="n">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="BF5" t="n">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="BG5" t="n">
-        <v>480</v>
+        <v>515</v>
       </c>
       <c r="BH5" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="BI5" t="n">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="BJ5" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="BK5" t="n">
-        <v>256</v>
+        <v>284</v>
       </c>
       <c r="BL5" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="BM5" t="n">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="BN5" t="n">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="BO5" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="BP5" t="n">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="BQ5" t="n">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="BR5" t="n">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="BS5" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="BT5" t="n">
-        <v>1048.64</v>
+        <v>1142.96</v>
       </c>
       <c r="BU5" t="n">
-        <v>935.64</v>
+        <v>1024.96</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.8555345619552027</v>
+        <v>0.8565996595904095</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.8770683250485956</v>
+        <v>0.889860878667544</v>
       </c>
       <c r="BX5" t="n">
-        <v>95.81907201159787</v>
+        <v>95.51027777817964</v>
       </c>
       <c r="BY5" t="n">
-        <v>100.4211833336144</v>
+        <v>102.0639003308744</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-4.602111322016543</v>
+        <v>-6.553622552694771</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.2727887233278299</v>
+        <v>0.2638242061487661</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.6889940562114382</v>
+        <v>0.6830030604344899</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.4849174593120856</v>
+        <v>0.4781591027134184</v>
       </c>
       <c r="CD5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -1860,88 +1860,88 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8806337778245151</v>
+        <v>0.8781230070652373</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8614855738673717</v>
+        <v>0.8507794575981837</v>
       </c>
       <c r="E6" t="n">
-        <v>100.9396968907982</v>
+        <v>100.6431725145976</v>
       </c>
       <c r="F6" t="n">
-        <v>97.99172279557435</v>
+        <v>96.82006944313625</v>
       </c>
       <c r="G6" t="n">
-        <v>2.947974095223874</v>
+        <v>3.823103071461313</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3064049266268236</v>
+        <v>0.3044820546954171</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6940694743298274</v>
+        <v>0.6947024297705829</v>
       </c>
       <c r="J6" t="n">
-        <v>0.498709753771801</v>
+        <v>0.498010127877481</v>
       </c>
       <c r="K6" t="n">
-        <v>5025</v>
+        <v>5225</v>
       </c>
       <c r="L6" t="n">
-        <v>1958</v>
+        <v>2023</v>
       </c>
       <c r="M6" t="n">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="N6" t="n">
-        <v>900</v>
+        <v>928</v>
       </c>
       <c r="O6" t="n">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="P6" t="n">
-        <v>693</v>
+        <v>727</v>
       </c>
       <c r="Q6" t="n">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="R6" t="n">
-        <v>638</v>
+        <v>651</v>
       </c>
       <c r="S6" t="n">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="T6" t="n">
-        <v>621</v>
+        <v>648</v>
       </c>
       <c r="U6" t="n">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="V6" t="n">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="W6" t="n">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="X6" t="n">
-        <v>528</v>
+        <v>546</v>
       </c>
       <c r="Y6" t="n">
-        <v>565</v>
+        <v>580</v>
       </c>
       <c r="Z6" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AA6" t="n">
-        <v>1937</v>
+        <v>1984</v>
       </c>
       <c r="AB6" t="n">
-        <v>2227.72</v>
+        <v>2307.44</v>
       </c>
       <c r="AC6" t="n">
-        <v>1941.72</v>
+        <v>2011.44</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE6" t="n">
         <v>2625</v>
@@ -2022,82 +2022,82 @@
         <v>13</v>
       </c>
       <c r="BE6" t="n">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="BF6" t="n">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="BG6" t="n">
-        <v>436</v>
+        <v>464</v>
       </c>
       <c r="BH6" t="n">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="BI6" t="n">
-        <v>334</v>
+        <v>368</v>
       </c>
       <c r="BJ6" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="BK6" t="n">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="BL6" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="BM6" t="n">
-        <v>315</v>
+        <v>342</v>
       </c>
       <c r="BN6" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="BO6" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="BP6" t="n">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="BQ6" t="n">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="BR6" t="n">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="BS6" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="BT6" t="n">
-        <v>1053.6</v>
+        <v>1133.32</v>
       </c>
       <c r="BU6" t="n">
-        <v>908.6</v>
+        <v>978.3199999999999</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.8883313651577199</v>
+        <v>0.8827177015366101</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.8085871491713599</v>
+        <v>0.791244026224985</v>
       </c>
       <c r="BX6" t="n">
-        <v>102.7365056030042</v>
+        <v>102.0052407958178</v>
       </c>
       <c r="BY6" t="n">
-        <v>91.11671927230073</v>
+        <v>89.30225899229175</v>
       </c>
       <c r="BZ6" t="n">
-        <v>11.61978633070346</v>
+        <v>12.70298180352606</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.3203813862205845</v>
+        <v>0.3154605300813285</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.7239297968370425</v>
+        <v>0.7228987598333834</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.5211722914775206</v>
+        <v>0.518045152173056</v>
       </c>
       <c r="CD6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -2112,88 +2112,88 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.8813613606340612</v>
+        <v>0.8819990508135221</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7495306764944965</v>
+        <v>0.7539025466562197</v>
       </c>
       <c r="E7" t="n">
-        <v>102.7521256128761</v>
+        <v>102.5853418015902</v>
       </c>
       <c r="F7" t="n">
-        <v>85.9026509234902</v>
+        <v>86.07043674439097</v>
       </c>
       <c r="G7" t="n">
-        <v>16.84947468938592</v>
+        <v>16.51490505719926</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3517108079254072</v>
+        <v>0.3464994774750537</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6918099082388661</v>
+        <v>0.6983583335188037</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5209576318410256</v>
+        <v>0.5201515690779093</v>
       </c>
       <c r="K7" t="n">
-        <v>5075</v>
+        <v>5275</v>
       </c>
       <c r="L7" t="n">
-        <v>2003</v>
+        <v>2085</v>
       </c>
       <c r="M7" t="n">
-        <v>490</v>
+        <v>509</v>
       </c>
       <c r="N7" t="n">
-        <v>994</v>
+        <v>1037</v>
       </c>
       <c r="O7" t="n">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="P7" t="n">
-        <v>688</v>
+        <v>713</v>
       </c>
       <c r="Q7" t="n">
-        <v>402</v>
+        <v>419</v>
       </c>
       <c r="R7" t="n">
-        <v>633</v>
+        <v>661</v>
       </c>
       <c r="S7" t="n">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="T7" t="n">
-        <v>636</v>
+        <v>661</v>
       </c>
       <c r="U7" t="n">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="V7" t="n">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="W7" t="n">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="X7" t="n">
-        <v>582</v>
+        <v>605</v>
       </c>
       <c r="Y7" t="n">
-        <v>554</v>
+        <v>576</v>
       </c>
       <c r="Z7" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AA7" t="n">
-        <v>1674</v>
+        <v>1753</v>
       </c>
       <c r="AB7" t="n">
-        <v>2282.52</v>
+        <v>2373.84</v>
       </c>
       <c r="AC7" t="n">
-        <v>1952.52</v>
+        <v>2035.84</v>
       </c>
       <c r="AD7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE7" t="n">
         <v>2650</v>
@@ -2274,82 +2274,82 @@
         <v>13</v>
       </c>
       <c r="BE7" t="n">
-        <v>2425</v>
+        <v>2625</v>
       </c>
       <c r="BF7" t="n">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="BG7" t="n">
-        <v>491</v>
+        <v>534</v>
       </c>
       <c r="BH7" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="BI7" t="n">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="BJ7" t="n">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="BK7" t="n">
-        <v>282</v>
+        <v>310</v>
       </c>
       <c r="BL7" t="n">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="BM7" t="n">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="BN7" t="n">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="BO7" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="BP7" t="n">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="BQ7" t="n">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="BR7" t="n">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="BS7" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="BT7" t="n">
-        <v>1097.08</v>
+        <v>1188.4</v>
       </c>
       <c r="BU7" t="n">
-        <v>939.0799999999999</v>
+        <v>1022.4</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.858714433653916</v>
+        <v>0.8617318853190028</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.7255340618385538</v>
+        <v>0.7361236955970727</v>
       </c>
       <c r="BX7" t="n">
-        <v>100.0589456301867</v>
+        <v>99.93254569859103</v>
       </c>
       <c r="BY7" t="n">
-        <v>81.62642754761778</v>
+        <v>82.29093944910181</v>
       </c>
       <c r="BZ7" t="n">
-        <v>18.43251808256892</v>
+        <v>17.6416062494892</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.352798392891681</v>
+        <v>0.342292071608953</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.7207970730015508</v>
+        <v>0.731664141656604</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.5314395254689591</v>
+        <v>0.5290211004328853</v>
       </c>
       <c r="CD7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -2364,166 +2364,166 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9567161923814189</v>
+        <v>0.9508202761597372</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8709161415399924</v>
+        <v>0.8674294242900278</v>
       </c>
       <c r="E8" t="n">
-        <v>109.5265406225832</v>
+        <v>109.1186299566897</v>
       </c>
       <c r="F8" t="n">
-        <v>98.45023002850263</v>
+        <v>98.36768304006003</v>
       </c>
       <c r="G8" t="n">
-        <v>11.07631059408054</v>
+        <v>10.75094691662964</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3346518230684604</v>
+        <v>0.3382641155878053</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7001259265279984</v>
+        <v>0.6983459352710043</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5179739193714414</v>
+        <v>0.5193284412941437</v>
       </c>
       <c r="K8" t="n">
-        <v>5000</v>
+        <v>5200</v>
       </c>
       <c r="L8" t="n">
-        <v>2235</v>
+        <v>2312</v>
       </c>
       <c r="M8" t="n">
-        <v>553</v>
+        <v>570</v>
       </c>
       <c r="N8" t="n">
-        <v>990</v>
+        <v>1028</v>
       </c>
       <c r="O8" t="n">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="P8" t="n">
-        <v>718</v>
+        <v>745</v>
       </c>
       <c r="Q8" t="n">
-        <v>376</v>
+        <v>401</v>
       </c>
       <c r="R8" t="n">
-        <v>604</v>
+        <v>640</v>
       </c>
       <c r="S8" t="n">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="T8" t="n">
-        <v>617</v>
+        <v>651</v>
       </c>
       <c r="U8" t="n">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="V8" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="W8" t="n">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="X8" t="n">
-        <v>558</v>
+        <v>574</v>
       </c>
       <c r="Y8" t="n">
-        <v>541</v>
+        <v>566</v>
       </c>
       <c r="Z8" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AA8" t="n">
-        <v>1973</v>
+        <v>2047</v>
       </c>
       <c r="AB8" t="n">
-        <v>2332.76</v>
+        <v>2428.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>2039.76</v>
+        <v>2117.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE8" t="n">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="AF8" t="n">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="AG8" t="n">
-        <v>468</v>
+        <v>506</v>
       </c>
       <c r="AH8" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="AI8" t="n">
-        <v>342</v>
+        <v>369</v>
       </c>
       <c r="AJ8" t="n">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="AK8" t="n">
-        <v>309</v>
+        <v>345</v>
       </c>
       <c r="AL8" t="n">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="AM8" t="n">
-        <v>258</v>
+        <v>292</v>
       </c>
       <c r="AN8" t="n">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="AO8" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AP8" t="n">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="AQ8" t="n">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="AR8" t="n">
-        <v>278</v>
+        <v>303</v>
       </c>
       <c r="AS8" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AT8" t="n">
-        <v>1101.96</v>
+        <v>1197.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>964.96</v>
+        <v>1042.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.9244469352968511</v>
+        <v>0.9151373533984545</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.9210739405710027</v>
+        <v>0.9102422138379187</v>
       </c>
       <c r="AX8" t="n">
-        <v>105.4877797629138</v>
+        <v>104.9826323434091</v>
       </c>
       <c r="AY8" t="n">
-        <v>103.5801257865238</v>
+        <v>103.0204244436369</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.90765397639003</v>
+        <v>1.96220789977212</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.3133056275959089</v>
+        <v>0.3221722276709489</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.6835726747556681</v>
+        <v>0.68128601930109</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.488420376791544</v>
+        <v>0.4934027700661715</v>
       </c>
       <c r="BD8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BE8" t="n">
         <v>2600</v>
@@ -2616,166 +2616,166 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.8794510318030223</v>
+        <v>0.8851124994947063</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8866265511738084</v>
+        <v>0.8853269213640691</v>
       </c>
       <c r="E9" t="n">
-        <v>99.76026470518349</v>
+        <v>100.5253994403985</v>
       </c>
       <c r="F9" t="n">
-        <v>101.6817719751607</v>
+        <v>101.5798847385439</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.921507269977174</v>
+        <v>-1.054485298145323</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2987793932901127</v>
+        <v>0.3008013916770834</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6722840926522222</v>
+        <v>0.6699312856698718</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4824512696667486</v>
+        <v>0.482335915248586</v>
       </c>
       <c r="K9" t="n">
-        <v>5075</v>
+        <v>5275</v>
       </c>
       <c r="L9" t="n">
-        <v>2022</v>
+        <v>2116</v>
       </c>
       <c r="M9" t="n">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="N9" t="n">
-        <v>989</v>
+        <v>1026</v>
       </c>
       <c r="O9" t="n">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="P9" t="n">
-        <v>683</v>
+        <v>715</v>
       </c>
       <c r="Q9" t="n">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="R9" t="n">
-        <v>609</v>
+        <v>633</v>
       </c>
       <c r="S9" t="n">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="T9" t="n">
-        <v>615</v>
+        <v>637</v>
       </c>
       <c r="U9" t="n">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="V9" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="W9" t="n">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="X9" t="n">
-        <v>640</v>
+        <v>672</v>
       </c>
       <c r="Y9" t="n">
-        <v>546</v>
+        <v>565</v>
       </c>
       <c r="Z9" t="n">
         <v>48</v>
       </c>
       <c r="AA9" t="n">
-        <v>2057</v>
+        <v>2143</v>
       </c>
       <c r="AB9" t="n">
-        <v>2316.96</v>
+        <v>2408.52</v>
       </c>
       <c r="AC9" t="n">
-        <v>2033.96</v>
+        <v>2112.52</v>
       </c>
       <c r="AD9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE9" t="n">
-        <v>2450</v>
+        <v>2650</v>
       </c>
       <c r="AF9" t="n">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="AG9" t="n">
-        <v>498</v>
+        <v>535</v>
       </c>
       <c r="AH9" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="AI9" t="n">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="AJ9" t="n">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="AK9" t="n">
+        <v>313</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>149</v>
+      </c>
+      <c r="AM9" t="n">
         <v>289</v>
       </c>
-      <c r="AL9" t="n">
-        <v>136</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>267</v>
-      </c>
       <c r="AN9" t="n">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="AO9" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AP9" t="n">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="AQ9" t="n">
-        <v>307</v>
+        <v>339</v>
       </c>
       <c r="AR9" t="n">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="AS9" t="n">
         <v>19</v>
       </c>
       <c r="AT9" t="n">
-        <v>1109.16</v>
+        <v>1200.72</v>
       </c>
       <c r="AU9" t="n">
-        <v>973.16</v>
+        <v>1051.72</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.8648878557140557</v>
+        <v>0.8773310354119596</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.9003691964642723</v>
+        <v>0.8967128102839887</v>
       </c>
       <c r="AX9" t="n">
-        <v>97.82823662169959</v>
+        <v>99.507123637013</v>
       </c>
       <c r="AY9" t="n">
-        <v>102.7915409895599</v>
+        <v>102.5023996690648</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-4.963304367860325</v>
+        <v>-2.995276032051767</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.2887438766485061</v>
+        <v>0.2935598362410327</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.6564040784806914</v>
+        <v>0.6529200040676468</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.4602884608065301</v>
+        <v>0.4617625834209909</v>
       </c>
       <c r="BD9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BE9" t="n">
         <v>2625</v>
@@ -2868,88 +2868,88 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.814134359132702</v>
+        <v>0.815393940275086</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8555538201319564</v>
+        <v>0.8531220170159555</v>
       </c>
       <c r="E10" t="n">
-        <v>92.06434799149734</v>
+        <v>92.06021312986337</v>
       </c>
       <c r="F10" t="n">
-        <v>95.8666875362299</v>
+        <v>95.70468443291246</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.802339544732551</v>
+        <v>-3.644471303049055</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2860391213132434</v>
+        <v>0.2821226368902643</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7222463129844644</v>
+        <v>0.7190402582115577</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4959332116966336</v>
+        <v>0.4924513729931247</v>
       </c>
       <c r="K10" t="n">
-        <v>5075</v>
+        <v>5275</v>
       </c>
       <c r="L10" t="n">
-        <v>1873</v>
+        <v>1948</v>
       </c>
       <c r="M10" t="n">
-        <v>469</v>
+        <v>487</v>
       </c>
       <c r="N10" t="n">
-        <v>1002</v>
+        <v>1042</v>
       </c>
       <c r="O10" t="n">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="P10" t="n">
-        <v>638</v>
+        <v>659</v>
       </c>
       <c r="Q10" t="n">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="R10" t="n">
-        <v>603</v>
+        <v>627</v>
       </c>
       <c r="S10" t="n">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="T10" t="n">
-        <v>627</v>
+        <v>650</v>
       </c>
       <c r="U10" t="n">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="V10" t="n">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="W10" t="n">
-        <v>404</v>
+        <v>421</v>
       </c>
       <c r="X10" t="n">
-        <v>556</v>
+        <v>579</v>
       </c>
       <c r="Y10" t="n">
-        <v>549</v>
+        <v>569</v>
       </c>
       <c r="Z10" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="AA10" t="n">
-        <v>1936</v>
+        <v>2012</v>
       </c>
       <c r="AB10" t="n">
-        <v>2309.32</v>
+        <v>2397.88</v>
       </c>
       <c r="AC10" t="n">
-        <v>2037.32</v>
+        <v>2118.88</v>
       </c>
       <c r="AD10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE10" t="n">
         <v>2650</v>
@@ -3030,82 +3030,82 @@
         <v>13</v>
       </c>
       <c r="BE10" t="n">
-        <v>2425</v>
+        <v>2625</v>
       </c>
       <c r="BF10" t="n">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="BG10" t="n">
-        <v>475</v>
+        <v>515</v>
       </c>
       <c r="BH10" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="BI10" t="n">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="BJ10" t="n">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="BK10" t="n">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="BL10" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="BM10" t="n">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="BN10" t="n">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="BO10" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="BP10" t="n">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="BQ10" t="n">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="BR10" t="n">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="BS10" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BT10" t="n">
-        <v>1090</v>
+        <v>1178.56</v>
       </c>
       <c r="BU10" t="n">
-        <v>973</v>
+        <v>1054.56</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.8615072576757571</v>
+        <v>0.8603823508418287</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.8613344611090591</v>
+        <v>0.8560261901865106</v>
       </c>
       <c r="BX10" t="n">
-        <v>96.44983021787486</v>
+        <v>96.1042157079625</v>
       </c>
       <c r="BY10" t="n">
-        <v>96.74256006426852</v>
+        <v>96.35117904778447</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0.292729846393654</v>
+        <v>-0.2469633398219621</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.2753323339904222</v>
+        <v>0.2683229641692966</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.7101724224949377</v>
+        <v>0.704689073756011</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.4924843873113957</v>
+        <v>0.485786004087858</v>
       </c>
       <c r="CD10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -3120,166 +3120,166 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.854101281328731</v>
+        <v>0.8568637676593924</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8830719549280545</v>
+        <v>0.8808460175277355</v>
       </c>
       <c r="E11" t="n">
-        <v>97.47813760581515</v>
+        <v>97.64868734406079</v>
       </c>
       <c r="F11" t="n">
-        <v>98.91821854655932</v>
+        <v>98.61286341537733</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.440080940744138</v>
+        <v>-0.9641760713165357</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3141918058725944</v>
+        <v>0.3111572794023815</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7275847566481757</v>
+        <v>0.7307362586818539</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5200380756467359</v>
+        <v>0.5212916719275295</v>
       </c>
       <c r="K11" t="n">
-        <v>5025</v>
+        <v>5225</v>
       </c>
       <c r="L11" t="n">
-        <v>1923</v>
+        <v>2004</v>
       </c>
       <c r="M11" t="n">
-        <v>477</v>
+        <v>501</v>
       </c>
       <c r="N11" t="n">
-        <v>975</v>
+        <v>1021</v>
       </c>
       <c r="O11" t="n">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="P11" t="n">
-        <v>626</v>
+        <v>647</v>
       </c>
       <c r="Q11" t="n">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="R11" t="n">
-        <v>584</v>
+        <v>601</v>
       </c>
       <c r="S11" t="n">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="T11" t="n">
-        <v>618</v>
+        <v>652</v>
       </c>
       <c r="U11" t="n">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="V11" t="n">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="W11" t="n">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="X11" t="n">
-        <v>567</v>
+        <v>587</v>
       </c>
       <c r="Y11" t="n">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="Z11" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AA11" t="n">
-        <v>1951</v>
+        <v>2022</v>
       </c>
       <c r="AB11" t="n">
-        <v>2244.96</v>
+        <v>2332.44</v>
       </c>
       <c r="AC11" t="n">
-        <v>1970.96</v>
+        <v>2050.44</v>
       </c>
       <c r="AD11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE11" t="n">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="AF11" t="n">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="AG11" t="n">
-        <v>464</v>
+        <v>510</v>
       </c>
       <c r="AH11" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="AI11" t="n">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="AJ11" t="n">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="AK11" t="n">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="AL11" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="AM11" t="n">
-        <v>302</v>
+        <v>336</v>
       </c>
       <c r="AN11" t="n">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="AO11" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="AP11" t="n">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="AQ11" t="n">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="AR11" t="n">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="AS11" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AT11" t="n">
-        <v>1075.32</v>
+        <v>1162.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>951.3199999999999</v>
+        <v>1030.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.8445272625342586</v>
+        <v>0.8507886981797715</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.8694084905390532</v>
+        <v>0.8660076514606458</v>
       </c>
       <c r="AX11" t="n">
-        <v>95.43090092342997</v>
+        <v>95.92948014472007</v>
       </c>
       <c r="AY11" t="n">
-        <v>99.28622037793322</v>
+        <v>98.64720228238664</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-3.855319454503253</v>
+        <v>-2.717722137666577</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.2943632306783068</v>
+        <v>0.2898194527528262</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.6948785444863583</v>
+        <v>0.7036974110277008</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.4994321274745528</v>
+        <v>0.5035243929724618</v>
       </c>
       <c r="BD11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BE11" t="n">
         <v>2625</v>
@@ -3372,166 +3372,166 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.850863370446023</v>
+        <v>0.8486119692410194</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8214994447237463</v>
+        <v>0.8224757533433978</v>
       </c>
       <c r="E12" t="n">
-        <v>95.48064826858685</v>
+        <v>95.33349282940951</v>
       </c>
       <c r="F12" t="n">
-        <v>95.00819810470979</v>
+        <v>94.8908382387215</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4724501638770835</v>
+        <v>0.4426545906880287</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2763295913549361</v>
+        <v>0.2795904190378659</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6811885873509614</v>
+        <v>0.6863655445176248</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4921597848786214</v>
+        <v>0.4960995852523127</v>
       </c>
       <c r="K12" t="n">
-        <v>5050</v>
+        <v>5250</v>
       </c>
       <c r="L12" t="n">
-        <v>1909</v>
+        <v>1985</v>
       </c>
       <c r="M12" t="n">
-        <v>454</v>
+        <v>473</v>
       </c>
       <c r="N12" t="n">
-        <v>933</v>
+        <v>970</v>
       </c>
       <c r="O12" t="n">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="P12" t="n">
-        <v>635</v>
+        <v>668</v>
       </c>
       <c r="Q12" t="n">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="R12" t="n">
-        <v>664</v>
+        <v>682</v>
       </c>
       <c r="S12" t="n">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="T12" t="n">
-        <v>676</v>
+        <v>707</v>
       </c>
       <c r="U12" t="n">
-        <v>409</v>
+        <v>426</v>
       </c>
       <c r="V12" t="n">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="W12" t="n">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="X12" t="n">
-        <v>511</v>
+        <v>532</v>
       </c>
       <c r="Y12" t="n">
-        <v>553</v>
+        <v>575</v>
       </c>
       <c r="Z12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA12" t="n">
-        <v>1904</v>
+        <v>1979</v>
       </c>
       <c r="AB12" t="n">
-        <v>2252.16</v>
+        <v>2348.08</v>
       </c>
       <c r="AC12" t="n">
-        <v>2001.16</v>
+        <v>2084.08</v>
       </c>
       <c r="AD12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE12" t="n">
-        <v>2425</v>
+        <v>2625</v>
       </c>
       <c r="AF12" t="n">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="AG12" t="n">
-        <v>438</v>
+        <v>475</v>
       </c>
       <c r="AH12" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="AI12" t="n">
-        <v>297</v>
+        <v>330</v>
       </c>
       <c r="AJ12" t="n">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="AK12" t="n">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="AL12" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="AM12" t="n">
-        <v>324</v>
+        <v>355</v>
       </c>
       <c r="AN12" t="n">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="AO12" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="AP12" t="n">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="AQ12" t="n">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="AR12" t="n">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="AS12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AT12" t="n">
-        <v>1075.68</v>
+        <v>1171.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>954.6799999999999</v>
+        <v>1037.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.8160613960742603</v>
+        <v>0.8142356686159271</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.8224792995606204</v>
+        <v>0.8243565433509333</v>
       </c>
       <c r="AX12" t="n">
-        <v>91.48743469065387</v>
+        <v>91.50029408752479</v>
       </c>
       <c r="AY12" t="n">
-        <v>95.3525632476384</v>
+        <v>95.0913538892827</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-3.865128556984502</v>
+        <v>-3.591059801757874</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.2581560254310034</v>
+        <v>0.2660756474063963</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.6820901998943221</v>
+        <v>0.6923747594166212</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.4793290226874696</v>
+        <v>0.4881956051418638</v>
       </c>
       <c r="BD12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BE12" t="n">
         <v>2625</v>
@@ -3624,166 +3624,166 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.7641125126242505</v>
+        <v>0.7571515140951827</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8207841584229345</v>
+        <v>0.8205752961021791</v>
       </c>
       <c r="E13" t="n">
-        <v>87.07987940095173</v>
+        <v>86.32791233292218</v>
       </c>
       <c r="F13" t="n">
-        <v>93.70414135175264</v>
+        <v>93.68590757320759</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.624261950800917</v>
+        <v>-7.357995240285392</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3067895466387587</v>
+        <v>0.3061235519299806</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7172319146432424</v>
+        <v>0.718245677295031</v>
       </c>
       <c r="J13" t="n">
-        <v>0.524321747233812</v>
+        <v>0.5241355461663776</v>
       </c>
       <c r="K13" t="n">
-        <v>5025</v>
+        <v>5225</v>
       </c>
       <c r="L13" t="n">
-        <v>1723</v>
+        <v>1770</v>
       </c>
       <c r="M13" t="n">
-        <v>462</v>
+        <v>477</v>
       </c>
       <c r="N13" t="n">
-        <v>1007</v>
+        <v>1043</v>
       </c>
       <c r="O13" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="P13" t="n">
-        <v>537</v>
+        <v>558</v>
       </c>
       <c r="Q13" t="n">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="R13" t="n">
-        <v>625</v>
+        <v>640</v>
       </c>
       <c r="S13" t="n">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="T13" t="n">
-        <v>733</v>
+        <v>762</v>
       </c>
       <c r="U13" t="n">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="V13" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="W13" t="n">
-        <v>429</v>
+        <v>446</v>
       </c>
       <c r="X13" t="n">
-        <v>544</v>
+        <v>559</v>
       </c>
       <c r="Y13" t="n">
-        <v>567</v>
+        <v>585</v>
       </c>
       <c r="Z13" t="n">
         <v>57</v>
       </c>
       <c r="AA13" t="n">
-        <v>1885</v>
+        <v>1950</v>
       </c>
       <c r="AB13" t="n">
-        <v>2248</v>
+        <v>2328.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>1972</v>
+        <v>2041.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE13" t="n">
-        <v>2425</v>
+        <v>2625</v>
       </c>
       <c r="AF13" t="n">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="AG13" t="n">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="AH13" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="AI13" t="n">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="AJ13" t="n">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="AK13" t="n">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="AL13" t="n">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="AM13" t="n">
-        <v>326</v>
+        <v>355</v>
       </c>
       <c r="AN13" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="AO13" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="AP13" t="n">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="AQ13" t="n">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="AR13" t="n">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AS13" t="n">
         <v>38</v>
       </c>
       <c r="AT13" t="n">
-        <v>1085.56</v>
+        <v>1166.16</v>
       </c>
       <c r="AU13" t="n">
-        <v>958.5600000000001</v>
+        <v>1028.16</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.7653611366322367</v>
+        <v>0.7513430915734868</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.8817266943656207</v>
+        <v>0.8766210823439031</v>
       </c>
       <c r="AX13" t="n">
-        <v>86.6650330642846</v>
+        <v>85.19301018489224</v>
       </c>
       <c r="AY13" t="n">
-        <v>100.5756422931646</v>
+        <v>100.0105977405813</v>
       </c>
       <c r="AZ13" t="n">
-        <v>-13.91060922887999</v>
+        <v>-14.81758755568901</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.2904720823118913</v>
+        <v>0.2903952824579402</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.6977255755354709</v>
+        <v>0.7012535884627226</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.4976752902317338</v>
+        <v>0.4993526155585635</v>
       </c>
       <c r="BD13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BE13" t="n">
         <v>2600</v>
@@ -3876,88 +3876,88 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.8829394377296625</v>
+        <v>0.8789902860108645</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7876164090049853</v>
+        <v>0.7882243306054743</v>
       </c>
       <c r="E14" t="n">
-        <v>101.739007646554</v>
+        <v>101.5299692112633</v>
       </c>
       <c r="F14" t="n">
-        <v>88.1488661239662</v>
+        <v>88.56317370801952</v>
       </c>
       <c r="G14" t="n">
-        <v>13.59014152258786</v>
+        <v>12.96679550324382</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3377284668019019</v>
+        <v>0.3380525198538998</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7309581102141125</v>
+        <v>0.724822358722361</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5298848945094531</v>
+        <v>0.5266896489759472</v>
       </c>
       <c r="K14" t="n">
-        <v>5000</v>
+        <v>5200</v>
       </c>
       <c r="L14" t="n">
-        <v>1999</v>
+        <v>2073</v>
       </c>
       <c r="M14" t="n">
-        <v>477</v>
+        <v>497</v>
       </c>
       <c r="N14" t="n">
-        <v>990</v>
+        <v>1035</v>
       </c>
       <c r="O14" t="n">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="P14" t="n">
-        <v>603</v>
+        <v>645</v>
       </c>
       <c r="Q14" t="n">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="R14" t="n">
-        <v>693</v>
+        <v>704</v>
       </c>
       <c r="S14" t="n">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="T14" t="n">
-        <v>618</v>
+        <v>642</v>
       </c>
       <c r="U14" t="n">
-        <v>385</v>
+        <v>402</v>
       </c>
       <c r="V14" t="n">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="W14" t="n">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="X14" t="n">
-        <v>541</v>
+        <v>566</v>
       </c>
       <c r="Y14" t="n">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="Z14" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AA14" t="n">
-        <v>1719</v>
+        <v>1796</v>
       </c>
       <c r="AB14" t="n">
-        <v>2272.92</v>
+        <v>2367.76</v>
       </c>
       <c r="AC14" t="n">
-        <v>1966.92</v>
+        <v>2043.76</v>
       </c>
       <c r="AD14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE14" t="n">
         <v>2600</v>
@@ -4038,82 +4038,82 @@
         <v>13</v>
       </c>
       <c r="BE14" t="n">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="BF14" t="n">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="BG14" t="n">
-        <v>491</v>
+        <v>536</v>
       </c>
       <c r="BH14" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="BI14" t="n">
-        <v>291</v>
+        <v>333</v>
       </c>
       <c r="BJ14" t="n">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="BK14" t="n">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="BL14" t="n">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="BM14" t="n">
-        <v>316</v>
+        <v>340</v>
       </c>
       <c r="BN14" t="n">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="BO14" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="BP14" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="BQ14" t="n">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="BR14" t="n">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="BS14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BT14" t="n">
-        <v>1099.84</v>
+        <v>1194.68</v>
       </c>
       <c r="BU14" t="n">
-        <v>944.84</v>
+        <v>1021.68</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.9103021577665901</v>
+        <v>0.9002990297107686</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.7805040299906394</v>
+        <v>0.7822669792696437</v>
       </c>
       <c r="BX14" t="n">
-        <v>105.2222346043068</v>
+        <v>104.5362171985136</v>
       </c>
       <c r="BY14" t="n">
-        <v>86.62306058252437</v>
+        <v>87.56904540766499</v>
       </c>
       <c r="BZ14" t="n">
-        <v>18.5991740217824</v>
+        <v>16.96717179084859</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.3510521540078428</v>
+        <v>0.3506753610959969</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.7615915102440985</v>
+        <v>0.7469635918736733</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.5556043335089983</v>
+        <v>0.547235424057406</v>
       </c>
       <c r="CD14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -4128,166 +4128,166 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.8698868530068125</v>
+        <v>0.8765593402794322</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8221700215668472</v>
+        <v>0.823985821937849</v>
       </c>
       <c r="E15" t="n">
-        <v>99.03280455761467</v>
+        <v>99.90756223993695</v>
       </c>
       <c r="F15" t="n">
-        <v>93.13410948002891</v>
+        <v>93.08298015299553</v>
       </c>
       <c r="G15" t="n">
-        <v>5.898695077585753</v>
+        <v>6.824582086941435</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3258319132498672</v>
+        <v>0.3282571815436758</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7112595036619613</v>
+        <v>0.7163552919826551</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5210402834919265</v>
+        <v>0.5241903178372597</v>
       </c>
       <c r="K15" t="n">
-        <v>5025</v>
+        <v>5225</v>
       </c>
       <c r="L15" t="n">
-        <v>2151</v>
+        <v>2253</v>
       </c>
       <c r="M15" t="n">
-        <v>570</v>
+        <v>593</v>
       </c>
       <c r="N15" t="n">
-        <v>1123</v>
+        <v>1161</v>
       </c>
       <c r="O15" t="n">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="P15" t="n">
-        <v>643</v>
+        <v>673</v>
       </c>
       <c r="Q15" t="n">
-        <v>447</v>
+        <v>470</v>
       </c>
       <c r="R15" t="n">
-        <v>637</v>
+        <v>666</v>
       </c>
       <c r="S15" t="n">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="T15" t="n">
-        <v>694</v>
+        <v>721</v>
       </c>
       <c r="U15" t="n">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="V15" t="n">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="W15" t="n">
-        <v>438</v>
+        <v>455</v>
       </c>
       <c r="X15" t="n">
-        <v>548</v>
+        <v>574</v>
       </c>
       <c r="Y15" t="n">
-        <v>566</v>
+        <v>594</v>
       </c>
       <c r="Z15" t="n">
         <v>83</v>
       </c>
       <c r="AA15" t="n">
-        <v>1994</v>
+        <v>2076</v>
       </c>
       <c r="AB15" t="n">
-        <v>2484.28</v>
+        <v>2582.04</v>
       </c>
       <c r="AC15" t="n">
-        <v>2177.28</v>
+        <v>2261.04</v>
       </c>
       <c r="AD15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE15" t="n">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="AF15" t="n">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="AG15" t="n">
-        <v>521</v>
+        <v>559</v>
       </c>
       <c r="AH15" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="AI15" t="n">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="AJ15" t="n">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="AK15" t="n">
-        <v>313</v>
+        <v>342</v>
       </c>
       <c r="AL15" t="n">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="AM15" t="n">
-        <v>331</v>
+        <v>358</v>
       </c>
       <c r="AN15" t="n">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="AO15" t="n">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="AP15" t="n">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="AQ15" t="n">
-        <v>267</v>
+        <v>293</v>
       </c>
       <c r="AR15" t="n">
-        <v>273</v>
+        <v>301</v>
       </c>
       <c r="AS15" t="n">
         <v>47</v>
       </c>
       <c r="AT15" t="n">
-        <v>1168.72</v>
+        <v>1266.48</v>
       </c>
       <c r="AU15" t="n">
-        <v>1029.72</v>
+        <v>1113.48</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.842688710602327</v>
+        <v>0.8581258499479115</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.8499182626795033</v>
+        <v>0.8514153833359178</v>
       </c>
       <c r="AX15" t="n">
-        <v>95.64195163994198</v>
+        <v>97.65230184440755</v>
       </c>
       <c r="AY15" t="n">
-        <v>94.839210890144</v>
+        <v>94.60579058914529</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.8027407497979802</v>
+        <v>3.046511255262251</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.3063418611436905</v>
+        <v>0.3126916325087058</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.737161643297314</v>
+        <v>0.7453607476590591</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.5196584041509079</v>
+        <v>0.5260647712524217</v>
       </c>
       <c r="BD15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BE15" t="n">
         <v>2625</v>

--- a/data/3FEB_25_26/teams_25_26_3FEB.xlsx
+++ b/data/3FEB_25_26/teams_25_26_3FEB.xlsx
@@ -852,244 +852,244 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.8001833169490543</v>
+        <v>0.7928294889524842</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8953743731225363</v>
+        <v>0.8986599544797419</v>
       </c>
       <c r="E2" t="n">
-        <v>88.20076215048373</v>
+        <v>87.60007049650642</v>
       </c>
       <c r="F2" t="n">
-        <v>102.9383994952986</v>
+        <v>103.77011001493</v>
       </c>
       <c r="G2" t="n">
-        <v>-14.73763734481487</v>
+        <v>-16.1700395184236</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2247772017729559</v>
+        <v>0.2296314275164409</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6517377843894578</v>
+        <v>0.6406535135261598</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4326921930352894</v>
+        <v>0.4298006004259114</v>
       </c>
       <c r="K2" t="n">
-        <v>5375</v>
+        <v>4975</v>
       </c>
       <c r="L2" t="n">
-        <v>1932</v>
+        <v>1773</v>
       </c>
       <c r="M2" t="n">
-        <v>507</v>
+        <v>468</v>
       </c>
       <c r="N2" t="n">
-        <v>1082</v>
+        <v>1011</v>
       </c>
       <c r="O2" t="n">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="P2" t="n">
-        <v>633</v>
+        <v>579</v>
       </c>
       <c r="Q2" t="n">
-        <v>405</v>
+        <v>369</v>
       </c>
       <c r="R2" t="n">
-        <v>624</v>
+        <v>567</v>
       </c>
       <c r="S2" t="n">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="T2" t="n">
-        <v>616</v>
+        <v>565</v>
       </c>
       <c r="U2" t="n">
-        <v>347</v>
+        <v>312</v>
       </c>
       <c r="V2" t="n">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="W2" t="n">
-        <v>433</v>
+        <v>404</v>
       </c>
       <c r="X2" t="n">
-        <v>620</v>
+        <v>571</v>
       </c>
       <c r="Y2" t="n">
-        <v>549</v>
+        <v>501</v>
       </c>
       <c r="Z2" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="AA2" t="n">
-        <v>2267</v>
+        <v>2115</v>
       </c>
       <c r="AB2" t="n">
-        <v>2422.56</v>
+        <v>2243.48</v>
       </c>
       <c r="AC2" t="n">
-        <v>2189.56</v>
+        <v>2022.48</v>
       </c>
       <c r="AD2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE2" t="n">
-        <v>2675</v>
+        <v>2475</v>
       </c>
       <c r="AF2" t="n">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="AG2" t="n">
-        <v>558</v>
+        <v>522</v>
       </c>
       <c r="AH2" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AI2" t="n">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="AJ2" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AK2" t="n">
-        <v>333</v>
+        <v>300</v>
       </c>
       <c r="AL2" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="AM2" t="n">
-        <v>306</v>
+        <v>277</v>
       </c>
       <c r="AN2" t="n">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="AO2" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="AP2" t="n">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="AQ2" t="n">
-        <v>310</v>
+        <v>287</v>
       </c>
       <c r="AR2" t="n">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="AS2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT2" t="n">
-        <v>1201.52</v>
+        <v>1110</v>
       </c>
       <c r="AU2" t="n">
-        <v>1093.52</v>
+        <v>1006</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.8294186435504246</v>
+        <v>0.8266035887880183</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.9371677145330783</v>
+        <v>0.9404365819691645</v>
       </c>
       <c r="AX2" t="n">
-        <v>90.86260620212694</v>
+        <v>90.91239986339498</v>
       </c>
       <c r="AY2" t="n">
-        <v>108.1422381687244</v>
+        <v>108.9527791394979</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-17.27963196659747</v>
+        <v>-18.04037927610286</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.2078604218701013</v>
+        <v>0.2136878708190465</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.6442877458466462</v>
+        <v>0.6326630760185513</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.4244543158467804</v>
+        <v>0.4181588421673454</v>
       </c>
       <c r="BD2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BE2" t="n">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="BF2" t="n">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="BG2" t="n">
-        <v>524</v>
+        <v>489</v>
       </c>
       <c r="BH2" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="BI2" t="n">
-        <v>336</v>
+        <v>302</v>
       </c>
       <c r="BJ2" t="n">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="BK2" t="n">
-        <v>291</v>
+        <v>267</v>
       </c>
       <c r="BL2" t="n">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="BM2" t="n">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="BN2" t="n">
-        <v>189</v>
+        <v>168</v>
       </c>
       <c r="BO2" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="BP2" t="n">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="BQ2" t="n">
-        <v>310</v>
+        <v>284</v>
       </c>
       <c r="BR2" t="n">
-        <v>271</v>
+        <v>246</v>
       </c>
       <c r="BS2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BT2" t="n">
-        <v>1221.04</v>
+        <v>1133.48</v>
       </c>
       <c r="BU2" t="n">
-        <v>1096.04</v>
+        <v>1016.48</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.7709479903476841</v>
+        <v>0.7590553891169501</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.8535810317119943</v>
+        <v>0.8568833269903194</v>
       </c>
       <c r="BX2" t="n">
-        <v>85.53891809884051</v>
+        <v>84.28774112961786</v>
       </c>
       <c r="BY2" t="n">
-        <v>97.7345608218728</v>
+        <v>98.5874408903622</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-12.19564272303228</v>
+        <v>-14.29969976074433</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.2416939816758107</v>
+        <v>0.2455749842138355</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.65918782293227</v>
+        <v>0.6486439510337686</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.4409300702237984</v>
+        <v>0.4414423586844773</v>
       </c>
       <c r="CD2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -1104,244 +1104,244 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7723078428252476</v>
+        <v>0.7761132237011646</v>
       </c>
       <c r="D3" t="n">
-        <v>0.883110518157143</v>
+        <v>0.8752694388958985</v>
       </c>
       <c r="E3" t="n">
-        <v>87.77210813310401</v>
+        <v>88.2741821754877</v>
       </c>
       <c r="F3" t="n">
-        <v>100.6535761402495</v>
+        <v>100.1415291687097</v>
       </c>
       <c r="G3" t="n">
-        <v>-12.88146800714543</v>
+        <v>-11.86734699322201</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2832405978473672</v>
+        <v>0.2860106476679811</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6939619181235611</v>
+        <v>0.6890651353382878</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4844984572690079</v>
+        <v>0.4863054415990148</v>
       </c>
       <c r="K3" t="n">
-        <v>5300</v>
+        <v>4900</v>
       </c>
       <c r="L3" t="n">
-        <v>1888</v>
+        <v>1756</v>
       </c>
       <c r="M3" t="n">
-        <v>505</v>
+        <v>473</v>
       </c>
       <c r="N3" t="n">
-        <v>1111</v>
+        <v>1030</v>
       </c>
       <c r="O3" t="n">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="P3" t="n">
-        <v>611</v>
+        <v>555</v>
       </c>
       <c r="Q3" t="n">
-        <v>422</v>
+        <v>396</v>
       </c>
       <c r="R3" t="n">
-        <v>659</v>
+        <v>620</v>
       </c>
       <c r="S3" t="n">
-        <v>294</v>
+        <v>273</v>
       </c>
       <c r="T3" t="n">
-        <v>696</v>
+        <v>650</v>
       </c>
       <c r="U3" t="n">
-        <v>313</v>
+        <v>287</v>
       </c>
       <c r="V3" t="n">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="W3" t="n">
-        <v>429</v>
+        <v>400</v>
       </c>
       <c r="X3" t="n">
-        <v>591</v>
+        <v>556</v>
       </c>
       <c r="Y3" t="n">
-        <v>583</v>
+        <v>545</v>
       </c>
       <c r="Z3" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AA3" t="n">
-        <v>2177</v>
+        <v>2005</v>
       </c>
       <c r="AB3" t="n">
-        <v>2440.96</v>
+        <v>2257.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>2146.96</v>
+        <v>1984.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE3" t="n">
-        <v>2625</v>
+        <v>2425</v>
       </c>
       <c r="AF3" t="n">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="AG3" t="n">
-        <v>559</v>
+        <v>520</v>
       </c>
       <c r="AH3" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="AI3" t="n">
-        <v>303</v>
+        <v>278</v>
       </c>
       <c r="AJ3" t="n">
+        <v>191</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>291</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>141</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>298</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>119</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>88</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>195</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>269</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>262</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1121.04</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>980.04</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.7447167418509636</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.9173596606819795</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>85.18072152433017</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>105.3200257751431</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-20.1393042508129</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0.2893831029863625</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0.664883229227427</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0.4699609216836479</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>2475</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>248</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>510</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>74</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>277</v>
+      </c>
+      <c r="BJ3" t="n">
         <v>205</v>
       </c>
-      <c r="AK3" t="n">
-        <v>314</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>154</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>318</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>129</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>94</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>218</v>
-      </c>
-      <c r="AQ3" t="n">
+      <c r="BK3" t="n">
+        <v>329</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>132</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>352</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>168</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>89</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>205</v>
+      </c>
+      <c r="BQ3" t="n">
         <v>287</v>
       </c>
-      <c r="AR3" t="n">
-        <v>280</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1218.16</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1064.16</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0.7357453741784841</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0.9259074569878447</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>84.20647018501028</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>105.8095506229975</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>-21.60308043798723</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0.2909323881046276</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0.6707184224207589</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0.4705993792129994</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>2675</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>267</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>552</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>81</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>308</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>217</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>345</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>140</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>378</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>184</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>95</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>211</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>304</v>
-      </c>
       <c r="BR3" t="n">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="BS3" t="n">
         <v>23</v>
       </c>
       <c r="BT3" t="n">
-        <v>1222.8</v>
+        <v>1136.76</v>
       </c>
       <c r="BU3" t="n">
-        <v>1082.8</v>
+        <v>1004.76</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.808870311472011</v>
+        <v>0.8075097055513655</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.8403135793264409</v>
+        <v>0.8331792171098171</v>
       </c>
       <c r="BX3" t="n">
-        <v>91.33774608119776</v>
+        <v>91.36764282664525</v>
       </c>
       <c r="BY3" t="n">
-        <v>95.49760165750136</v>
+        <v>94.96303256227638</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-4.159855576303626</v>
+        <v>-3.595389735631134</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.2755488075901065</v>
+        <v>0.2826381923495995</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.7172054138263635</v>
+        <v>0.7132470414491486</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.4983975353250163</v>
+        <v>0.5026499615143817</v>
       </c>
       <c r="CD3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -1356,244 +1356,244 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8503861259577228</v>
+        <v>0.8552340941452962</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8756891343622798</v>
+        <v>0.8565393372336615</v>
       </c>
       <c r="E4" t="n">
-        <v>96.42768440340714</v>
+        <v>96.45266167279361</v>
       </c>
       <c r="F4" t="n">
-        <v>98.58153994949302</v>
+        <v>96.18436661761011</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.153855546085888</v>
+        <v>0.2682950551834975</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2960061101006743</v>
+        <v>0.2861350388654794</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7194365008385494</v>
+        <v>0.7238938050439468</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5070028612992488</v>
+        <v>0.50535037336184</v>
       </c>
       <c r="K4" t="n">
-        <v>5200</v>
+        <v>4600</v>
       </c>
       <c r="L4" t="n">
-        <v>2002</v>
+        <v>1766</v>
       </c>
       <c r="M4" t="n">
-        <v>456</v>
+        <v>396</v>
       </c>
       <c r="N4" t="n">
-        <v>962</v>
+        <v>837</v>
       </c>
       <c r="O4" t="n">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="P4" t="n">
-        <v>694</v>
+        <v>611</v>
       </c>
       <c r="Q4" t="n">
-        <v>442</v>
+        <v>398</v>
       </c>
       <c r="R4" t="n">
-        <v>655</v>
+        <v>580</v>
       </c>
       <c r="S4" t="n">
-        <v>280</v>
+        <v>235</v>
       </c>
       <c r="T4" t="n">
-        <v>662</v>
+        <v>588</v>
       </c>
       <c r="U4" t="n">
-        <v>365</v>
+        <v>320</v>
       </c>
       <c r="V4" t="n">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="W4" t="n">
-        <v>411</v>
+        <v>362</v>
       </c>
       <c r="X4" t="n">
-        <v>639</v>
+        <v>573</v>
       </c>
       <c r="Y4" t="n">
-        <v>593</v>
+        <v>529</v>
       </c>
       <c r="Z4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA4" t="n">
-        <v>2032</v>
+        <v>1752</v>
       </c>
       <c r="AB4" t="n">
-        <v>2355.2</v>
+        <v>2065.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>2075.2</v>
+        <v>1830.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE4" t="n">
-        <v>2600</v>
+        <v>2200</v>
       </c>
       <c r="AF4" t="n">
-        <v>232</v>
+        <v>194</v>
       </c>
       <c r="AG4" t="n">
-        <v>489</v>
+        <v>404</v>
       </c>
       <c r="AH4" t="n">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AI4" t="n">
-        <v>343</v>
+        <v>288</v>
       </c>
       <c r="AJ4" t="n">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="AK4" t="n">
-        <v>304</v>
+        <v>265</v>
       </c>
       <c r="AL4" t="n">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="AM4" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="AN4" t="n">
-        <v>173</v>
+        <v>140</v>
       </c>
       <c r="AO4" t="n">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="AP4" t="n">
+        <v>165</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>276</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>250</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>973.6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>876.6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.8112845099956398</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.8427723790680651</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>90.0643309952619</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>94.94027726900917</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-4.875946273747268</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.2579706936183871</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0.7094003932538758</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0.4840333923164064</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>2400</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>202</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>433</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>115</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>323</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>228</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>315</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>138</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>313</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>180</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>93</v>
+      </c>
+      <c r="BP4" t="n">
         <v>197</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>321</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>288</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1162.76</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1034.76</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.8085345033377256</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.8701045934620747</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>90.79873177993005</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>98.1206837400087</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>-7.321951960078656</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0.2741416699711442</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0.7085036294565762</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0.4894488597487033</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>2600</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>224</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>473</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>122</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>351</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>249</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>351</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>152</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>337</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>192</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>96</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>214</v>
-      </c>
       <c r="BQ4" t="n">
-        <v>318</v>
+        <v>297</v>
       </c>
       <c r="BR4" t="n">
-        <v>305</v>
+        <v>279</v>
       </c>
       <c r="BS4" t="n">
         <v>15</v>
       </c>
       <c r="BT4" t="n">
-        <v>1192.44</v>
+        <v>1091.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>1040.44</v>
+        <v>953.6</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.89223774857772</v>
+        <v>0.8955212129491478</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.881273675262485</v>
+        <v>0.8691590488854583</v>
       </c>
       <c r="BX4" t="n">
-        <v>102.0566370268842</v>
+        <v>102.308631460531</v>
       </c>
       <c r="BY4" t="n">
-        <v>99.04239615897737</v>
+        <v>97.32478185382764</v>
       </c>
       <c r="BZ4" t="n">
-        <v>3.014240867906881</v>
+        <v>4.983849606703366</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.3178705502302044</v>
+        <v>0.3119523553419807</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.7303693722205222</v>
+        <v>0.7371794325181783</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.5245568628497945</v>
+        <v>0.5248909393201541</v>
       </c>
       <c r="CD4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -1608,244 +1608,244 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8093353406194697</v>
+        <v>0.8013209404971456</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8609966653626249</v>
+        <v>0.8463740428219602</v>
       </c>
       <c r="E5" t="n">
-        <v>90.11644051259223</v>
+        <v>89.34702561525641</v>
       </c>
       <c r="F5" t="n">
-        <v>98.64533892791329</v>
+        <v>96.99888919837541</v>
       </c>
       <c r="G5" t="n">
-        <v>-8.528898415321011</v>
+        <v>-7.65186358311898</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2457822514283938</v>
+        <v>0.2478142502256003</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6928036337642655</v>
+        <v>0.6938323219520928</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4711222917457827</v>
+        <v>0.4727511565272252</v>
       </c>
       <c r="K5" t="n">
-        <v>5200</v>
+        <v>4400</v>
       </c>
       <c r="L5" t="n">
-        <v>1853</v>
+        <v>1539</v>
       </c>
       <c r="M5" t="n">
-        <v>497</v>
+        <v>413</v>
       </c>
       <c r="N5" t="n">
-        <v>1024</v>
+        <v>864</v>
       </c>
       <c r="O5" t="n">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="P5" t="n">
-        <v>642</v>
+        <v>545</v>
       </c>
       <c r="Q5" t="n">
-        <v>358</v>
+        <v>281</v>
       </c>
       <c r="R5" t="n">
-        <v>571</v>
+        <v>461</v>
       </c>
       <c r="S5" t="n">
-        <v>234</v>
+        <v>199</v>
       </c>
       <c r="T5" t="n">
-        <v>670</v>
+        <v>568</v>
       </c>
       <c r="U5" t="n">
-        <v>348</v>
+        <v>293</v>
       </c>
       <c r="V5" t="n">
-        <v>215</v>
+        <v>186</v>
       </c>
       <c r="W5" t="n">
-        <v>380</v>
+        <v>317</v>
       </c>
       <c r="X5" t="n">
-        <v>581</v>
+        <v>487</v>
       </c>
       <c r="Y5" t="n">
-        <v>511</v>
+        <v>420</v>
       </c>
       <c r="Z5" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="AA5" t="n">
-        <v>2006</v>
+        <v>1662</v>
       </c>
       <c r="AB5" t="n">
-        <v>2297.24</v>
+        <v>1928.84</v>
       </c>
       <c r="AC5" t="n">
-        <v>2063.24</v>
+        <v>1729.84</v>
       </c>
       <c r="AD5" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE5" t="n">
-        <v>2600</v>
+        <v>2400</v>
       </c>
       <c r="AF5" t="n">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="AG5" t="n">
-        <v>509</v>
+        <v>465</v>
       </c>
       <c r="AH5" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="AI5" t="n">
-        <v>330</v>
+        <v>306</v>
       </c>
       <c r="AJ5" t="n">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="AK5" t="n">
-        <v>287</v>
+        <v>261</v>
       </c>
       <c r="AL5" t="n">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="AM5" t="n">
-        <v>344</v>
+        <v>318</v>
       </c>
       <c r="AN5" t="n">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="AO5" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="AP5" t="n">
+        <v>173</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>261</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>231</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1058.84</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>953.84</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.7609639197224817</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.8300582054482447</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>84.47980423604744</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>94.89754631805302</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-10.4177420820056</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0.2248932579416265</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0.7055990021296555</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.4646934272215936</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>195</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>399</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>72</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>239</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>129</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>200</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>94</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>250</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>143</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>78</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>144</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>226</v>
+      </c>
+      <c r="BR5" t="n">
         <v>189</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>281</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>254</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1154.28</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1038.28</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.7620710216485297</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.8321324520577057</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>84.72260324700484</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>95.22677752495207</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-10.50417427794725</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0.2277402967080216</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0.702604207094041</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0.4640854807781472</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>2600</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>256</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>515</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>91</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>312</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>190</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>284</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>118</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>326</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>186</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>98</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>191</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>300</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>257</v>
-      </c>
       <c r="BS5" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="BT5" t="n">
-        <v>1142.96</v>
+        <v>870</v>
       </c>
       <c r="BU5" t="n">
-        <v>1024.96</v>
+        <v>776</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.8565996595904095</v>
+        <v>0.8497493654267423</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.889860878667544</v>
+        <v>0.8659530476704186</v>
       </c>
       <c r="BX5" t="n">
-        <v>95.51027777817964</v>
+        <v>95.18769127030717</v>
       </c>
       <c r="BY5" t="n">
-        <v>102.0639003308744</v>
+        <v>99.52050065476222</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-6.553622552694771</v>
+        <v>-4.332809384455037</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.2638242061487661</v>
+        <v>0.2753194409663689</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.6830030604344899</v>
+        <v>0.6797123057390178</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.4781591027134184</v>
+        <v>0.4824204316939832</v>
       </c>
       <c r="CD5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -1860,244 +1860,244 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8781230070652373</v>
+        <v>0.8789396993117592</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8507794575981837</v>
+        <v>0.8523930884133065</v>
       </c>
       <c r="E6" t="n">
-        <v>100.6431725145976</v>
+        <v>101.0512653000211</v>
       </c>
       <c r="F6" t="n">
-        <v>96.82006944313625</v>
+        <v>96.93093791543052</v>
       </c>
       <c r="G6" t="n">
-        <v>3.823103071461313</v>
+        <v>4.12032738459059</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3044820546954171</v>
+        <v>0.3117755413645598</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6947024297705829</v>
+        <v>0.6911677743245737</v>
       </c>
       <c r="J6" t="n">
-        <v>0.498010127877481</v>
+        <v>0.4973924544778555</v>
       </c>
       <c r="K6" t="n">
-        <v>5225</v>
+        <v>4625</v>
       </c>
       <c r="L6" t="n">
-        <v>2023</v>
+        <v>1796</v>
       </c>
       <c r="M6" t="n">
-        <v>447</v>
+        <v>398</v>
       </c>
       <c r="N6" t="n">
-        <v>928</v>
+        <v>838</v>
       </c>
       <c r="O6" t="n">
-        <v>222</v>
+        <v>195</v>
       </c>
       <c r="P6" t="n">
-        <v>727</v>
+        <v>640</v>
       </c>
       <c r="Q6" t="n">
-        <v>463</v>
+        <v>415</v>
       </c>
       <c r="R6" t="n">
-        <v>651</v>
+        <v>576</v>
       </c>
       <c r="S6" t="n">
-        <v>296</v>
+        <v>269</v>
       </c>
       <c r="T6" t="n">
-        <v>648</v>
+        <v>562</v>
       </c>
       <c r="U6" t="n">
-        <v>342</v>
+        <v>306</v>
       </c>
       <c r="V6" t="n">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="W6" t="n">
-        <v>366</v>
+        <v>317</v>
       </c>
       <c r="X6" t="n">
-        <v>546</v>
+        <v>475</v>
       </c>
       <c r="Y6" t="n">
-        <v>580</v>
+        <v>513</v>
       </c>
       <c r="Z6" t="n">
+        <v>77</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1762</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2048.44</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1779.44</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2225</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>193</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>402</v>
+      </c>
+      <c r="AH6" t="n">
         <v>88</v>
       </c>
-      <c r="AA6" t="n">
-        <v>1984</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2307.44</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2011.44</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2625</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>228</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>464</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>104</v>
-      </c>
       <c r="AI6" t="n">
-        <v>359</v>
+        <v>306</v>
       </c>
       <c r="AJ6" t="n">
-        <v>256</v>
+        <v>212</v>
       </c>
       <c r="AK6" t="n">
-        <v>348</v>
+        <v>286</v>
       </c>
       <c r="AL6" t="n">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="AM6" t="n">
-        <v>306</v>
+        <v>247</v>
       </c>
       <c r="AN6" t="n">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="AO6" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="AP6" t="n">
-        <v>198</v>
+        <v>161</v>
       </c>
       <c r="AQ6" t="n">
-        <v>293</v>
+        <v>240</v>
       </c>
       <c r="AR6" t="n">
-        <v>303</v>
+        <v>251</v>
       </c>
       <c r="AS6" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AT6" t="n">
-        <v>1174.12</v>
+        <v>994.84</v>
       </c>
       <c r="AU6" t="n">
-        <v>1033.12</v>
+        <v>870.84</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.8735283125938645</v>
+        <v>0.86869424566162</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.910314888971382</v>
+        <v>0.9001813857681568</v>
       </c>
       <c r="AX6" t="n">
-        <v>99.28110423337732</v>
+        <v>99.21282133313046</v>
       </c>
       <c r="AY6" t="n">
-        <v>104.3378798939808</v>
+        <v>103.2737218897539</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-5.056775660603435</v>
+        <v>-4.060900556623451</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.2935035793095058</v>
+        <v>0.3023873469761691</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.6665060997077827</v>
+        <v>0.6554273861291534</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.4779751035819058</v>
+        <v>0.4714508141145842</v>
       </c>
       <c r="BD6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BE6" t="n">
-        <v>2600</v>
+        <v>2400</v>
       </c>
       <c r="BF6" t="n">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="BG6" t="n">
-        <v>464</v>
+        <v>436</v>
       </c>
       <c r="BH6" t="n">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="BI6" t="n">
-        <v>368</v>
+        <v>334</v>
       </c>
       <c r="BJ6" t="n">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="BK6" t="n">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="BL6" t="n">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="BM6" t="n">
-        <v>342</v>
+        <v>315</v>
       </c>
       <c r="BN6" t="n">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="BO6" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="BP6" t="n">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="BQ6" t="n">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="BR6" t="n">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="BS6" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="BT6" t="n">
-        <v>1133.32</v>
+        <v>1053.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>978.3199999999999</v>
+        <v>908.6</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.8827177015366101</v>
+        <v>0.8883313651577199</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.791244026224985</v>
+        <v>0.8085871491713599</v>
       </c>
       <c r="BX6" t="n">
-        <v>102.0052407958178</v>
+        <v>102.7365056030042</v>
       </c>
       <c r="BY6" t="n">
-        <v>89.30225899229175</v>
+        <v>91.11671927230073</v>
       </c>
       <c r="BZ6" t="n">
-        <v>12.70298180352606</v>
+        <v>11.61978633070346</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.3154605300813285</v>
+        <v>0.3203813862205845</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.7228987598333834</v>
+        <v>0.7239297968370425</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.518045152173056</v>
+        <v>0.5211722914775206</v>
       </c>
       <c r="CD6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -2112,244 +2112,244 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.8819990508135221</v>
+        <v>0.8828071603471722</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7539025466562197</v>
+        <v>0.7480008392960273</v>
       </c>
       <c r="E7" t="n">
-        <v>102.5853418015902</v>
+        <v>103.1750037849061</v>
       </c>
       <c r="F7" t="n">
-        <v>86.07043674439097</v>
+        <v>85.65952282289264</v>
       </c>
       <c r="G7" t="n">
-        <v>16.51490505719926</v>
+        <v>17.51548096201343</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3464994774750537</v>
+        <v>0.3591586515658247</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6983583335188037</v>
+        <v>0.6909909001528111</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5201515690779093</v>
+        <v>0.5231941132847586</v>
       </c>
       <c r="K7" t="n">
-        <v>5275</v>
+        <v>4650</v>
       </c>
       <c r="L7" t="n">
-        <v>2085</v>
+        <v>1850</v>
       </c>
       <c r="M7" t="n">
+        <v>454</v>
+      </c>
+      <c r="N7" t="n">
+        <v>914</v>
+      </c>
+      <c r="O7" t="n">
+        <v>189</v>
+      </c>
+      <c r="P7" t="n">
+        <v>632</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>375</v>
+      </c>
+      <c r="R7" t="n">
+        <v>589</v>
+      </c>
+      <c r="S7" t="n">
+        <v>307</v>
+      </c>
+      <c r="T7" t="n">
+        <v>572</v>
+      </c>
+      <c r="U7" t="n">
+        <v>342</v>
+      </c>
+      <c r="V7" t="n">
+        <v>260</v>
+      </c>
+      <c r="W7" t="n">
+        <v>296</v>
+      </c>
+      <c r="X7" t="n">
+        <v>538</v>
+      </c>
+      <c r="Y7" t="n">
         <v>509</v>
       </c>
-      <c r="N7" t="n">
-        <v>1037</v>
-      </c>
-      <c r="O7" t="n">
-        <v>216</v>
-      </c>
-      <c r="P7" t="n">
-        <v>713</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>419</v>
-      </c>
-      <c r="R7" t="n">
-        <v>661</v>
-      </c>
-      <c r="S7" t="n">
-        <v>338</v>
-      </c>
-      <c r="T7" t="n">
-        <v>661</v>
-      </c>
-      <c r="U7" t="n">
-        <v>387</v>
-      </c>
-      <c r="V7" t="n">
-        <v>286</v>
-      </c>
-      <c r="W7" t="n">
-        <v>333</v>
-      </c>
-      <c r="X7" t="n">
-        <v>605</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>576</v>
-      </c>
       <c r="Z7" t="n">
+        <v>67</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1524</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2101.16</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1794.16</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2225</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>203</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>423</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>105</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>311</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>189</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>307</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>149</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>266</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>162</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>107</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>135</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>266</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>257</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1004.08</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>855.08</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.9090901349216334</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.7725100510678167</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>106.5743399536909</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>90.05926312319251</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>16.51507683049837</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.3660971155739813</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.6584750752269134</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.5141991181747219</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>2425</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>251</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>491</v>
+      </c>
+      <c r="BH7" t="n">
         <v>84</v>
       </c>
-      <c r="AA7" t="n">
-        <v>1753</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2373.84</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2035.84</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2650</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>239</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>503</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>123</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>367</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>216</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>351</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>172</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>330</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>191</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>123</v>
-      </c>
-      <c r="AP7" t="n">
+      <c r="BI7" t="n">
+        <v>321</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>186</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>282</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>158</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>306</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>180</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>153</v>
+      </c>
+      <c r="BP7" t="n">
         <v>161</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>310</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>302</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>41</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1185.44</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1013.44</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0.9022662163080415</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0.7716813977153668</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>105.2381379045895</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>89.84993403968014</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>15.38820386490931</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0.3507068833411544</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0.6650525253810038</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0.5112820377229331</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>2625</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>270</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>534</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>93</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>346</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>203</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>310</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>166</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>331</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>196</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>163</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>172</v>
-      </c>
       <c r="BQ7" t="n">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="BR7" t="n">
-        <v>274</v>
+        <v>252</v>
       </c>
       <c r="BS7" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="BT7" t="n">
-        <v>1188.4</v>
+        <v>1097.08</v>
       </c>
       <c r="BU7" t="n">
-        <v>1022.4</v>
+        <v>939.0799999999999</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.8617318853190028</v>
+        <v>0.858714433653916</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.7361236955970727</v>
+        <v>0.7255340618385538</v>
       </c>
       <c r="BX7" t="n">
-        <v>99.93254569859103</v>
+        <v>100.0589456301867</v>
       </c>
       <c r="BY7" t="n">
-        <v>82.29093944910181</v>
+        <v>81.62642754761778</v>
       </c>
       <c r="BZ7" t="n">
-        <v>17.6416062494892</v>
+        <v>18.43251808256892</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.342292071608953</v>
+        <v>0.352798392891681</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.731664141656604</v>
+        <v>0.7207970730015508</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.5290211004328853</v>
+        <v>0.5314395254689591</v>
       </c>
       <c r="CD7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -2364,244 +2364,244 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9508202761597372</v>
+        <v>0.9498924400998298</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8674294242900278</v>
+        <v>0.8675705963652832</v>
       </c>
       <c r="E8" t="n">
-        <v>109.1186299566897</v>
+        <v>108.6539176433104</v>
       </c>
       <c r="F8" t="n">
-        <v>98.36768304006003</v>
+        <v>97.83594119831035</v>
       </c>
       <c r="G8" t="n">
-        <v>10.75094691662964</v>
+        <v>10.81797644500007</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3382641155878053</v>
+        <v>0.3331446662062285</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6983459352710043</v>
+        <v>0.7044592023015666</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5193284412941437</v>
+        <v>0.5193890115807258</v>
       </c>
       <c r="K8" t="n">
-        <v>5200</v>
+        <v>4600</v>
       </c>
       <c r="L8" t="n">
-        <v>2312</v>
+        <v>2043</v>
       </c>
       <c r="M8" t="n">
-        <v>570</v>
+        <v>505</v>
       </c>
       <c r="N8" t="n">
-        <v>1028</v>
+        <v>914</v>
       </c>
       <c r="O8" t="n">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="P8" t="n">
-        <v>745</v>
+        <v>656</v>
       </c>
       <c r="Q8" t="n">
-        <v>401</v>
+        <v>346</v>
       </c>
       <c r="R8" t="n">
-        <v>640</v>
+        <v>546</v>
       </c>
       <c r="S8" t="n">
-        <v>311</v>
+        <v>268</v>
       </c>
       <c r="T8" t="n">
-        <v>651</v>
+        <v>569</v>
       </c>
       <c r="U8" t="n">
-        <v>419</v>
+        <v>365</v>
       </c>
       <c r="V8" t="n">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="W8" t="n">
-        <v>374</v>
+        <v>337</v>
       </c>
       <c r="X8" t="n">
-        <v>574</v>
+        <v>516</v>
       </c>
       <c r="Y8" t="n">
-        <v>566</v>
+        <v>496</v>
       </c>
       <c r="Z8" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="AA8" t="n">
-        <v>2047</v>
+        <v>1803</v>
       </c>
       <c r="AB8" t="n">
-        <v>2428.6</v>
+        <v>2147.24</v>
       </c>
       <c r="AC8" t="n">
-        <v>2117.6</v>
+        <v>1879.24</v>
       </c>
       <c r="AD8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2200</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>225</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>430</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>107</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>316</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>164</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>275</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>124</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>236</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>172</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>111</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>142</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>249</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>252</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1009</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>885</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.9253628591597004</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.9093653200407121</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>105.4136550526525</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>102.410289398452</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>3.003365654200495</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0.3089596745490724</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0.6811995161557435</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0.4853324056179123</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>2400</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>280</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>484</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>122</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>340</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>182</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>271</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>144</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>333</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>193</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>113</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>195</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>267</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>244</v>
+      </c>
+      <c r="BS8" t="n">
         <v>26</v>
       </c>
-      <c r="AE8" t="n">
-        <v>2600</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>264</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>506</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>121</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>369</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>206</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>345</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>155</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>292</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>198</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>117</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>171</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>286</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>303</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1197.8</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1042.8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0.9151373533984545</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0.9102422138379187</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>104.9826323434091</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>103.0204244436369</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.96220789977212</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0.3221722276709489</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0.68128601930109</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0.4934027700661715</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>2600</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>306</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>522</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>136</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>376</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>195</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>295</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>156</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>359</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>221</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>124</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>203</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>288</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>263</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>31</v>
-      </c>
       <c r="BT8" t="n">
-        <v>1230.8</v>
+        <v>1138.24</v>
       </c>
       <c r="BU8" t="n">
-        <v>1074.8</v>
+        <v>994.24</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.9865031989210201</v>
+        <v>0.9723778892949483</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.8246166347421369</v>
+        <v>0.8292587663294735</v>
       </c>
       <c r="BX8" t="n">
-        <v>113.2546275699703</v>
+        <v>111.6241583514135</v>
       </c>
       <c r="BY8" t="n">
-        <v>93.71494163648312</v>
+        <v>93.64278868151382</v>
       </c>
       <c r="BZ8" t="n">
-        <v>19.53968593348717</v>
+        <v>17.98136966989969</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.3543560035046616</v>
+        <v>0.3553142418919549</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.7154058512409188</v>
+        <v>0.725780581268571</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.5452541125221161</v>
+        <v>0.5506075670466384</v>
       </c>
       <c r="CD8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -2616,244 +2616,244 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.8851124994947063</v>
+        <v>0.8743831858975031</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8853269213640691</v>
+        <v>0.8871317244136425</v>
       </c>
       <c r="E9" t="n">
-        <v>100.5253994403985</v>
+        <v>98.91306997899575</v>
       </c>
       <c r="F9" t="n">
-        <v>101.5798847385439</v>
+        <v>101.8519472883067</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.054485298145323</v>
+        <v>-2.938877309310904</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3008013916770834</v>
+        <v>0.2950500651704123</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6699312856698718</v>
+        <v>0.6671307425308836</v>
       </c>
       <c r="J9" t="n">
-        <v>0.482335915248586</v>
+        <v>0.477416168048935</v>
       </c>
       <c r="K9" t="n">
-        <v>5275</v>
+        <v>4675</v>
       </c>
       <c r="L9" t="n">
-        <v>2116</v>
+        <v>1845</v>
       </c>
       <c r="M9" t="n">
-        <v>497</v>
+        <v>445</v>
       </c>
       <c r="N9" t="n">
-        <v>1026</v>
+        <v>917</v>
       </c>
       <c r="O9" t="n">
-        <v>224</v>
+        <v>188</v>
       </c>
       <c r="P9" t="n">
-        <v>715</v>
+        <v>620</v>
       </c>
       <c r="Q9" t="n">
-        <v>450</v>
+        <v>391</v>
       </c>
       <c r="R9" t="n">
-        <v>633</v>
+        <v>550</v>
       </c>
       <c r="S9" t="n">
-        <v>296</v>
+        <v>256</v>
       </c>
       <c r="T9" t="n">
-        <v>637</v>
+        <v>555</v>
       </c>
       <c r="U9" t="n">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="V9" t="n">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="W9" t="n">
-        <v>389</v>
+        <v>349</v>
       </c>
       <c r="X9" t="n">
-        <v>672</v>
+        <v>588</v>
       </c>
       <c r="Y9" t="n">
-        <v>565</v>
+        <v>501</v>
       </c>
       <c r="Z9" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AA9" t="n">
-        <v>2143</v>
+        <v>1891</v>
       </c>
       <c r="AB9" t="n">
-        <v>2408.52</v>
+        <v>2128</v>
       </c>
       <c r="AC9" t="n">
-        <v>2112.52</v>
+        <v>1872</v>
       </c>
       <c r="AD9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE9" t="n">
-        <v>2650</v>
+        <v>2450</v>
       </c>
       <c r="AF9" t="n">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="AG9" t="n">
-        <v>535</v>
+        <v>498</v>
       </c>
       <c r="AH9" t="n">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="AI9" t="n">
-        <v>343</v>
+        <v>311</v>
       </c>
       <c r="AJ9" t="n">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="AK9" t="n">
-        <v>313</v>
+        <v>289</v>
       </c>
       <c r="AL9" t="n">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="AM9" t="n">
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="AN9" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="AO9" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="AP9" t="n">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="AQ9" t="n">
-        <v>339</v>
+        <v>307</v>
       </c>
       <c r="AR9" t="n">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="AS9" t="n">
         <v>19</v>
       </c>
       <c r="AT9" t="n">
-        <v>1200.72</v>
+        <v>1109.16</v>
       </c>
       <c r="AU9" t="n">
-        <v>1051.72</v>
+        <v>973.16</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.8773310354119596</v>
+        <v>0.8648878557140557</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.8967128102839887</v>
+        <v>0.9003691964642723</v>
       </c>
       <c r="AX9" t="n">
-        <v>99.507123637013</v>
+        <v>97.82823662169959</v>
       </c>
       <c r="AY9" t="n">
-        <v>102.5023996690648</v>
+        <v>102.7915409895599</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-2.995276032051767</v>
+        <v>-4.963304367860325</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.2935598362410327</v>
+        <v>0.2887438766485061</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.6529200040676468</v>
+        <v>0.6564040784806914</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.4617625834209909</v>
+        <v>0.4602884608065301</v>
       </c>
       <c r="BD9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BE9" t="n">
-        <v>2625</v>
+        <v>2225</v>
       </c>
       <c r="BF9" t="n">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="BG9" t="n">
-        <v>491</v>
+        <v>419</v>
       </c>
       <c r="BH9" t="n">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="BI9" t="n">
-        <v>372</v>
+        <v>309</v>
       </c>
       <c r="BJ9" t="n">
-        <v>224</v>
+        <v>185</v>
       </c>
       <c r="BK9" t="n">
-        <v>320</v>
+        <v>261</v>
       </c>
       <c r="BL9" t="n">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="BM9" t="n">
-        <v>348</v>
+        <v>288</v>
       </c>
       <c r="BN9" t="n">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="BO9" t="n">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="BP9" t="n">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="BQ9" t="n">
-        <v>333</v>
+        <v>281</v>
       </c>
       <c r="BR9" t="n">
-        <v>292</v>
+        <v>247</v>
       </c>
       <c r="BS9" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="BT9" t="n">
-        <v>1207.8</v>
+        <v>1018.84</v>
       </c>
       <c r="BU9" t="n">
-        <v>1060.8</v>
+        <v>898.8399999999999</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.8928939635774529</v>
+        <v>0.8847417279158093</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.8739410324441496</v>
+        <v>0.8726908458129556</v>
       </c>
       <c r="BX9" t="n">
-        <v>101.543675243784</v>
+        <v>100.0965245505916</v>
       </c>
       <c r="BY9" t="n">
-        <v>100.6573698080229</v>
+        <v>100.8269359778485</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.8863054357611205</v>
+        <v>-0.7304114272569897</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.3080429471131341</v>
+        <v>0.3019295435579464</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.6869425672720971</v>
+        <v>0.6788325578583657</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.502909247076181</v>
+        <v>0.496100939586104</v>
       </c>
       <c r="CD9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -2868,244 +2868,244 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.815393940275086</v>
+        <v>0.8244978657817087</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8531220170159555</v>
+        <v>0.8627134383910202</v>
       </c>
       <c r="E10" t="n">
-        <v>92.06021312986337</v>
+        <v>93.14777181756794</v>
       </c>
       <c r="F10" t="n">
-        <v>95.70468443291246</v>
+        <v>96.44763743093011</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.644471303049055</v>
+        <v>-3.299865613362164</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2821226368902643</v>
+        <v>0.2873365030019487</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7190402582115577</v>
+        <v>0.7280343538032615</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4924513729931247</v>
+        <v>0.500313570613112</v>
       </c>
       <c r="K10" t="n">
-        <v>5275</v>
+        <v>4875</v>
       </c>
       <c r="L10" t="n">
-        <v>1948</v>
+        <v>1822</v>
       </c>
       <c r="M10" t="n">
-        <v>487</v>
+        <v>456</v>
       </c>
       <c r="N10" t="n">
-        <v>1042</v>
+        <v>961</v>
       </c>
       <c r="O10" t="n">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="P10" t="n">
-        <v>659</v>
+        <v>612</v>
       </c>
       <c r="Q10" t="n">
-        <v>407</v>
+        <v>376</v>
       </c>
       <c r="R10" t="n">
-        <v>627</v>
+        <v>573</v>
       </c>
       <c r="S10" t="n">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="T10" t="n">
-        <v>650</v>
+        <v>606</v>
       </c>
       <c r="U10" t="n">
-        <v>399</v>
+        <v>373</v>
       </c>
       <c r="V10" t="n">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="W10" t="n">
-        <v>421</v>
+        <v>394</v>
       </c>
       <c r="X10" t="n">
-        <v>579</v>
+        <v>532</v>
       </c>
       <c r="Y10" t="n">
-        <v>569</v>
+        <v>524</v>
       </c>
       <c r="Z10" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA10" t="n">
-        <v>2012</v>
+        <v>1874</v>
       </c>
       <c r="AB10" t="n">
-        <v>2397.88</v>
+        <v>2219.12</v>
       </c>
       <c r="AC10" t="n">
-        <v>2118.88</v>
+        <v>1960.12</v>
       </c>
       <c r="AD10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE10" t="n">
-        <v>2650</v>
+        <v>2450</v>
       </c>
       <c r="AF10" t="n">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="AG10" t="n">
-        <v>527</v>
+        <v>486</v>
       </c>
       <c r="AH10" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="AI10" t="n">
-        <v>325</v>
+        <v>299</v>
       </c>
       <c r="AJ10" t="n">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="AK10" t="n">
-        <v>328</v>
+        <v>298</v>
       </c>
       <c r="AL10" t="n">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="AM10" t="n">
-        <v>329</v>
+        <v>308</v>
       </c>
       <c r="AN10" t="n">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="AO10" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="AP10" t="n">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="AQ10" t="n">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="AR10" t="n">
-        <v>290</v>
+        <v>265</v>
       </c>
       <c r="AS10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT10" t="n">
-        <v>1219.32</v>
+        <v>1129.12</v>
       </c>
       <c r="AU10" t="n">
-        <v>1064.32</v>
+        <v>987.12</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.7704055297083436</v>
+        <v>0.7874884738876604</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.8502178438453998</v>
+        <v>0.8640924156729811</v>
       </c>
       <c r="AX10" t="n">
-        <v>88.01621055176426</v>
+        <v>89.845713417261</v>
       </c>
       <c r="AY10" t="n">
-        <v>95.0581898180404</v>
+        <v>96.15271479759168</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-7.041979266276147</v>
+        <v>-6.307001380330674</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.2959223096112322</v>
+        <v>0.2993406720134754</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.7333914426671048</v>
+        <v>0.7458962851115857</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.4991167418983916</v>
+        <v>0.5081427539148284</v>
       </c>
       <c r="BD10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BE10" t="n">
-        <v>2625</v>
+        <v>2425</v>
       </c>
       <c r="BF10" t="n">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="BG10" t="n">
-        <v>515</v>
+        <v>475</v>
       </c>
       <c r="BH10" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="BI10" t="n">
-        <v>334</v>
+        <v>313</v>
       </c>
       <c r="BJ10" t="n">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="BK10" t="n">
-        <v>299</v>
+        <v>275</v>
       </c>
       <c r="BL10" t="n">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="BM10" t="n">
-        <v>321</v>
+        <v>298</v>
       </c>
       <c r="BN10" t="n">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="BO10" t="n">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="BP10" t="n">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="BQ10" t="n">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="BR10" t="n">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="BS10" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BT10" t="n">
-        <v>1178.56</v>
+        <v>1090</v>
       </c>
       <c r="BU10" t="n">
-        <v>1054.56</v>
+        <v>973</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.8603823508418287</v>
+        <v>0.8615072576757571</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.8560261901865106</v>
+        <v>0.8613344611090591</v>
       </c>
       <c r="BX10" t="n">
-        <v>96.1042157079625</v>
+        <v>96.44983021787486</v>
       </c>
       <c r="BY10" t="n">
-        <v>96.35117904778447</v>
+        <v>96.74256006426852</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0.2469633398219621</v>
+        <v>-0.292729846393654</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.2683229641692966</v>
+        <v>0.2753323339904222</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.704689073756011</v>
+        <v>0.7101724224949377</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.485786004087858</v>
+        <v>0.4924843873113957</v>
       </c>
       <c r="CD10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -3120,244 +3120,244 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8568637676593924</v>
+        <v>0.8595718085586398</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8808460175277355</v>
+        <v>0.8842453853900665</v>
       </c>
       <c r="E11" t="n">
-        <v>97.64868734406079</v>
+        <v>98.26502607392173</v>
       </c>
       <c r="F11" t="n">
-        <v>98.61286341537733</v>
+        <v>99.24601979626637</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9641760713165357</v>
+        <v>-0.9809937223446218</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3111572794023815</v>
+        <v>0.3168664644506192</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7307362586818539</v>
+        <v>0.7229545516160432</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5212916719275295</v>
+        <v>0.5184012440529205</v>
       </c>
       <c r="K11" t="n">
-        <v>5225</v>
+        <v>4825</v>
       </c>
       <c r="L11" t="n">
-        <v>2004</v>
+        <v>1860</v>
       </c>
       <c r="M11" t="n">
-        <v>501</v>
+        <v>463</v>
       </c>
       <c r="N11" t="n">
-        <v>1021</v>
+        <v>939</v>
       </c>
       <c r="O11" t="n">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="P11" t="n">
-        <v>647</v>
+        <v>600</v>
       </c>
       <c r="Q11" t="n">
-        <v>393</v>
+        <v>373</v>
       </c>
       <c r="R11" t="n">
-        <v>601</v>
+        <v>570</v>
       </c>
       <c r="S11" t="n">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="T11" t="n">
-        <v>652</v>
+        <v>592</v>
       </c>
       <c r="U11" t="n">
-        <v>350</v>
+        <v>325</v>
       </c>
       <c r="V11" t="n">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="W11" t="n">
-        <v>400</v>
+        <v>368</v>
       </c>
       <c r="X11" t="n">
-        <v>587</v>
+        <v>544</v>
       </c>
       <c r="Y11" t="n">
-        <v>549</v>
+        <v>513</v>
       </c>
       <c r="Z11" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="AA11" t="n">
-        <v>2022</v>
+        <v>1881</v>
       </c>
       <c r="AB11" t="n">
-        <v>2332.44</v>
+        <v>2157.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>2050.44</v>
+        <v>1890.8</v>
       </c>
       <c r="AD11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2400</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>233</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>464</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>289</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>190</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>278</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>124</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>302</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>157</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>106</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>200</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>265</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>251</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1075.32</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>951.3199999999999</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.8445272625342586</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.8694084905390532</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>95.43090092342997</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>99.28622037793322</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-3.855319454503253</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.2943632306783068</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.6948785444863583</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.4994321274745528</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>2425</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>230</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>475</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>102</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>311</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>183</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>292</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>143</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>290</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>168</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>103</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>168</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>279</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>262</v>
+      </c>
+      <c r="BS11" t="n">
         <v>26</v>
       </c>
-      <c r="AE11" t="n">
-        <v>2600</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>257</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>510</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>93</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>310</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>199</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>295</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>132</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>336</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>172</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>213</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>285</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>268</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1162.8</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1030.8</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0.8507886981797715</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0.8660076514606458</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>95.92948014472007</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>98.64720228238664</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>-2.717722137666577</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0.2898194527528262</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>0.7036974110277008</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>0.5035243929724618</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>2625</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>244</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>511</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>110</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>337</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>194</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>306</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>150</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>316</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>178</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>112</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>187</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>302</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>281</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>28</v>
-      </c>
       <c r="BT11" t="n">
-        <v>1169.64</v>
+        <v>1082.48</v>
       </c>
       <c r="BU11" t="n">
-        <v>1019.64</v>
+        <v>939.48</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.8629388371390133</v>
+        <v>0.8746163545830208</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.8956843835948244</v>
+        <v>0.8990822802410793</v>
       </c>
       <c r="BX11" t="n">
-        <v>99.36789454340149</v>
+        <v>101.0991512244135</v>
       </c>
       <c r="BY11" t="n">
-        <v>98.57852454836799</v>
+        <v>99.20581921459949</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.7893699950335061</v>
+        <v>1.893332009814009</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.3324951060519369</v>
+        <v>0.3393696982229317</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.7577751063360073</v>
+        <v>0.7510305587457284</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.539058950882597</v>
+        <v>0.537370360631288</v>
       </c>
       <c r="CD11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -3372,244 +3372,244 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.8486119692410194</v>
+        <v>0.8344884557429629</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8224757533433978</v>
+        <v>0.8258706688338877</v>
       </c>
       <c r="E12" t="n">
-        <v>95.33349282940951</v>
+        <v>93.86452312443944</v>
       </c>
       <c r="F12" t="n">
-        <v>94.8908382387215</v>
+        <v>95.4950585621211</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4426545906880287</v>
+        <v>-1.630535437681617</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2795904190378659</v>
+        <v>0.2764633888682166</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6863655445176248</v>
+        <v>0.6826238958438676</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4960995852523127</v>
+        <v>0.4915062413579238</v>
       </c>
       <c r="K12" t="n">
-        <v>5250</v>
+        <v>4650</v>
       </c>
       <c r="L12" t="n">
-        <v>1985</v>
+        <v>1722</v>
       </c>
       <c r="M12" t="n">
-        <v>473</v>
+        <v>406</v>
       </c>
       <c r="N12" t="n">
-        <v>970</v>
+        <v>843</v>
       </c>
       <c r="O12" t="n">
+        <v>171</v>
+      </c>
+      <c r="P12" t="n">
+        <v>587</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>397</v>
+      </c>
+      <c r="R12" t="n">
+        <v>621</v>
+      </c>
+      <c r="S12" t="n">
+        <v>235</v>
+      </c>
+      <c r="T12" t="n">
+        <v>624</v>
+      </c>
+      <c r="U12" t="n">
+        <v>362</v>
+      </c>
+      <c r="V12" t="n">
+        <v>196</v>
+      </c>
+      <c r="W12" t="n">
+        <v>369</v>
+      </c>
+      <c r="X12" t="n">
+        <v>467</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>514</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1758</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2072.24</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1837.24</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2425</v>
+      </c>
+      <c r="AF12" t="n">
         <v>201</v>
       </c>
-      <c r="P12" t="n">
-        <v>668</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>436</v>
-      </c>
-      <c r="R12" t="n">
-        <v>682</v>
-      </c>
-      <c r="S12" t="n">
-        <v>264</v>
-      </c>
-      <c r="T12" t="n">
-        <v>707</v>
-      </c>
-      <c r="U12" t="n">
-        <v>426</v>
-      </c>
-      <c r="V12" t="n">
-        <v>225</v>
-      </c>
-      <c r="W12" t="n">
-        <v>410</v>
-      </c>
-      <c r="X12" t="n">
-        <v>532</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>575</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1979</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2348.08</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2084.08</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2625</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>220</v>
-      </c>
       <c r="AG12" t="n">
-        <v>475</v>
+        <v>438</v>
       </c>
       <c r="AH12" t="n">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="AI12" t="n">
-        <v>330</v>
+        <v>297</v>
       </c>
       <c r="AJ12" t="n">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="AK12" t="n">
-        <v>365</v>
+        <v>347</v>
       </c>
       <c r="AL12" t="n">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="AM12" t="n">
-        <v>355</v>
+        <v>324</v>
       </c>
       <c r="AN12" t="n">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="AO12" t="n">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="AP12" t="n">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="AQ12" t="n">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="AR12" t="n">
-        <v>306</v>
+        <v>284</v>
       </c>
       <c r="AS12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AT12" t="n">
-        <v>1171.6</v>
+        <v>1075.68</v>
       </c>
       <c r="AU12" t="n">
-        <v>1037.6</v>
+        <v>954.6799999999999</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.8142356686159271</v>
+        <v>0.8160613960742603</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.8243565433509333</v>
+        <v>0.8224792995606204</v>
       </c>
       <c r="AX12" t="n">
-        <v>91.50029408752479</v>
+        <v>91.48743469065387</v>
       </c>
       <c r="AY12" t="n">
-        <v>95.0913538892827</v>
+        <v>95.3525632476384</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-3.591059801757874</v>
+        <v>-3.865128556984502</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.2660756474063963</v>
+        <v>0.2581560254310034</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.6923747594166212</v>
+        <v>0.6820901998943221</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.4881956051418638</v>
+        <v>0.4793290226874696</v>
       </c>
       <c r="BD12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BE12" t="n">
-        <v>2625</v>
+        <v>2225</v>
       </c>
       <c r="BF12" t="n">
-        <v>253</v>
+        <v>205</v>
       </c>
       <c r="BG12" t="n">
-        <v>495</v>
+        <v>405</v>
       </c>
       <c r="BH12" t="n">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="BI12" t="n">
-        <v>338</v>
+        <v>290</v>
       </c>
       <c r="BJ12" t="n">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="BK12" t="n">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="BL12" t="n">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="BM12" t="n">
-        <v>352</v>
+        <v>300</v>
       </c>
       <c r="BN12" t="n">
-        <v>228</v>
+        <v>181</v>
       </c>
       <c r="BO12" t="n">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="BP12" t="n">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="BQ12" t="n">
-        <v>276</v>
+        <v>232</v>
       </c>
       <c r="BR12" t="n">
-        <v>269</v>
+        <v>230</v>
       </c>
       <c r="BS12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BT12" t="n">
-        <v>1176.48</v>
+        <v>996.5599999999999</v>
       </c>
       <c r="BU12" t="n">
-        <v>1046.48</v>
+        <v>882.5599999999999</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.8829882698661117</v>
+        <v>0.8545907026542751</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.8205949633358625</v>
+        <v>0.8295703444047248</v>
       </c>
       <c r="BX12" t="n">
-        <v>99.16669157129422</v>
+        <v>96.45771050675101</v>
       </c>
       <c r="BY12" t="n">
-        <v>94.6903225881603</v>
+        <v>95.65050799610221</v>
       </c>
       <c r="BZ12" t="n">
-        <v>4.476368983133932</v>
+        <v>0.8072025106488018</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.2931051906693355</v>
+        <v>0.2964350580724492</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.6803563296186286</v>
+        <v>0.6832061096070086</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.5040035653627617</v>
+        <v>0.5047904799075101</v>
       </c>
       <c r="CD12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -3624,244 +3624,244 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.7571515140951827</v>
+        <v>0.7674620764038266</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8205752961021791</v>
+        <v>0.8314247400423675</v>
       </c>
       <c r="E13" t="n">
-        <v>86.32791233292218</v>
+        <v>87.29471229001534</v>
       </c>
       <c r="F13" t="n">
-        <v>93.68590757320759</v>
+        <v>94.8558899011672</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.357995240285392</v>
+        <v>-7.561177611151865</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3061235519299806</v>
+        <v>0.3022113333042626</v>
       </c>
       <c r="I13" t="n">
-        <v>0.718245677295031</v>
+        <v>0.7160708261193905</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5241355461663776</v>
+        <v>0.5207853449394354</v>
       </c>
       <c r="K13" t="n">
-        <v>5225</v>
+        <v>4825</v>
       </c>
       <c r="L13" t="n">
-        <v>1770</v>
+        <v>1661</v>
       </c>
       <c r="M13" t="n">
-        <v>477</v>
+        <v>442</v>
       </c>
       <c r="N13" t="n">
-        <v>1043</v>
+        <v>970</v>
       </c>
       <c r="O13" t="n">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="P13" t="n">
-        <v>558</v>
+        <v>510</v>
       </c>
       <c r="Q13" t="n">
-        <v>369</v>
+        <v>348</v>
       </c>
       <c r="R13" t="n">
-        <v>640</v>
+        <v>603</v>
       </c>
       <c r="S13" t="n">
-        <v>287</v>
+        <v>261</v>
       </c>
       <c r="T13" t="n">
-        <v>762</v>
+        <v>695</v>
       </c>
       <c r="U13" t="n">
-        <v>292</v>
+        <v>274</v>
       </c>
       <c r="V13" t="n">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="W13" t="n">
-        <v>446</v>
+        <v>412</v>
       </c>
       <c r="X13" t="n">
-        <v>559</v>
+        <v>519</v>
       </c>
       <c r="Y13" t="n">
-        <v>585</v>
+        <v>544</v>
       </c>
       <c r="Z13" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AA13" t="n">
-        <v>1950</v>
+        <v>1834</v>
       </c>
       <c r="AB13" t="n">
-        <v>2328.6</v>
+        <v>2157.32</v>
       </c>
       <c r="AC13" t="n">
-        <v>2041.6</v>
+        <v>1896.32</v>
       </c>
       <c r="AD13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE13" t="n">
-        <v>2625</v>
+        <v>2425</v>
       </c>
       <c r="AF13" t="n">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="AG13" t="n">
-        <v>528</v>
+        <v>492</v>
       </c>
       <c r="AH13" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AI13" t="n">
-        <v>283</v>
+        <v>262</v>
       </c>
       <c r="AJ13" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="AK13" t="n">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="AL13" t="n">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="AM13" t="n">
-        <v>355</v>
+        <v>326</v>
       </c>
       <c r="AN13" t="n">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="AO13" t="n">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="AP13" t="n">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="AQ13" t="n">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="AR13" t="n">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="AS13" t="n">
         <v>38</v>
       </c>
       <c r="AT13" t="n">
-        <v>1166.16</v>
+        <v>1085.56</v>
       </c>
       <c r="AU13" t="n">
-        <v>1028.16</v>
+        <v>958.5600000000001</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.7513430915734868</v>
+        <v>0.7653611366322367</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.8766210823439031</v>
+        <v>0.8817266943656207</v>
       </c>
       <c r="AX13" t="n">
-        <v>85.19301018489224</v>
+        <v>86.6650330642846</v>
       </c>
       <c r="AY13" t="n">
-        <v>100.0105977405813</v>
+        <v>100.5756422931646</v>
       </c>
       <c r="AZ13" t="n">
-        <v>-14.81758755568901</v>
+        <v>-13.91060922887999</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.2903952824579402</v>
+        <v>0.2904720823118913</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.7012535884627226</v>
+        <v>0.6977255755354709</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.4993526155585635</v>
+        <v>0.4976752902317338</v>
       </c>
       <c r="BD13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BE13" t="n">
-        <v>2600</v>
+        <v>2400</v>
       </c>
       <c r="BF13" t="n">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="BG13" t="n">
-        <v>515</v>
+        <v>478</v>
       </c>
       <c r="BH13" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="BI13" t="n">
-        <v>275</v>
+        <v>248</v>
       </c>
       <c r="BJ13" t="n">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="BK13" t="n">
-        <v>351</v>
+        <v>329</v>
       </c>
       <c r="BL13" t="n">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="BM13" t="n">
-        <v>407</v>
+        <v>369</v>
       </c>
       <c r="BN13" t="n">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="BO13" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="BP13" t="n">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="BQ13" t="n">
-        <v>295</v>
+        <v>270</v>
       </c>
       <c r="BR13" t="n">
-        <v>308</v>
+        <v>285</v>
       </c>
       <c r="BS13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BT13" t="n">
-        <v>1162.44</v>
+        <v>1071.76</v>
       </c>
       <c r="BU13" t="n">
-        <v>1013.44</v>
+        <v>937.76</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.7629599366168786</v>
+        <v>0.7695630161754164</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.7645295098604545</v>
+        <v>0.7811227857191141</v>
       </c>
       <c r="BX13" t="n">
-        <v>87.46281448095215</v>
+        <v>87.92439151574608</v>
       </c>
       <c r="BY13" t="n">
-        <v>87.36121740583391</v>
+        <v>89.13613750916981</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.1015970751182286</v>
+        <v>-1.211745993423738</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.321851821402021</v>
+        <v>0.3139505842966339</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.7352377661273397</v>
+        <v>0.7344160767033108</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.5489184767741915</v>
+        <v>0.5438953996471366</v>
       </c>
       <c r="CD13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -3876,244 +3876,244 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.8789902860108645</v>
+        <v>0.8841073466417416</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7882243306054743</v>
+        <v>0.7903167332214046</v>
       </c>
       <c r="E14" t="n">
-        <v>101.5299692112633</v>
+        <v>102.1843417754275</v>
       </c>
       <c r="F14" t="n">
-        <v>88.56317370801952</v>
+        <v>88.54703494699572</v>
       </c>
       <c r="G14" t="n">
-        <v>12.96679550324382</v>
+        <v>13.63730682843183</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3380525198538998</v>
+        <v>0.3450800561444543</v>
       </c>
       <c r="I14" t="n">
-        <v>0.724822358722361</v>
+        <v>0.7301646981397005</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5266896489759472</v>
+        <v>0.5336018498597763</v>
       </c>
       <c r="K14" t="n">
-        <v>5200</v>
+        <v>4800</v>
       </c>
       <c r="L14" t="n">
-        <v>2073</v>
+        <v>1929</v>
       </c>
       <c r="M14" t="n">
-        <v>497</v>
+        <v>462</v>
       </c>
       <c r="N14" t="n">
-        <v>1035</v>
+        <v>955</v>
       </c>
       <c r="O14" t="n">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="P14" t="n">
-        <v>645</v>
+        <v>581</v>
       </c>
       <c r="Q14" t="n">
-        <v>476</v>
+        <v>447</v>
       </c>
       <c r="R14" t="n">
-        <v>704</v>
+        <v>666</v>
       </c>
       <c r="S14" t="n">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="T14" t="n">
-        <v>642</v>
+        <v>597</v>
       </c>
       <c r="U14" t="n">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="V14" t="n">
+        <v>243</v>
+      </c>
+      <c r="W14" t="n">
+        <v>362</v>
+      </c>
+      <c r="X14" t="n">
+        <v>522</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>558</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>45</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1656</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2191.04</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1890.04</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2400</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>227</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>464</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>87</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>290</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>220</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>330</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>146</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>281</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>178</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>122</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>192</v>
+      </c>
+      <c r="AQ14" t="n">
         <v>260</v>
       </c>
-      <c r="W14" t="n">
-        <v>378</v>
-      </c>
-      <c r="X14" t="n">
-        <v>566</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>597</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>49</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1796</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2367.76</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2043.76</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2600</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>242</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>499</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>93</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>312</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>242</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>357</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>151</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>302</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>186</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>132</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>205</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>279</v>
-      </c>
       <c r="AR14" t="n">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="AS14" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AT14" t="n">
-        <v>1173.08</v>
+        <v>1091.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>1022.08</v>
+        <v>945.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.8576815423109602</v>
+        <v>0.8579125355168932</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.7941816819413042</v>
+        <v>0.8001294364521695</v>
       </c>
       <c r="AX14" t="n">
-        <v>98.52372122401306</v>
+        <v>99.14644894654832</v>
       </c>
       <c r="AY14" t="n">
-        <v>89.55730200837401</v>
+        <v>90.47100931146706</v>
       </c>
       <c r="AZ14" t="n">
-        <v>8.966419215639053</v>
+        <v>8.675439635081265</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.3254296786118027</v>
+        <v>0.3391079582810658</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.7026811255710486</v>
+        <v>0.6987378860353025</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.5061438738944881</v>
+        <v>0.5115993662105542</v>
       </c>
       <c r="BD14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BE14" t="n">
-        <v>2600</v>
+        <v>2400</v>
       </c>
       <c r="BF14" t="n">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="BG14" t="n">
-        <v>536</v>
+        <v>491</v>
       </c>
       <c r="BH14" t="n">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="BI14" t="n">
-        <v>333</v>
+        <v>291</v>
       </c>
       <c r="BJ14" t="n">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="BK14" t="n">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="BL14" t="n">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="BM14" t="n">
-        <v>340</v>
+        <v>316</v>
       </c>
       <c r="BN14" t="n">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="BO14" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="BP14" t="n">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="BQ14" t="n">
-        <v>287</v>
+        <v>262</v>
       </c>
       <c r="BR14" t="n">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="BS14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BT14" t="n">
-        <v>1194.68</v>
+        <v>1099.84</v>
       </c>
       <c r="BU14" t="n">
-        <v>1021.68</v>
+        <v>944.84</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.9002990297107686</v>
+        <v>0.9103021577665901</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.7822669792696437</v>
+        <v>0.7805040299906394</v>
       </c>
       <c r="BX14" t="n">
-        <v>104.5362171985136</v>
+        <v>105.2222346043068</v>
       </c>
       <c r="BY14" t="n">
-        <v>87.56904540766499</v>
+        <v>86.62306058252437</v>
       </c>
       <c r="BZ14" t="n">
-        <v>16.96717179084859</v>
+        <v>18.5991740217824</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.3506753610959969</v>
+        <v>0.3510521540078428</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.7469635918736733</v>
+        <v>0.7615915102440985</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.547235424057406</v>
+        <v>0.5556043335089983</v>
       </c>
       <c r="CD14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -4128,244 +4128,244 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.8765593402794322</v>
+        <v>0.8790411739577983</v>
       </c>
       <c r="D15" t="n">
-        <v>0.823985821937849</v>
+        <v>0.8280067815599695</v>
       </c>
       <c r="E15" t="n">
-        <v>99.90756223993695</v>
+        <v>99.91538486447435</v>
       </c>
       <c r="F15" t="n">
-        <v>93.08298015299553</v>
+        <v>93.63869925384647</v>
       </c>
       <c r="G15" t="n">
-        <v>6.824582086941435</v>
+        <v>6.276685610627879</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3282571815436758</v>
+        <v>0.325771879332248</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7163552919826551</v>
+        <v>0.7125619829812098</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5241903178372597</v>
+        <v>0.5221153746691695</v>
       </c>
       <c r="K15" t="n">
-        <v>5225</v>
+        <v>4800</v>
       </c>
       <c r="L15" t="n">
-        <v>2253</v>
+        <v>2080</v>
       </c>
       <c r="M15" t="n">
-        <v>593</v>
+        <v>555</v>
       </c>
       <c r="N15" t="n">
-        <v>1161</v>
+        <v>1075</v>
       </c>
       <c r="O15" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="P15" t="n">
-        <v>673</v>
+        <v>612</v>
       </c>
       <c r="Q15" t="n">
-        <v>470</v>
+        <v>424</v>
       </c>
       <c r="R15" t="n">
-        <v>666</v>
+        <v>607</v>
       </c>
       <c r="S15" t="n">
-        <v>321</v>
+        <v>289</v>
       </c>
       <c r="T15" t="n">
-        <v>721</v>
+        <v>660</v>
       </c>
       <c r="U15" t="n">
-        <v>448</v>
+        <v>417</v>
       </c>
       <c r="V15" t="n">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="W15" t="n">
-        <v>455</v>
+        <v>421</v>
       </c>
       <c r="X15" t="n">
-        <v>574</v>
+        <v>528</v>
       </c>
       <c r="Y15" t="n">
-        <v>594</v>
+        <v>541</v>
       </c>
       <c r="Z15" t="n">
         <v>83</v>
       </c>
       <c r="AA15" t="n">
-        <v>2076</v>
+        <v>1925</v>
       </c>
       <c r="AB15" t="n">
-        <v>2582.04</v>
+        <v>2375.08</v>
       </c>
       <c r="AC15" t="n">
-        <v>2261.04</v>
+        <v>2086.08</v>
       </c>
       <c r="AD15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE15" t="n">
-        <v>2600</v>
+        <v>2400</v>
       </c>
       <c r="AF15" t="n">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="AG15" t="n">
-        <v>559</v>
+        <v>521</v>
       </c>
       <c r="AH15" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="AI15" t="n">
-        <v>333</v>
+        <v>303</v>
       </c>
       <c r="AJ15" t="n">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="AK15" t="n">
-        <v>342</v>
+        <v>313</v>
       </c>
       <c r="AL15" t="n">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="AM15" t="n">
-        <v>358</v>
+        <v>331</v>
       </c>
       <c r="AN15" t="n">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="AO15" t="n">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="AP15" t="n">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="AQ15" t="n">
-        <v>293</v>
+        <v>267</v>
       </c>
       <c r="AR15" t="n">
-        <v>301</v>
+        <v>273</v>
       </c>
       <c r="AS15" t="n">
         <v>47</v>
       </c>
       <c r="AT15" t="n">
-        <v>1266.48</v>
+        <v>1168.72</v>
       </c>
       <c r="AU15" t="n">
-        <v>1113.48</v>
+        <v>1029.72</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.8581258499479115</v>
+        <v>0.842688710602327</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.8514153833359178</v>
+        <v>0.8499182626795033</v>
       </c>
       <c r="AX15" t="n">
-        <v>97.65230184440755</v>
+        <v>95.64195163994198</v>
       </c>
       <c r="AY15" t="n">
-        <v>94.60579058914529</v>
+        <v>94.839210890144</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.046511255262251</v>
+        <v>0.8027407497979802</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.3126916325087058</v>
+        <v>0.3063418611436905</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.7453607476590591</v>
+        <v>0.737161643297314</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.5260647712524217</v>
+        <v>0.5196584041509079</v>
       </c>
       <c r="BD15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BE15" t="n">
-        <v>2625</v>
+        <v>2400</v>
       </c>
       <c r="BF15" t="n">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="BG15" t="n">
-        <v>602</v>
+        <v>554</v>
       </c>
       <c r="BH15" t="n">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="BI15" t="n">
-        <v>340</v>
+        <v>309</v>
       </c>
       <c r="BJ15" t="n">
-        <v>226</v>
+        <v>203</v>
       </c>
       <c r="BK15" t="n">
-        <v>324</v>
+        <v>294</v>
       </c>
       <c r="BL15" t="n">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="BM15" t="n">
-        <v>363</v>
+        <v>329</v>
       </c>
       <c r="BN15" t="n">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="BO15" t="n">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="BP15" t="n">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="BQ15" t="n">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="BR15" t="n">
-        <v>293</v>
+        <v>268</v>
       </c>
       <c r="BS15" t="n">
         <v>36</v>
       </c>
       <c r="BT15" t="n">
-        <v>1315.56</v>
+        <v>1206.36</v>
       </c>
       <c r="BU15" t="n">
-        <v>1147.56</v>
+        <v>1056.36</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.8949928306109529</v>
+        <v>0.9153936373132697</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.7965562605397802</v>
+        <v>0.8060953004404361</v>
       </c>
       <c r="BX15" t="n">
-        <v>102.1628226354664</v>
+        <v>104.1888180890067</v>
       </c>
       <c r="BY15" t="n">
-        <v>91.56016971684572</v>
+        <v>92.43818761754891</v>
       </c>
       <c r="BZ15" t="n">
-        <v>10.60265291862062</v>
+        <v>11.75063047145778</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.3438227305786459</v>
+        <v>0.3452018975208058</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.6873498363062516</v>
+        <v>0.6879623226651059</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.5223158644220975</v>
+        <v>0.5245723451874311</v>
       </c>
       <c r="CD15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data/3FEB_25_26/teams_25_26_3FEB.xlsx
+++ b/data/3FEB_25_26/teams_25_26_3FEB.xlsx
@@ -852,244 +852,244 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7928294889524842</v>
+        <v>0.8001833169490543</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8986599544797419</v>
+        <v>0.8953743731225363</v>
       </c>
       <c r="E2" t="n">
-        <v>87.60007049650642</v>
+        <v>88.20076215048373</v>
       </c>
       <c r="F2" t="n">
-        <v>103.77011001493</v>
+        <v>102.9383994952986</v>
       </c>
       <c r="G2" t="n">
-        <v>-16.1700395184236</v>
+        <v>-14.73763734481487</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2296314275164409</v>
+        <v>0.2247772017729559</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6406535135261598</v>
+        <v>0.6517377843894578</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4298006004259114</v>
+        <v>0.4326921930352894</v>
       </c>
       <c r="K2" t="n">
-        <v>4975</v>
+        <v>5375</v>
       </c>
       <c r="L2" t="n">
-        <v>1773</v>
+        <v>1932</v>
       </c>
       <c r="M2" t="n">
-        <v>468</v>
+        <v>507</v>
       </c>
       <c r="N2" t="n">
-        <v>1011</v>
+        <v>1082</v>
       </c>
       <c r="O2" t="n">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="P2" t="n">
-        <v>579</v>
+        <v>633</v>
       </c>
       <c r="Q2" t="n">
-        <v>369</v>
+        <v>405</v>
       </c>
       <c r="R2" t="n">
-        <v>567</v>
+        <v>624</v>
       </c>
       <c r="S2" t="n">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="T2" t="n">
-        <v>565</v>
+        <v>616</v>
       </c>
       <c r="U2" t="n">
-        <v>312</v>
+        <v>347</v>
       </c>
       <c r="V2" t="n">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="W2" t="n">
-        <v>404</v>
+        <v>433</v>
       </c>
       <c r="X2" t="n">
-        <v>571</v>
+        <v>620</v>
       </c>
       <c r="Y2" t="n">
-        <v>501</v>
+        <v>549</v>
       </c>
       <c r="Z2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="AA2" t="n">
-        <v>2115</v>
+        <v>2267</v>
       </c>
       <c r="AB2" t="n">
-        <v>2243.48</v>
+        <v>2422.56</v>
       </c>
       <c r="AC2" t="n">
-        <v>2022.48</v>
+        <v>2189.56</v>
       </c>
       <c r="AD2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE2" t="n">
-        <v>2475</v>
+        <v>2675</v>
       </c>
       <c r="AF2" t="n">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="AG2" t="n">
-        <v>522</v>
+        <v>558</v>
       </c>
       <c r="AH2" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AI2" t="n">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="AJ2" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AK2" t="n">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="AL2" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="AM2" t="n">
-        <v>277</v>
+        <v>306</v>
       </c>
       <c r="AN2" t="n">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="AO2" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="AP2" t="n">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="AQ2" t="n">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="AR2" t="n">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="AS2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT2" t="n">
-        <v>1110</v>
+        <v>1201.52</v>
       </c>
       <c r="AU2" t="n">
-        <v>1006</v>
+        <v>1093.52</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.8266035887880183</v>
+        <v>0.8294186435504246</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.9404365819691645</v>
+        <v>0.9371677145330783</v>
       </c>
       <c r="AX2" t="n">
-        <v>90.91239986339498</v>
+        <v>90.86260620212694</v>
       </c>
       <c r="AY2" t="n">
-        <v>108.9527791394979</v>
+        <v>108.1422381687244</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-18.04037927610286</v>
+        <v>-17.27963196659747</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.2136878708190465</v>
+        <v>0.2078604218701013</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.6326630760185513</v>
+        <v>0.6442877458466462</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.4181588421673454</v>
+        <v>0.4244543158467804</v>
       </c>
       <c r="BD2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BE2" t="n">
-        <v>2500</v>
+        <v>2700</v>
       </c>
       <c r="BF2" t="n">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="BG2" t="n">
-        <v>489</v>
+        <v>524</v>
       </c>
       <c r="BH2" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="BI2" t="n">
-        <v>302</v>
+        <v>336</v>
       </c>
       <c r="BJ2" t="n">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="BK2" t="n">
-        <v>267</v>
+        <v>291</v>
       </c>
       <c r="BL2" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="BM2" t="n">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="BN2" t="n">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="BO2" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="BP2" t="n">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="BQ2" t="n">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="BR2" t="n">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="BS2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BT2" t="n">
-        <v>1133.48</v>
+        <v>1221.04</v>
       </c>
       <c r="BU2" t="n">
-        <v>1016.48</v>
+        <v>1096.04</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.7590553891169501</v>
+        <v>0.7709479903476841</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.8568833269903194</v>
+        <v>0.8535810317119943</v>
       </c>
       <c r="BX2" t="n">
-        <v>84.28774112961786</v>
+        <v>85.53891809884051</v>
       </c>
       <c r="BY2" t="n">
-        <v>98.5874408903622</v>
+        <v>97.7345608218728</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-14.29969976074433</v>
+        <v>-12.19564272303228</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.2455749842138355</v>
+        <v>0.2416939816758107</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.6486439510337686</v>
+        <v>0.65918782293227</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.4414423586844773</v>
+        <v>0.4409300702237984</v>
       </c>
       <c r="CD2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -1104,244 +1104,244 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7761132237011646</v>
+        <v>0.7723078428252476</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8752694388958985</v>
+        <v>0.883110518157143</v>
       </c>
       <c r="E3" t="n">
-        <v>88.2741821754877</v>
+        <v>87.77210813310401</v>
       </c>
       <c r="F3" t="n">
-        <v>100.1415291687097</v>
+        <v>100.6535761402495</v>
       </c>
       <c r="G3" t="n">
-        <v>-11.86734699322201</v>
+        <v>-12.88146800714543</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2860106476679811</v>
+        <v>0.2832405978473672</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6890651353382878</v>
+        <v>0.6939619181235611</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4863054415990148</v>
+        <v>0.4844984572690079</v>
       </c>
       <c r="K3" t="n">
-        <v>4900</v>
+        <v>5300</v>
       </c>
       <c r="L3" t="n">
-        <v>1756</v>
+        <v>1888</v>
       </c>
       <c r="M3" t="n">
-        <v>473</v>
+        <v>505</v>
       </c>
       <c r="N3" t="n">
-        <v>1030</v>
+        <v>1111</v>
       </c>
       <c r="O3" t="n">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="P3" t="n">
-        <v>555</v>
+        <v>611</v>
       </c>
       <c r="Q3" t="n">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="R3" t="n">
-        <v>620</v>
+        <v>659</v>
       </c>
       <c r="S3" t="n">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="T3" t="n">
-        <v>650</v>
+        <v>696</v>
       </c>
       <c r="U3" t="n">
+        <v>313</v>
+      </c>
+      <c r="V3" t="n">
+        <v>189</v>
+      </c>
+      <c r="W3" t="n">
+        <v>429</v>
+      </c>
+      <c r="X3" t="n">
+        <v>591</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>583</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2177</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2440.96</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2146.96</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2625</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>238</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>559</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>71</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>303</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>205</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>314</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>154</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>318</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>129</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>94</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>218</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>287</v>
       </c>
-      <c r="V3" t="n">
-        <v>177</v>
-      </c>
-      <c r="W3" t="n">
-        <v>400</v>
-      </c>
-      <c r="X3" t="n">
-        <v>556</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>545</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>41</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2005</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2257.8</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1984.8</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2425</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>225</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>520</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>64</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>278</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>191</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>291</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>141</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>298</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>119</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>88</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>195</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>269</v>
-      </c>
       <c r="AR3" t="n">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="AS3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT3" t="n">
-        <v>1121.04</v>
+        <v>1218.16</v>
       </c>
       <c r="AU3" t="n">
-        <v>980.04</v>
+        <v>1064.16</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.7447167418509636</v>
+        <v>0.7357453741784841</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.9173596606819795</v>
+        <v>0.9259074569878447</v>
       </c>
       <c r="AX3" t="n">
-        <v>85.18072152433017</v>
+        <v>84.20647018501028</v>
       </c>
       <c r="AY3" t="n">
-        <v>105.3200257751431</v>
+        <v>105.8095506229975</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-20.1393042508129</v>
+        <v>-21.60308043798723</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.2893831029863625</v>
+        <v>0.2909323881046276</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.664883229227427</v>
+        <v>0.6707184224207589</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.4699609216836479</v>
+        <v>0.4705993792129994</v>
       </c>
       <c r="BD3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BE3" t="n">
-        <v>2475</v>
+        <v>2675</v>
       </c>
       <c r="BF3" t="n">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="BG3" t="n">
-        <v>510</v>
+        <v>552</v>
       </c>
       <c r="BH3" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="BI3" t="n">
-        <v>277</v>
+        <v>308</v>
       </c>
       <c r="BJ3" t="n">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="BK3" t="n">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="BL3" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="BM3" t="n">
-        <v>352</v>
+        <v>378</v>
       </c>
       <c r="BN3" t="n">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="BO3" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="BP3" t="n">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="BQ3" t="n">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="BR3" t="n">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="BS3" t="n">
         <v>23</v>
       </c>
       <c r="BT3" t="n">
-        <v>1136.76</v>
+        <v>1222.8</v>
       </c>
       <c r="BU3" t="n">
-        <v>1004.76</v>
+        <v>1082.8</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.8075097055513655</v>
+        <v>0.808870311472011</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.8331792171098171</v>
+        <v>0.8403135793264409</v>
       </c>
       <c r="BX3" t="n">
-        <v>91.36764282664525</v>
+        <v>91.33774608119776</v>
       </c>
       <c r="BY3" t="n">
-        <v>94.96303256227638</v>
+        <v>95.49760165750136</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-3.595389735631134</v>
+        <v>-4.159855576303626</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.2826381923495995</v>
+        <v>0.2755488075901065</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.7132470414491486</v>
+        <v>0.7172054138263635</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.5026499615143817</v>
+        <v>0.4983975353250163</v>
       </c>
       <c r="CD3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -1356,244 +1356,244 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8552340941452962</v>
+        <v>0.8503861259577228</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8565393372336615</v>
+        <v>0.8756891343622798</v>
       </c>
       <c r="E4" t="n">
-        <v>96.45266167279361</v>
+        <v>96.42768440340714</v>
       </c>
       <c r="F4" t="n">
-        <v>96.18436661761011</v>
+        <v>98.58153994949302</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2682950551834975</v>
+        <v>-2.153855546085888</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2861350388654794</v>
+        <v>0.2960061101006743</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7238938050439468</v>
+        <v>0.7194365008385494</v>
       </c>
       <c r="J4" t="n">
-        <v>0.50535037336184</v>
+        <v>0.5070028612992488</v>
       </c>
       <c r="K4" t="n">
-        <v>4600</v>
+        <v>5200</v>
       </c>
       <c r="L4" t="n">
-        <v>1766</v>
+        <v>2002</v>
       </c>
       <c r="M4" t="n">
-        <v>396</v>
+        <v>456</v>
       </c>
       <c r="N4" t="n">
-        <v>837</v>
+        <v>962</v>
       </c>
       <c r="O4" t="n">
+        <v>216</v>
+      </c>
+      <c r="P4" t="n">
+        <v>694</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>442</v>
+      </c>
+      <c r="R4" t="n">
+        <v>655</v>
+      </c>
+      <c r="S4" t="n">
+        <v>280</v>
+      </c>
+      <c r="T4" t="n">
+        <v>662</v>
+      </c>
+      <c r="U4" t="n">
+        <v>365</v>
+      </c>
+      <c r="V4" t="n">
+        <v>198</v>
+      </c>
+      <c r="W4" t="n">
+        <v>411</v>
+      </c>
+      <c r="X4" t="n">
+        <v>639</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>593</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2032</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2355.2</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2075.2</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2600</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>232</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>489</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>94</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>343</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>193</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>304</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>128</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>325</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>173</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>102</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>197</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>321</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>288</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1162.76</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1034.76</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.8085345033377256</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.8701045934620747</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>90.79873177993005</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>98.1206837400087</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-7.321951960078656</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.2741416699711442</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0.7085036294565762</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0.4894488597487033</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>13</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>2600</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>224</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>473</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>122</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>351</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>249</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>351</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>152</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>337</v>
+      </c>
+      <c r="BN4" t="n">
         <v>192</v>
       </c>
-      <c r="P4" t="n">
-        <v>611</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>398</v>
-      </c>
-      <c r="R4" t="n">
-        <v>580</v>
-      </c>
-      <c r="S4" t="n">
-        <v>235</v>
-      </c>
-      <c r="T4" t="n">
-        <v>588</v>
-      </c>
-      <c r="U4" t="n">
-        <v>320</v>
-      </c>
-      <c r="V4" t="n">
-        <v>183</v>
-      </c>
-      <c r="W4" t="n">
-        <v>362</v>
-      </c>
-      <c r="X4" t="n">
-        <v>573</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>529</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1752</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2065.2</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1830.2</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2200</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>194</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>404</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>77</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>288</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>170</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>265</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>97</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>275</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>140</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>165</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>276</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>250</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>973.6</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>876.6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.8112845099956398</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.8427723790680651</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>90.0643309952619</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>94.94027726900917</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>-4.875946273747268</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0.2579706936183871</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0.7094003932538758</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0.4840333923164064</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>11</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>2400</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>202</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>433</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>115</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>323</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>228</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>315</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>138</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>313</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>180</v>
-      </c>
       <c r="BO4" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="BP4" t="n">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="BQ4" t="n">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="BR4" t="n">
-        <v>279</v>
+        <v>305</v>
       </c>
       <c r="BS4" t="n">
         <v>15</v>
       </c>
       <c r="BT4" t="n">
-        <v>1091.6</v>
+        <v>1192.44</v>
       </c>
       <c r="BU4" t="n">
-        <v>953.6</v>
+        <v>1040.44</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.8955212129491478</v>
+        <v>0.89223774857772</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.8691590488854583</v>
+        <v>0.881273675262485</v>
       </c>
       <c r="BX4" t="n">
-        <v>102.308631460531</v>
+        <v>102.0566370268842</v>
       </c>
       <c r="BY4" t="n">
-        <v>97.32478185382764</v>
+        <v>99.04239615897737</v>
       </c>
       <c r="BZ4" t="n">
-        <v>4.983849606703366</v>
+        <v>3.014240867906881</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.3119523553419807</v>
+        <v>0.3178705502302044</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.7371794325181783</v>
+        <v>0.7303693722205222</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.5248909393201541</v>
+        <v>0.5245568628497945</v>
       </c>
       <c r="CD4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -1608,244 +1608,244 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8013209404971456</v>
+        <v>0.8093353406194697</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8463740428219602</v>
+        <v>0.8609966653626249</v>
       </c>
       <c r="E5" t="n">
-        <v>89.34702561525641</v>
+        <v>90.11644051259223</v>
       </c>
       <c r="F5" t="n">
-        <v>96.99888919837541</v>
+        <v>98.64533892791329</v>
       </c>
       <c r="G5" t="n">
-        <v>-7.65186358311898</v>
+        <v>-8.528898415321011</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2478142502256003</v>
+        <v>0.2457822514283938</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6938323219520928</v>
+        <v>0.6928036337642655</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4727511565272252</v>
+        <v>0.4711222917457827</v>
       </c>
       <c r="K5" t="n">
-        <v>4400</v>
+        <v>5200</v>
       </c>
       <c r="L5" t="n">
-        <v>1539</v>
+        <v>1853</v>
       </c>
       <c r="M5" t="n">
-        <v>413</v>
+        <v>497</v>
       </c>
       <c r="N5" t="n">
-        <v>864</v>
+        <v>1024</v>
       </c>
       <c r="O5" t="n">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="P5" t="n">
-        <v>545</v>
+        <v>642</v>
       </c>
       <c r="Q5" t="n">
+        <v>358</v>
+      </c>
+      <c r="R5" t="n">
+        <v>571</v>
+      </c>
+      <c r="S5" t="n">
+        <v>234</v>
+      </c>
+      <c r="T5" t="n">
+        <v>670</v>
+      </c>
+      <c r="U5" t="n">
+        <v>348</v>
+      </c>
+      <c r="V5" t="n">
+        <v>215</v>
+      </c>
+      <c r="W5" t="n">
+        <v>380</v>
+      </c>
+      <c r="X5" t="n">
+        <v>581</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>511</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>63</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2006</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2297.24</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2063.24</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2600</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>241</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>509</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>76</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>330</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>168</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>287</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>116</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>344</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>162</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>117</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>189</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>281</v>
       </c>
-      <c r="R5" t="n">
-        <v>461</v>
-      </c>
-      <c r="S5" t="n">
-        <v>199</v>
-      </c>
-      <c r="T5" t="n">
-        <v>568</v>
-      </c>
-      <c r="U5" t="n">
-        <v>293</v>
-      </c>
-      <c r="V5" t="n">
+      <c r="AR5" t="n">
+        <v>254</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1154.28</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1038.28</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.7620710216485297</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.8321324520577057</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>84.72260324700484</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>95.22677752495207</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-10.50417427794725</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0.2277402967080216</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0.702604207094041</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.4640854807781472</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>2600</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>256</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>515</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>91</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>312</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>190</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>284</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>118</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>326</v>
+      </c>
+      <c r="BN5" t="n">
         <v>186</v>
       </c>
-      <c r="W5" t="n">
-        <v>317</v>
-      </c>
-      <c r="X5" t="n">
-        <v>487</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>420</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>57</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1662</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1928.84</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1729.84</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2400</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>218</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>465</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>72</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>306</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>152</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>261</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>105</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>318</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>150</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>108</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>173</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>261</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>231</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1058.84</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>953.84</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.7609639197224817</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.8300582054482447</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>84.47980423604744</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>94.89754631805302</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-10.4177420820056</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0.2248932579416265</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0.7055990021296555</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0.4646934272215936</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>12</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>2000</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>195</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>399</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>72</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>239</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>129</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>200</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>94</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>250</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>143</v>
-      </c>
       <c r="BO5" t="n">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="BP5" t="n">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="BQ5" t="n">
-        <v>226</v>
+        <v>300</v>
       </c>
       <c r="BR5" t="n">
-        <v>189</v>
+        <v>257</v>
       </c>
       <c r="BS5" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="BT5" t="n">
-        <v>870</v>
+        <v>1142.96</v>
       </c>
       <c r="BU5" t="n">
-        <v>776</v>
+        <v>1024.96</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.8497493654267423</v>
+        <v>0.8565996595904095</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.8659530476704186</v>
+        <v>0.889860878667544</v>
       </c>
       <c r="BX5" t="n">
-        <v>95.18769127030717</v>
+        <v>95.51027777817964</v>
       </c>
       <c r="BY5" t="n">
-        <v>99.52050065476222</v>
+        <v>102.0639003308744</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-4.332809384455037</v>
+        <v>-6.553622552694771</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.2753194409663689</v>
+        <v>0.2638242061487661</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.6797123057390178</v>
+        <v>0.6830030604344899</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.4824204316939832</v>
+        <v>0.4781591027134184</v>
       </c>
       <c r="CD5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -1860,244 +1860,244 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8789396993117592</v>
+        <v>0.8781230070652373</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8523930884133065</v>
+        <v>0.8507794575981837</v>
       </c>
       <c r="E6" t="n">
-        <v>101.0512653000211</v>
+        <v>100.6431725145976</v>
       </c>
       <c r="F6" t="n">
-        <v>96.93093791543052</v>
+        <v>96.82006944313625</v>
       </c>
       <c r="G6" t="n">
-        <v>4.12032738459059</v>
+        <v>3.823103071461313</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3117755413645598</v>
+        <v>0.3044820546954171</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6911677743245737</v>
+        <v>0.6947024297705829</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4973924544778555</v>
+        <v>0.498010127877481</v>
       </c>
       <c r="K6" t="n">
-        <v>4625</v>
+        <v>5225</v>
       </c>
       <c r="L6" t="n">
-        <v>1796</v>
+        <v>2023</v>
       </c>
       <c r="M6" t="n">
-        <v>398</v>
+        <v>447</v>
       </c>
       <c r="N6" t="n">
-        <v>838</v>
+        <v>928</v>
       </c>
       <c r="O6" t="n">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="P6" t="n">
-        <v>640</v>
+        <v>727</v>
       </c>
       <c r="Q6" t="n">
-        <v>415</v>
+        <v>463</v>
       </c>
       <c r="R6" t="n">
-        <v>576</v>
+        <v>651</v>
       </c>
       <c r="S6" t="n">
-        <v>269</v>
+        <v>296</v>
       </c>
       <c r="T6" t="n">
-        <v>562</v>
+        <v>648</v>
       </c>
       <c r="U6" t="n">
+        <v>342</v>
+      </c>
+      <c r="V6" t="n">
+        <v>223</v>
+      </c>
+      <c r="W6" t="n">
+        <v>366</v>
+      </c>
+      <c r="X6" t="n">
+        <v>546</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>580</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>88</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1984</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2307.44</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2011.44</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2625</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>228</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>464</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>104</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>359</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>256</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>348</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>141</v>
+      </c>
+      <c r="AM6" t="n">
         <v>306</v>
       </c>
-      <c r="V6" t="n">
-        <v>205</v>
-      </c>
-      <c r="W6" t="n">
-        <v>317</v>
-      </c>
-      <c r="X6" t="n">
-        <v>475</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>513</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>77</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1762</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2048.44</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1779.44</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2225</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>193</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>402</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>88</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>306</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>212</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>286</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>124</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>247</v>
-      </c>
       <c r="AN6" t="n">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="AO6" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="AP6" t="n">
-        <v>161</v>
+        <v>198</v>
       </c>
       <c r="AQ6" t="n">
-        <v>240</v>
+        <v>293</v>
       </c>
       <c r="AR6" t="n">
-        <v>251</v>
+        <v>303</v>
       </c>
       <c r="AS6" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AT6" t="n">
-        <v>994.84</v>
+        <v>1174.12</v>
       </c>
       <c r="AU6" t="n">
-        <v>870.84</v>
+        <v>1033.12</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.86869424566162</v>
+        <v>0.8735283125938645</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.9001813857681568</v>
+        <v>0.910314888971382</v>
       </c>
       <c r="AX6" t="n">
-        <v>99.21282133313046</v>
+        <v>99.28110423337732</v>
       </c>
       <c r="AY6" t="n">
-        <v>103.2737218897539</v>
+        <v>104.3378798939808</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-4.060900556623451</v>
+        <v>-5.056775660603435</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.3023873469761691</v>
+        <v>0.2935035793095058</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.6554273861291534</v>
+        <v>0.6665060997077827</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.4714508141145842</v>
+        <v>0.4779751035819058</v>
       </c>
       <c r="BD6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BE6" t="n">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="BF6" t="n">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="BG6" t="n">
-        <v>436</v>
+        <v>464</v>
       </c>
       <c r="BH6" t="n">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="BI6" t="n">
-        <v>334</v>
+        <v>368</v>
       </c>
       <c r="BJ6" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="BK6" t="n">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="BL6" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="BM6" t="n">
-        <v>315</v>
+        <v>342</v>
       </c>
       <c r="BN6" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="BO6" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="BP6" t="n">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="BQ6" t="n">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="BR6" t="n">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="BS6" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="BT6" t="n">
-        <v>1053.6</v>
+        <v>1133.32</v>
       </c>
       <c r="BU6" t="n">
-        <v>908.6</v>
+        <v>978.3199999999999</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.8883313651577199</v>
+        <v>0.8827177015366101</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.8085871491713599</v>
+        <v>0.791244026224985</v>
       </c>
       <c r="BX6" t="n">
-        <v>102.7365056030042</v>
+        <v>102.0052407958178</v>
       </c>
       <c r="BY6" t="n">
-        <v>91.11671927230073</v>
+        <v>89.30225899229175</v>
       </c>
       <c r="BZ6" t="n">
-        <v>11.61978633070346</v>
+        <v>12.70298180352606</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.3203813862205845</v>
+        <v>0.3154605300813285</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.7239297968370425</v>
+        <v>0.7228987598333834</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.5211722914775206</v>
+        <v>0.518045152173056</v>
       </c>
       <c r="CD6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -2112,244 +2112,244 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.8828071603471722</v>
+        <v>0.8819990508135221</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7480008392960273</v>
+        <v>0.7539025466562197</v>
       </c>
       <c r="E7" t="n">
-        <v>103.1750037849061</v>
+        <v>102.5853418015902</v>
       </c>
       <c r="F7" t="n">
-        <v>85.65952282289264</v>
+        <v>86.07043674439097</v>
       </c>
       <c r="G7" t="n">
-        <v>17.51548096201343</v>
+        <v>16.51490505719926</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3591586515658247</v>
+        <v>0.3464994774750537</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6909909001528111</v>
+        <v>0.6983583335188037</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5231941132847586</v>
+        <v>0.5201515690779093</v>
       </c>
       <c r="K7" t="n">
-        <v>4650</v>
+        <v>5275</v>
       </c>
       <c r="L7" t="n">
-        <v>1850</v>
+        <v>2085</v>
       </c>
       <c r="M7" t="n">
-        <v>454</v>
+        <v>509</v>
       </c>
       <c r="N7" t="n">
-        <v>914</v>
+        <v>1037</v>
       </c>
       <c r="O7" t="n">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="P7" t="n">
-        <v>632</v>
+        <v>713</v>
       </c>
       <c r="Q7" t="n">
-        <v>375</v>
+        <v>419</v>
       </c>
       <c r="R7" t="n">
-        <v>589</v>
+        <v>661</v>
       </c>
       <c r="S7" t="n">
-        <v>307</v>
+        <v>338</v>
       </c>
       <c r="T7" t="n">
-        <v>572</v>
+        <v>661</v>
       </c>
       <c r="U7" t="n">
-        <v>342</v>
+        <v>387</v>
       </c>
       <c r="V7" t="n">
-        <v>260</v>
+        <v>286</v>
       </c>
       <c r="W7" t="n">
-        <v>296</v>
+        <v>333</v>
       </c>
       <c r="X7" t="n">
-        <v>538</v>
+        <v>605</v>
       </c>
       <c r="Y7" t="n">
-        <v>509</v>
+        <v>576</v>
       </c>
       <c r="Z7" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="AA7" t="n">
-        <v>1524</v>
+        <v>1753</v>
       </c>
       <c r="AB7" t="n">
-        <v>2101.16</v>
+        <v>2373.84</v>
       </c>
       <c r="AC7" t="n">
-        <v>1794.16</v>
+        <v>2035.84</v>
       </c>
       <c r="AD7" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE7" t="n">
-        <v>2225</v>
+        <v>2650</v>
       </c>
       <c r="AF7" t="n">
+        <v>239</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>503</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>123</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>367</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>216</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>351</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>172</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>330</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>191</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>123</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>161</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>310</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>302</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>41</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1185.44</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1013.44</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.9022662163080415</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.7716813977153668</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>105.2381379045895</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>89.84993403968014</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>15.38820386490931</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.3507068833411544</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.6650525253810038</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.5112820377229331</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>13</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>2625</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>270</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>534</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>93</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>346</v>
+      </c>
+      <c r="BJ7" t="n">
         <v>203</v>
       </c>
-      <c r="AG7" t="n">
-        <v>423</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>105</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>311</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>189</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>307</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>149</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>266</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>162</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>107</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>135</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>266</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>257</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1004.08</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>855.08</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0.9090901349216334</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0.7725100510678167</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>106.5743399536909</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>90.05926312319251</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>16.51507683049837</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0.3660971155739813</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0.6584750752269134</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0.5141991181747219</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>11</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>2425</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>251</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>491</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>84</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>321</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>186</v>
-      </c>
       <c r="BK7" t="n">
-        <v>282</v>
+        <v>310</v>
       </c>
       <c r="BL7" t="n">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="BM7" t="n">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="BN7" t="n">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="BO7" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="BP7" t="n">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="BQ7" t="n">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="BR7" t="n">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="BS7" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="BT7" t="n">
-        <v>1097.08</v>
+        <v>1188.4</v>
       </c>
       <c r="BU7" t="n">
-        <v>939.0799999999999</v>
+        <v>1022.4</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.858714433653916</v>
+        <v>0.8617318853190028</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.7255340618385538</v>
+        <v>0.7361236955970727</v>
       </c>
       <c r="BX7" t="n">
-        <v>100.0589456301867</v>
+        <v>99.93254569859103</v>
       </c>
       <c r="BY7" t="n">
-        <v>81.62642754761778</v>
+        <v>82.29093944910181</v>
       </c>
       <c r="BZ7" t="n">
-        <v>18.43251808256892</v>
+        <v>17.6416062494892</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.352798392891681</v>
+        <v>0.342292071608953</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.7207970730015508</v>
+        <v>0.731664141656604</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.5314395254689591</v>
+        <v>0.5290211004328853</v>
       </c>
       <c r="CD7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -2364,244 +2364,244 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9498924400998298</v>
+        <v>0.9508202761597372</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8675705963652832</v>
+        <v>0.8674294242900278</v>
       </c>
       <c r="E8" t="n">
-        <v>108.6539176433104</v>
+        <v>109.1186299566897</v>
       </c>
       <c r="F8" t="n">
-        <v>97.83594119831035</v>
+        <v>98.36768304006003</v>
       </c>
       <c r="G8" t="n">
-        <v>10.81797644500007</v>
+        <v>10.75094691662964</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3331446662062285</v>
+        <v>0.3382641155878053</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7044592023015666</v>
+        <v>0.6983459352710043</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5193890115807258</v>
+        <v>0.5193284412941437</v>
       </c>
       <c r="K8" t="n">
-        <v>4600</v>
+        <v>5200</v>
       </c>
       <c r="L8" t="n">
-        <v>2043</v>
+        <v>2312</v>
       </c>
       <c r="M8" t="n">
-        <v>505</v>
+        <v>570</v>
       </c>
       <c r="N8" t="n">
-        <v>914</v>
+        <v>1028</v>
       </c>
       <c r="O8" t="n">
-        <v>229</v>
+        <v>257</v>
       </c>
       <c r="P8" t="n">
-        <v>656</v>
+        <v>745</v>
       </c>
       <c r="Q8" t="n">
-        <v>346</v>
+        <v>401</v>
       </c>
       <c r="R8" t="n">
-        <v>546</v>
+        <v>640</v>
       </c>
       <c r="S8" t="n">
-        <v>268</v>
+        <v>311</v>
       </c>
       <c r="T8" t="n">
-        <v>569</v>
+        <v>651</v>
       </c>
       <c r="U8" t="n">
-        <v>365</v>
+        <v>419</v>
       </c>
       <c r="V8" t="n">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="W8" t="n">
-        <v>337</v>
+        <v>374</v>
       </c>
       <c r="X8" t="n">
-        <v>516</v>
+        <v>574</v>
       </c>
       <c r="Y8" t="n">
-        <v>496</v>
+        <v>566</v>
       </c>
       <c r="Z8" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="AA8" t="n">
-        <v>1803</v>
+        <v>2047</v>
       </c>
       <c r="AB8" t="n">
-        <v>2147.24</v>
+        <v>2428.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>1879.24</v>
+        <v>2117.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE8" t="n">
-        <v>2200</v>
+        <v>2600</v>
       </c>
       <c r="AF8" t="n">
-        <v>225</v>
+        <v>264</v>
       </c>
       <c r="AG8" t="n">
-        <v>430</v>
+        <v>506</v>
       </c>
       <c r="AH8" t="n">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="AI8" t="n">
-        <v>316</v>
+        <v>369</v>
       </c>
       <c r="AJ8" t="n">
-        <v>164</v>
+        <v>206</v>
       </c>
       <c r="AK8" t="n">
-        <v>275</v>
+        <v>345</v>
       </c>
       <c r="AL8" t="n">
+        <v>155</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>292</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>198</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>117</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>171</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>286</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>303</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1197.8</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1042.8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.9151373533984545</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.9102422138379187</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>104.9826323434091</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>103.0204244436369</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>1.96220789977212</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0.3221722276709489</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0.68128601930109</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0.4934027700661715</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>2600</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>306</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>522</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>136</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>376</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>195</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>295</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>156</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>359</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>221</v>
+      </c>
+      <c r="BO8" t="n">
         <v>124</v>
       </c>
-      <c r="AM8" t="n">
-        <v>236</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>172</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>111</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>142</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>249</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>252</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1009</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>885</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0.9253628591597004</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0.9093653200407121</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>105.4136550526525</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>102.410289398452</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>3.003365654200495</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0.3089596745490724</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0.6811995161557435</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0.4853324056179123</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>11</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>2400</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>280</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>484</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>122</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>340</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>182</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>271</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>144</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>333</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>193</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>113</v>
-      </c>
       <c r="BP8" t="n">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="BQ8" t="n">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="BR8" t="n">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="BS8" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="BT8" t="n">
-        <v>1138.24</v>
+        <v>1230.8</v>
       </c>
       <c r="BU8" t="n">
-        <v>994.24</v>
+        <v>1074.8</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.9723778892949483</v>
+        <v>0.9865031989210201</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.8292587663294735</v>
+        <v>0.8246166347421369</v>
       </c>
       <c r="BX8" t="n">
-        <v>111.6241583514135</v>
+        <v>113.2546275699703</v>
       </c>
       <c r="BY8" t="n">
-        <v>93.64278868151382</v>
+        <v>93.71494163648312</v>
       </c>
       <c r="BZ8" t="n">
-        <v>17.98136966989969</v>
+        <v>19.53968593348717</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.3553142418919549</v>
+        <v>0.3543560035046616</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.725780581268571</v>
+        <v>0.7154058512409188</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.5506075670466384</v>
+        <v>0.5452541125221161</v>
       </c>
       <c r="CD8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -2616,244 +2616,244 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.8743831858975031</v>
+        <v>0.8851124994947063</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8871317244136425</v>
+        <v>0.8853269213640691</v>
       </c>
       <c r="E9" t="n">
-        <v>98.91306997899575</v>
+        <v>100.5253994403985</v>
       </c>
       <c r="F9" t="n">
-        <v>101.8519472883067</v>
+        <v>101.5798847385439</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.938877309310904</v>
+        <v>-1.054485298145323</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2950500651704123</v>
+        <v>0.3008013916770834</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6671307425308836</v>
+        <v>0.6699312856698718</v>
       </c>
       <c r="J9" t="n">
-        <v>0.477416168048935</v>
+        <v>0.482335915248586</v>
       </c>
       <c r="K9" t="n">
-        <v>4675</v>
+        <v>5275</v>
       </c>
       <c r="L9" t="n">
-        <v>1845</v>
+        <v>2116</v>
       </c>
       <c r="M9" t="n">
-        <v>445</v>
+        <v>497</v>
       </c>
       <c r="N9" t="n">
-        <v>917</v>
+        <v>1026</v>
       </c>
       <c r="O9" t="n">
-        <v>188</v>
+        <v>224</v>
       </c>
       <c r="P9" t="n">
-        <v>620</v>
+        <v>715</v>
       </c>
       <c r="Q9" t="n">
-        <v>391</v>
+        <v>450</v>
       </c>
       <c r="R9" t="n">
-        <v>550</v>
+        <v>633</v>
       </c>
       <c r="S9" t="n">
-        <v>256</v>
+        <v>296</v>
       </c>
       <c r="T9" t="n">
-        <v>555</v>
+        <v>637</v>
       </c>
       <c r="U9" t="n">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="V9" t="n">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="W9" t="n">
-        <v>349</v>
+        <v>389</v>
       </c>
       <c r="X9" t="n">
-        <v>588</v>
+        <v>672</v>
       </c>
       <c r="Y9" t="n">
-        <v>501</v>
+        <v>565</v>
       </c>
       <c r="Z9" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AA9" t="n">
-        <v>1891</v>
+        <v>2143</v>
       </c>
       <c r="AB9" t="n">
-        <v>2128</v>
+        <v>2408.52</v>
       </c>
       <c r="AC9" t="n">
-        <v>1872</v>
+        <v>2112.52</v>
       </c>
       <c r="AD9" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE9" t="n">
-        <v>2450</v>
+        <v>2650</v>
       </c>
       <c r="AF9" t="n">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="AG9" t="n">
-        <v>498</v>
+        <v>535</v>
       </c>
       <c r="AH9" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="AI9" t="n">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="AJ9" t="n">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="AK9" t="n">
+        <v>313</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>149</v>
+      </c>
+      <c r="AM9" t="n">
         <v>289</v>
       </c>
-      <c r="AL9" t="n">
-        <v>136</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>267</v>
-      </c>
       <c r="AN9" t="n">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="AO9" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AP9" t="n">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="AQ9" t="n">
-        <v>307</v>
+        <v>339</v>
       </c>
       <c r="AR9" t="n">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="AS9" t="n">
         <v>19</v>
       </c>
       <c r="AT9" t="n">
-        <v>1109.16</v>
+        <v>1200.72</v>
       </c>
       <c r="AU9" t="n">
-        <v>973.16</v>
+        <v>1051.72</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.8648878557140557</v>
+        <v>0.8773310354119596</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.9003691964642723</v>
+        <v>0.8967128102839887</v>
       </c>
       <c r="AX9" t="n">
-        <v>97.82823662169959</v>
+        <v>99.507123637013</v>
       </c>
       <c r="AY9" t="n">
-        <v>102.7915409895599</v>
+        <v>102.5023996690648</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-4.963304367860325</v>
+        <v>-2.995276032051767</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.2887438766485061</v>
+        <v>0.2935598362410327</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.6564040784806914</v>
+        <v>0.6529200040676468</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.4602884608065301</v>
+        <v>0.4617625834209909</v>
       </c>
       <c r="BD9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BE9" t="n">
-        <v>2225</v>
+        <v>2625</v>
       </c>
       <c r="BF9" t="n">
-        <v>209</v>
+        <v>242</v>
       </c>
       <c r="BG9" t="n">
-        <v>419</v>
+        <v>491</v>
       </c>
       <c r="BH9" t="n">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="BI9" t="n">
-        <v>309</v>
+        <v>372</v>
       </c>
       <c r="BJ9" t="n">
-        <v>185</v>
+        <v>224</v>
       </c>
       <c r="BK9" t="n">
-        <v>261</v>
+        <v>320</v>
       </c>
       <c r="BL9" t="n">
+        <v>147</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>348</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>152</v>
+      </c>
+      <c r="BO9" t="n">
         <v>120</v>
       </c>
-      <c r="BM9" t="n">
-        <v>288</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>125</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>98</v>
-      </c>
       <c r="BP9" t="n">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="BQ9" t="n">
-        <v>281</v>
+        <v>333</v>
       </c>
       <c r="BR9" t="n">
-        <v>247</v>
+        <v>292</v>
       </c>
       <c r="BS9" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="BT9" t="n">
-        <v>1018.84</v>
+        <v>1207.8</v>
       </c>
       <c r="BU9" t="n">
-        <v>898.8399999999999</v>
+        <v>1060.8</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.8847417279158093</v>
+        <v>0.8928939635774529</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.8726908458129556</v>
+        <v>0.8739410324441496</v>
       </c>
       <c r="BX9" t="n">
-        <v>100.0965245505916</v>
+        <v>101.543675243784</v>
       </c>
       <c r="BY9" t="n">
-        <v>100.8269359778485</v>
+        <v>100.6573698080229</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0.7304114272569897</v>
+        <v>0.8863054357611205</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.3019295435579464</v>
+        <v>0.3080429471131341</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.6788325578583657</v>
+        <v>0.6869425672720971</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.496100939586104</v>
+        <v>0.502909247076181</v>
       </c>
       <c r="CD9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -2868,244 +2868,244 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.8244978657817087</v>
+        <v>0.815393940275086</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8627134383910202</v>
+        <v>0.8531220170159555</v>
       </c>
       <c r="E10" t="n">
-        <v>93.14777181756794</v>
+        <v>92.06021312986337</v>
       </c>
       <c r="F10" t="n">
-        <v>96.44763743093011</v>
+        <v>95.70468443291246</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.299865613362164</v>
+        <v>-3.644471303049055</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2873365030019487</v>
+        <v>0.2821226368902643</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7280343538032615</v>
+        <v>0.7190402582115577</v>
       </c>
       <c r="J10" t="n">
-        <v>0.500313570613112</v>
+        <v>0.4924513729931247</v>
       </c>
       <c r="K10" t="n">
-        <v>4875</v>
+        <v>5275</v>
       </c>
       <c r="L10" t="n">
-        <v>1822</v>
+        <v>1948</v>
       </c>
       <c r="M10" t="n">
-        <v>456</v>
+        <v>487</v>
       </c>
       <c r="N10" t="n">
-        <v>961</v>
+        <v>1042</v>
       </c>
       <c r="O10" t="n">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="P10" t="n">
-        <v>612</v>
+        <v>659</v>
       </c>
       <c r="Q10" t="n">
-        <v>376</v>
+        <v>407</v>
       </c>
       <c r="R10" t="n">
-        <v>573</v>
+        <v>627</v>
       </c>
       <c r="S10" t="n">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="T10" t="n">
-        <v>606</v>
+        <v>650</v>
       </c>
       <c r="U10" t="n">
-        <v>373</v>
+        <v>399</v>
       </c>
       <c r="V10" t="n">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="W10" t="n">
-        <v>394</v>
+        <v>421</v>
       </c>
       <c r="X10" t="n">
-        <v>532</v>
+        <v>579</v>
       </c>
       <c r="Y10" t="n">
-        <v>524</v>
+        <v>569</v>
       </c>
       <c r="Z10" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AA10" t="n">
-        <v>1874</v>
+        <v>2012</v>
       </c>
       <c r="AB10" t="n">
-        <v>2219.12</v>
+        <v>2397.88</v>
       </c>
       <c r="AC10" t="n">
-        <v>1960.12</v>
+        <v>2118.88</v>
       </c>
       <c r="AD10" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE10" t="n">
-        <v>2450</v>
+        <v>2650</v>
       </c>
       <c r="AF10" t="n">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="AG10" t="n">
-        <v>486</v>
+        <v>527</v>
       </c>
       <c r="AH10" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="AI10" t="n">
+        <v>325</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>207</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>328</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>155</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>329</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>194</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>139</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>223</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>286</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>290</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1219.32</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1064.32</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.7704055297083436</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.8502178438453998</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>88.01621055176426</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>95.0581898180404</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-7.041979266276147</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0.2959223096112322</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0.7333914426671048</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0.4991167418983916</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>13</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>2625</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>260</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>515</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>97</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>334</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>200</v>
+      </c>
+      <c r="BK10" t="n">
         <v>299</v>
       </c>
-      <c r="AJ10" t="n">
-        <v>194</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>298</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>142</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>308</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>185</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>128</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>213</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>262</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>265</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1129.12</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>987.12</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0.7874884738876604</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0.8640924156729811</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>89.845713417261</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>96.15271479759168</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>-6.307001380330674</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0.2993406720134754</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>0.7458962851115857</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>0.5081427539148284</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>12</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>2425</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>242</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>475</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>90</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>313</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>182</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>275</v>
-      </c>
       <c r="BL10" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="BM10" t="n">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="BN10" t="n">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="BO10" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="BP10" t="n">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="BQ10" t="n">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="BR10" t="n">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="BS10" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BT10" t="n">
-        <v>1090</v>
+        <v>1178.56</v>
       </c>
       <c r="BU10" t="n">
-        <v>973</v>
+        <v>1054.56</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.8615072576757571</v>
+        <v>0.8603823508418287</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.8613344611090591</v>
+        <v>0.8560261901865106</v>
       </c>
       <c r="BX10" t="n">
-        <v>96.44983021787486</v>
+        <v>96.1042157079625</v>
       </c>
       <c r="BY10" t="n">
-        <v>96.74256006426852</v>
+        <v>96.35117904778447</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0.292729846393654</v>
+        <v>-0.2469633398219621</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.2753323339904222</v>
+        <v>0.2683229641692966</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.7101724224949377</v>
+        <v>0.704689073756011</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.4924843873113957</v>
+        <v>0.485786004087858</v>
       </c>
       <c r="CD10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -3120,244 +3120,244 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8595718085586398</v>
+        <v>0.8568637676593924</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8842453853900665</v>
+        <v>0.8808460175277355</v>
       </c>
       <c r="E11" t="n">
-        <v>98.26502607392173</v>
+        <v>97.64868734406079</v>
       </c>
       <c r="F11" t="n">
-        <v>99.24601979626637</v>
+        <v>98.61286341537733</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9809937223446218</v>
+        <v>-0.9641760713165357</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3168664644506192</v>
+        <v>0.3111572794023815</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7229545516160432</v>
+        <v>0.7307362586818539</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5184012440529205</v>
+        <v>0.5212916719275295</v>
       </c>
       <c r="K11" t="n">
-        <v>4825</v>
+        <v>5225</v>
       </c>
       <c r="L11" t="n">
-        <v>1860</v>
+        <v>2004</v>
       </c>
       <c r="M11" t="n">
-        <v>463</v>
+        <v>501</v>
       </c>
       <c r="N11" t="n">
-        <v>939</v>
+        <v>1021</v>
       </c>
       <c r="O11" t="n">
+        <v>203</v>
+      </c>
+      <c r="P11" t="n">
+        <v>647</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>393</v>
+      </c>
+      <c r="R11" t="n">
+        <v>601</v>
+      </c>
+      <c r="S11" t="n">
+        <v>282</v>
+      </c>
+      <c r="T11" t="n">
+        <v>652</v>
+      </c>
+      <c r="U11" t="n">
+        <v>350</v>
+      </c>
+      <c r="V11" t="n">
+        <v>222</v>
+      </c>
+      <c r="W11" t="n">
+        <v>400</v>
+      </c>
+      <c r="X11" t="n">
+        <v>587</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>549</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2332.44</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2050.44</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2600</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>257</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>510</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>93</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>310</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>199</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>295</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>132</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>336</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>172</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>213</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>285</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>268</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1162.8</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1030.8</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.8507886981797715</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.8660076514606458</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>95.92948014472007</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>98.64720228238664</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-2.717722137666577</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.2898194527528262</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.7036974110277008</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.5035243929724618</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>2625</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>244</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>511</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>110</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>337</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>194</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>306</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>150</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>316</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>178</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>112</v>
+      </c>
+      <c r="BP11" t="n">
         <v>187</v>
       </c>
-      <c r="P11" t="n">
-        <v>600</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>373</v>
-      </c>
-      <c r="R11" t="n">
-        <v>570</v>
-      </c>
-      <c r="S11" t="n">
-        <v>267</v>
-      </c>
-      <c r="T11" t="n">
-        <v>592</v>
-      </c>
-      <c r="U11" t="n">
-        <v>325</v>
-      </c>
-      <c r="V11" t="n">
-        <v>209</v>
-      </c>
-      <c r="W11" t="n">
-        <v>368</v>
-      </c>
-      <c r="X11" t="n">
-        <v>544</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>513</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>51</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1881</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2157.8</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1890.8</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2400</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>233</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>464</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>85</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>289</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>190</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>278</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>124</v>
-      </c>
-      <c r="AM11" t="n">
+      <c r="BQ11" t="n">
         <v>302</v>
       </c>
-      <c r="AN11" t="n">
-        <v>157</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>106</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>200</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>265</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>251</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1075.32</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>951.3199999999999</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0.8445272625342586</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0.8694084905390532</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>95.43090092342997</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>99.28622037793322</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>-3.855319454503253</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0.2943632306783068</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>0.6948785444863583</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>0.4994321274745528</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>12</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>2425</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>230</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>475</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>102</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>311</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>183</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>292</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>143</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>290</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>168</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>103</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>168</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>279</v>
-      </c>
       <c r="BR11" t="n">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="BS11" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BT11" t="n">
-        <v>1082.48</v>
+        <v>1169.64</v>
       </c>
       <c r="BU11" t="n">
-        <v>939.48</v>
+        <v>1019.64</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.8746163545830208</v>
+        <v>0.8629388371390133</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.8990822802410793</v>
+        <v>0.8956843835948244</v>
       </c>
       <c r="BX11" t="n">
-        <v>101.0991512244135</v>
+        <v>99.36789454340149</v>
       </c>
       <c r="BY11" t="n">
-        <v>99.20581921459949</v>
+        <v>98.57852454836799</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.893332009814009</v>
+        <v>0.7893699950335061</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.3393696982229317</v>
+        <v>0.3324951060519369</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.7510305587457284</v>
+        <v>0.7577751063360073</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.537370360631288</v>
+        <v>0.539058950882597</v>
       </c>
       <c r="CD11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -3372,244 +3372,244 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.8344884557429629</v>
+        <v>0.8486119692410194</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8258706688338877</v>
+        <v>0.8224757533433978</v>
       </c>
       <c r="E12" t="n">
-        <v>93.86452312443944</v>
+        <v>95.33349282940951</v>
       </c>
       <c r="F12" t="n">
-        <v>95.4950585621211</v>
+        <v>94.8908382387215</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.630535437681617</v>
+        <v>0.4426545906880287</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2764633888682166</v>
+        <v>0.2795904190378659</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6826238958438676</v>
+        <v>0.6863655445176248</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4915062413579238</v>
+        <v>0.4960995852523127</v>
       </c>
       <c r="K12" t="n">
-        <v>4650</v>
+        <v>5250</v>
       </c>
       <c r="L12" t="n">
-        <v>1722</v>
+        <v>1985</v>
       </c>
       <c r="M12" t="n">
-        <v>406</v>
+        <v>473</v>
       </c>
       <c r="N12" t="n">
-        <v>843</v>
+        <v>970</v>
       </c>
       <c r="O12" t="n">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="P12" t="n">
-        <v>587</v>
+        <v>668</v>
       </c>
       <c r="Q12" t="n">
-        <v>397</v>
+        <v>436</v>
       </c>
       <c r="R12" t="n">
-        <v>621</v>
+        <v>682</v>
       </c>
       <c r="S12" t="n">
-        <v>235</v>
+        <v>264</v>
       </c>
       <c r="T12" t="n">
-        <v>624</v>
+        <v>707</v>
       </c>
       <c r="U12" t="n">
-        <v>362</v>
+        <v>426</v>
       </c>
       <c r="V12" t="n">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="W12" t="n">
-        <v>369</v>
+        <v>410</v>
       </c>
       <c r="X12" t="n">
-        <v>467</v>
+        <v>532</v>
       </c>
       <c r="Y12" t="n">
-        <v>514</v>
+        <v>575</v>
       </c>
       <c r="Z12" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AA12" t="n">
-        <v>1758</v>
+        <v>1979</v>
       </c>
       <c r="AB12" t="n">
-        <v>2072.24</v>
+        <v>2348.08</v>
       </c>
       <c r="AC12" t="n">
-        <v>1837.24</v>
+        <v>2084.08</v>
       </c>
       <c r="AD12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE12" t="n">
-        <v>2425</v>
+        <v>2625</v>
       </c>
       <c r="AF12" t="n">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="AG12" t="n">
-        <v>438</v>
+        <v>475</v>
       </c>
       <c r="AH12" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="AI12" t="n">
-        <v>297</v>
+        <v>330</v>
       </c>
       <c r="AJ12" t="n">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="AK12" t="n">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="AL12" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="AM12" t="n">
-        <v>324</v>
+        <v>355</v>
       </c>
       <c r="AN12" t="n">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="AO12" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="AP12" t="n">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="AQ12" t="n">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="AR12" t="n">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="AS12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AT12" t="n">
-        <v>1075.68</v>
+        <v>1171.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>954.6799999999999</v>
+        <v>1037.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.8160613960742603</v>
+        <v>0.8142356686159271</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.8224792995606204</v>
+        <v>0.8243565433509333</v>
       </c>
       <c r="AX12" t="n">
-        <v>91.48743469065387</v>
+        <v>91.50029408752479</v>
       </c>
       <c r="AY12" t="n">
-        <v>95.3525632476384</v>
+        <v>95.0913538892827</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-3.865128556984502</v>
+        <v>-3.591059801757874</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.2581560254310034</v>
+        <v>0.2660756474063963</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.6820901998943221</v>
+        <v>0.6923747594166212</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.4793290226874696</v>
+        <v>0.4881956051418638</v>
       </c>
       <c r="BD12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BE12" t="n">
-        <v>2225</v>
+        <v>2625</v>
       </c>
       <c r="BF12" t="n">
-        <v>205</v>
+        <v>253</v>
       </c>
       <c r="BG12" t="n">
-        <v>405</v>
+        <v>495</v>
       </c>
       <c r="BH12" t="n">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="BI12" t="n">
-        <v>290</v>
+        <v>338</v>
       </c>
       <c r="BJ12" t="n">
-        <v>179</v>
+        <v>207</v>
       </c>
       <c r="BK12" t="n">
-        <v>274</v>
+        <v>317</v>
       </c>
       <c r="BL12" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="BM12" t="n">
-        <v>300</v>
+        <v>352</v>
       </c>
       <c r="BN12" t="n">
-        <v>181</v>
+        <v>228</v>
       </c>
       <c r="BO12" t="n">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="BP12" t="n">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="BQ12" t="n">
-        <v>232</v>
+        <v>276</v>
       </c>
       <c r="BR12" t="n">
-        <v>230</v>
+        <v>269</v>
       </c>
       <c r="BS12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BT12" t="n">
-        <v>996.5599999999999</v>
+        <v>1176.48</v>
       </c>
       <c r="BU12" t="n">
-        <v>882.5599999999999</v>
+        <v>1046.48</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.8545907026542751</v>
+        <v>0.8829882698661117</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.8295703444047248</v>
+        <v>0.8205949633358625</v>
       </c>
       <c r="BX12" t="n">
-        <v>96.45771050675101</v>
+        <v>99.16669157129422</v>
       </c>
       <c r="BY12" t="n">
-        <v>95.65050799610221</v>
+        <v>94.6903225881603</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.8072025106488018</v>
+        <v>4.476368983133932</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.2964350580724492</v>
+        <v>0.2931051906693355</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.6832061096070086</v>
+        <v>0.6803563296186286</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.5047904799075101</v>
+        <v>0.5040035653627617</v>
       </c>
       <c r="CD12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -3624,244 +3624,244 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.7674620764038266</v>
+        <v>0.7571515140951827</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8314247400423675</v>
+        <v>0.8205752961021791</v>
       </c>
       <c r="E13" t="n">
-        <v>87.29471229001534</v>
+        <v>86.32791233292218</v>
       </c>
       <c r="F13" t="n">
-        <v>94.8558899011672</v>
+        <v>93.68590757320759</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.561177611151865</v>
+        <v>-7.357995240285392</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3022113333042626</v>
+        <v>0.3061235519299806</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7160708261193905</v>
+        <v>0.718245677295031</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5207853449394354</v>
+        <v>0.5241355461663776</v>
       </c>
       <c r="K13" t="n">
-        <v>4825</v>
+        <v>5225</v>
       </c>
       <c r="L13" t="n">
-        <v>1661</v>
+        <v>1770</v>
       </c>
       <c r="M13" t="n">
-        <v>442</v>
+        <v>477</v>
       </c>
       <c r="N13" t="n">
-        <v>970</v>
+        <v>1043</v>
       </c>
       <c r="O13" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="P13" t="n">
-        <v>510</v>
+        <v>558</v>
       </c>
       <c r="Q13" t="n">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="R13" t="n">
-        <v>603</v>
+        <v>640</v>
       </c>
       <c r="S13" t="n">
-        <v>261</v>
+        <v>287</v>
       </c>
       <c r="T13" t="n">
-        <v>695</v>
+        <v>762</v>
       </c>
       <c r="U13" t="n">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="V13" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="W13" t="n">
-        <v>412</v>
+        <v>446</v>
       </c>
       <c r="X13" t="n">
-        <v>519</v>
+        <v>559</v>
       </c>
       <c r="Y13" t="n">
-        <v>544</v>
+        <v>585</v>
       </c>
       <c r="Z13" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AA13" t="n">
-        <v>1834</v>
+        <v>1950</v>
       </c>
       <c r="AB13" t="n">
-        <v>2157.32</v>
+        <v>2328.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>1896.32</v>
+        <v>2041.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE13" t="n">
-        <v>2425</v>
+        <v>2625</v>
       </c>
       <c r="AF13" t="n">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="AG13" t="n">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="AH13" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="AI13" t="n">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="AJ13" t="n">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="AK13" t="n">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="AL13" t="n">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="AM13" t="n">
-        <v>326</v>
+        <v>355</v>
       </c>
       <c r="AN13" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="AO13" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="AP13" t="n">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="AQ13" t="n">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="AR13" t="n">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="AS13" t="n">
         <v>38</v>
       </c>
       <c r="AT13" t="n">
-        <v>1085.56</v>
+        <v>1166.16</v>
       </c>
       <c r="AU13" t="n">
-        <v>958.5600000000001</v>
+        <v>1028.16</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.7653611366322367</v>
+        <v>0.7513430915734868</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.8817266943656207</v>
+        <v>0.8766210823439031</v>
       </c>
       <c r="AX13" t="n">
-        <v>86.6650330642846</v>
+        <v>85.19301018489224</v>
       </c>
       <c r="AY13" t="n">
-        <v>100.5756422931646</v>
+        <v>100.0105977405813</v>
       </c>
       <c r="AZ13" t="n">
-        <v>-13.91060922887999</v>
+        <v>-14.81758755568901</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.2904720823118913</v>
+        <v>0.2903952824579402</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.6977255755354709</v>
+        <v>0.7012535884627226</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.4976752902317338</v>
+        <v>0.4993526155585635</v>
       </c>
       <c r="BD13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BE13" t="n">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="BF13" t="n">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="BG13" t="n">
-        <v>478</v>
+        <v>515</v>
       </c>
       <c r="BH13" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="BI13" t="n">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="BJ13" t="n">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="BK13" t="n">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="BL13" t="n">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="BM13" t="n">
-        <v>369</v>
+        <v>407</v>
       </c>
       <c r="BN13" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="BO13" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="BP13" t="n">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="BQ13" t="n">
-        <v>270</v>
+        <v>295</v>
       </c>
       <c r="BR13" t="n">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="BS13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BT13" t="n">
-        <v>1071.76</v>
+        <v>1162.44</v>
       </c>
       <c r="BU13" t="n">
-        <v>937.76</v>
+        <v>1013.44</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.7695630161754164</v>
+        <v>0.7629599366168786</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.7811227857191141</v>
+        <v>0.7645295098604545</v>
       </c>
       <c r="BX13" t="n">
-        <v>87.92439151574608</v>
+        <v>87.46281448095215</v>
       </c>
       <c r="BY13" t="n">
-        <v>89.13613750916981</v>
+        <v>87.36121740583391</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-1.211745993423738</v>
+        <v>0.1015970751182286</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.3139505842966339</v>
+        <v>0.321851821402021</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.7344160767033108</v>
+        <v>0.7352377661273397</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.5438953996471366</v>
+        <v>0.5489184767741915</v>
       </c>
       <c r="CD13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -3876,244 +3876,244 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.8841073466417416</v>
+        <v>0.8789902860108645</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7903167332214046</v>
+        <v>0.7882243306054743</v>
       </c>
       <c r="E14" t="n">
-        <v>102.1843417754275</v>
+        <v>101.5299692112633</v>
       </c>
       <c r="F14" t="n">
-        <v>88.54703494699572</v>
+        <v>88.56317370801952</v>
       </c>
       <c r="G14" t="n">
-        <v>13.63730682843183</v>
+        <v>12.96679550324382</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3450800561444543</v>
+        <v>0.3380525198538998</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7301646981397005</v>
+        <v>0.724822358722361</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5336018498597763</v>
+        <v>0.5266896489759472</v>
       </c>
       <c r="K14" t="n">
-        <v>4800</v>
+        <v>5200</v>
       </c>
       <c r="L14" t="n">
-        <v>1929</v>
+        <v>2073</v>
       </c>
       <c r="M14" t="n">
-        <v>462</v>
+        <v>497</v>
       </c>
       <c r="N14" t="n">
-        <v>955</v>
+        <v>1035</v>
       </c>
       <c r="O14" t="n">
+        <v>201</v>
+      </c>
+      <c r="P14" t="n">
+        <v>645</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>476</v>
+      </c>
+      <c r="R14" t="n">
+        <v>704</v>
+      </c>
+      <c r="S14" t="n">
+        <v>324</v>
+      </c>
+      <c r="T14" t="n">
+        <v>642</v>
+      </c>
+      <c r="U14" t="n">
+        <v>402</v>
+      </c>
+      <c r="V14" t="n">
+        <v>260</v>
+      </c>
+      <c r="W14" t="n">
+        <v>378</v>
+      </c>
+      <c r="X14" t="n">
+        <v>566</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>597</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1796</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2367.76</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2043.76</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2600</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>242</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>499</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>93</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>312</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>242</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>357</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>151</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>302</v>
+      </c>
+      <c r="AN14" t="n">
         <v>186</v>
       </c>
-      <c r="P14" t="n">
-        <v>581</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>447</v>
-      </c>
-      <c r="R14" t="n">
-        <v>666</v>
-      </c>
-      <c r="S14" t="n">
-        <v>301</v>
-      </c>
-      <c r="T14" t="n">
-        <v>597</v>
-      </c>
-      <c r="U14" t="n">
-        <v>377</v>
-      </c>
-      <c r="V14" t="n">
-        <v>243</v>
-      </c>
-      <c r="W14" t="n">
-        <v>362</v>
-      </c>
-      <c r="X14" t="n">
-        <v>522</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>558</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1656</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2191.04</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1890.04</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2400</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>227</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>464</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>87</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>290</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>220</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>330</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>146</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>281</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>178</v>
-      </c>
       <c r="AO14" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="AP14" t="n">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="AQ14" t="n">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="AR14" t="n">
-        <v>275</v>
+        <v>298</v>
       </c>
       <c r="AS14" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AT14" t="n">
-        <v>1091.2</v>
+        <v>1173.08</v>
       </c>
       <c r="AU14" t="n">
-        <v>945.2</v>
+        <v>1022.08</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.8579125355168932</v>
+        <v>0.8576815423109602</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.8001294364521695</v>
+        <v>0.7941816819413042</v>
       </c>
       <c r="AX14" t="n">
-        <v>99.14644894654832</v>
+        <v>98.52372122401306</v>
       </c>
       <c r="AY14" t="n">
-        <v>90.47100931146706</v>
+        <v>89.55730200837401</v>
       </c>
       <c r="AZ14" t="n">
-        <v>8.675439635081265</v>
+        <v>8.966419215639053</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.3391079582810658</v>
+        <v>0.3254296786118027</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.6987378860353025</v>
+        <v>0.7026811255710486</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.5115993662105542</v>
+        <v>0.5061438738944881</v>
       </c>
       <c r="BD14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BE14" t="n">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="BF14" t="n">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="BG14" t="n">
-        <v>491</v>
+        <v>536</v>
       </c>
       <c r="BH14" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="BI14" t="n">
-        <v>291</v>
+        <v>333</v>
       </c>
       <c r="BJ14" t="n">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="BK14" t="n">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="BL14" t="n">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="BM14" t="n">
-        <v>316</v>
+        <v>340</v>
       </c>
       <c r="BN14" t="n">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="BO14" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="BP14" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="BQ14" t="n">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="BR14" t="n">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="BS14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BT14" t="n">
-        <v>1099.84</v>
+        <v>1194.68</v>
       </c>
       <c r="BU14" t="n">
-        <v>944.84</v>
+        <v>1021.68</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.9103021577665901</v>
+        <v>0.9002990297107686</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.7805040299906394</v>
+        <v>0.7822669792696437</v>
       </c>
       <c r="BX14" t="n">
-        <v>105.2222346043068</v>
+        <v>104.5362171985136</v>
       </c>
       <c r="BY14" t="n">
-        <v>86.62306058252437</v>
+        <v>87.56904540766499</v>
       </c>
       <c r="BZ14" t="n">
-        <v>18.5991740217824</v>
+        <v>16.96717179084859</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.3510521540078428</v>
+        <v>0.3506753610959969</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.7615915102440985</v>
+        <v>0.7469635918736733</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.5556043335089983</v>
+        <v>0.547235424057406</v>
       </c>
       <c r="CD14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -4128,244 +4128,244 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.8790411739577983</v>
+        <v>0.8765593402794322</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8280067815599695</v>
+        <v>0.823985821937849</v>
       </c>
       <c r="E15" t="n">
-        <v>99.91538486447435</v>
+        <v>99.90756223993695</v>
       </c>
       <c r="F15" t="n">
-        <v>93.63869925384647</v>
+        <v>93.08298015299553</v>
       </c>
       <c r="G15" t="n">
-        <v>6.276685610627879</v>
+        <v>6.824582086941435</v>
       </c>
       <c r="H15" t="n">
-        <v>0.325771879332248</v>
+        <v>0.3282571815436758</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7125619829812098</v>
+        <v>0.7163552919826551</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5221153746691695</v>
+        <v>0.5241903178372597</v>
       </c>
       <c r="K15" t="n">
-        <v>4800</v>
+        <v>5225</v>
       </c>
       <c r="L15" t="n">
-        <v>2080</v>
+        <v>2253</v>
       </c>
       <c r="M15" t="n">
-        <v>555</v>
+        <v>593</v>
       </c>
       <c r="N15" t="n">
-        <v>1075</v>
+        <v>1161</v>
       </c>
       <c r="O15" t="n">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="P15" t="n">
-        <v>612</v>
+        <v>673</v>
       </c>
       <c r="Q15" t="n">
-        <v>424</v>
+        <v>470</v>
       </c>
       <c r="R15" t="n">
-        <v>607</v>
+        <v>666</v>
       </c>
       <c r="S15" t="n">
-        <v>289</v>
+        <v>321</v>
       </c>
       <c r="T15" t="n">
-        <v>660</v>
+        <v>721</v>
       </c>
       <c r="U15" t="n">
-        <v>417</v>
+        <v>448</v>
       </c>
       <c r="V15" t="n">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="W15" t="n">
-        <v>421</v>
+        <v>455</v>
       </c>
       <c r="X15" t="n">
-        <v>528</v>
+        <v>574</v>
       </c>
       <c r="Y15" t="n">
-        <v>541</v>
+        <v>594</v>
       </c>
       <c r="Z15" t="n">
         <v>83</v>
       </c>
       <c r="AA15" t="n">
-        <v>1925</v>
+        <v>2076</v>
       </c>
       <c r="AB15" t="n">
-        <v>2375.08</v>
+        <v>2582.04</v>
       </c>
       <c r="AC15" t="n">
-        <v>2086.08</v>
+        <v>2261.04</v>
       </c>
       <c r="AD15" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE15" t="n">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="AF15" t="n">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="AG15" t="n">
-        <v>521</v>
+        <v>559</v>
       </c>
       <c r="AH15" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="AI15" t="n">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="AJ15" t="n">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="AK15" t="n">
-        <v>313</v>
+        <v>342</v>
       </c>
       <c r="AL15" t="n">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="AM15" t="n">
-        <v>331</v>
+        <v>358</v>
       </c>
       <c r="AN15" t="n">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="AO15" t="n">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="AP15" t="n">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="AQ15" t="n">
-        <v>267</v>
+        <v>293</v>
       </c>
       <c r="AR15" t="n">
-        <v>273</v>
+        <v>301</v>
       </c>
       <c r="AS15" t="n">
         <v>47</v>
       </c>
       <c r="AT15" t="n">
-        <v>1168.72</v>
+        <v>1266.48</v>
       </c>
       <c r="AU15" t="n">
-        <v>1029.72</v>
+        <v>1113.48</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.842688710602327</v>
+        <v>0.8581258499479115</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.8499182626795033</v>
+        <v>0.8514153833359178</v>
       </c>
       <c r="AX15" t="n">
-        <v>95.64195163994198</v>
+        <v>97.65230184440755</v>
       </c>
       <c r="AY15" t="n">
-        <v>94.839210890144</v>
+        <v>94.60579058914529</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.8027407497979802</v>
+        <v>3.046511255262251</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.3063418611436905</v>
+        <v>0.3126916325087058</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.737161643297314</v>
+        <v>0.7453607476590591</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.5196584041509079</v>
+        <v>0.5260647712524217</v>
       </c>
       <c r="BD15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BE15" t="n">
-        <v>2400</v>
+        <v>2625</v>
       </c>
       <c r="BF15" t="n">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="BG15" t="n">
-        <v>554</v>
+        <v>602</v>
       </c>
       <c r="BH15" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="BI15" t="n">
-        <v>309</v>
+        <v>340</v>
       </c>
       <c r="BJ15" t="n">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="BK15" t="n">
-        <v>294</v>
+        <v>324</v>
       </c>
       <c r="BL15" t="n">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="BM15" t="n">
-        <v>329</v>
+        <v>363</v>
       </c>
       <c r="BN15" t="n">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="BO15" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="BP15" t="n">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="BQ15" t="n">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="BR15" t="n">
-        <v>268</v>
+        <v>293</v>
       </c>
       <c r="BS15" t="n">
         <v>36</v>
       </c>
       <c r="BT15" t="n">
-        <v>1206.36</v>
+        <v>1315.56</v>
       </c>
       <c r="BU15" t="n">
-        <v>1056.36</v>
+        <v>1147.56</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.9153936373132697</v>
+        <v>0.8949928306109529</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.8060953004404361</v>
+        <v>0.7965562605397802</v>
       </c>
       <c r="BX15" t="n">
-        <v>104.1888180890067</v>
+        <v>102.1628226354664</v>
       </c>
       <c r="BY15" t="n">
-        <v>92.43818761754891</v>
+        <v>91.56016971684572</v>
       </c>
       <c r="BZ15" t="n">
-        <v>11.75063047145778</v>
+        <v>10.60265291862062</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.3452018975208058</v>
+        <v>0.3438227305786459</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.6879623226651059</v>
+        <v>0.6873498363062516</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.5245723451874311</v>
+        <v>0.5223158644220975</v>
       </c>
       <c r="CD15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
